--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,58 +425,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Stakeholders</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Stakeholders</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>citation</t>
         </is>
       </c>
     </row>
@@ -476,17 +493,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-powered productivity, scan workflow, and manageability solutions tailored for SMBs into the Magellan printer. This includes features such as automated document handling, smart scan optimization, and AI-driven device management.</t>
+          <t>Develop new NGB keyed ink bottles supporting 6,000-page yield for black and 6,000-page yield for CMY, with CMY bottle size supporting over 8,000 pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Addresses SMB need for efficiency and ease of management, especially where IT resources are limited.</t>
+          <t>Higher yield bottles reduce frequency of replacement, enhance customer convenience, and lower total cost of ownership.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,17 +513,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires AI software integration, compatible hardware, and SMB portal support.</t>
+          <t>Bottle design, ink compatibility, printer hardware support</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Demonstrable AI-powered features in the product UI; workflow automation; measurable improvement in management tasks; positive feedback in SMB user testing.</t>
+          <t>Bottles must be able to reliably deliver 6,000 pages (black/CMY), and CMY bottles must have capacity for &gt;8,000 pages as validated in lab testing.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -514,9 +531,10 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,17 +544,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Design Magellan to deliver HP’s lowest business TCO for SMBs, with minimal intervention required for maintenance and supplies.</t>
+          <t>Ensure the new bottles and filling process achieve spill-free reliability during user operation and service.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SMBs prioritize ROI and cost-efficiency; low TCO is a key differentiator.</t>
+          <t>Spill-free operation is essential for user satisfaction and reducing warranty/service costs.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,17 +564,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'BA']</t>
+          <t>R&amp;D, End Users, Service</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Requires efficient consumables, high-yield tanks, and minimal service interventions.</t>
+          <t>Bottle design, NOA-F design, filling mechanism</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Documented TCO analysis showing Magellan has lowest TCO in HP SMB portfolio; validated by third-party or internal cost models.</t>
+          <t>User testing must show &lt;1% spill incidents across 1000 uses; no spills in standard service scenarios.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -564,9 +582,10 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -576,17 +595,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Customer-Replaceable Components (PHA, Maintenance Box)</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enable customer replaceability for key components (e.g., PHA, maintenance box) to reduce downtime and service costs. If out of warranty, service center support is required.</t>
+          <t>Integrate NOA-F with a metal foiled labyrinth and lid label, maintaining compatibility with existing push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SMBs lack dedicated IT; reducing service dependency and downtime is critical.</t>
+          <t>Improved NOA-F design enhances reliability and supports new bottle technology while leveraging existing mechanisms.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,17 +615,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'BA']</t>
+          <t>R&amp;D, Service, Manufacturing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Component design must allow safe and easy user replacement; service documentation required.</t>
+          <t>NOA-F design, compatibility with push-push and TDF</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>End users can replace specified components without technical support; replacement process validated in user testing.</t>
+          <t>NOA-F must pass reliability and compatibility testing with new and legacy mechanisms; functional in 100% of test cases.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -614,9 +633,10 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -626,37 +646,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Refilling</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Inks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Implement keyed bottles for ink refilling to prevent user errors and ensure compatibility.</t>
+          <t>Reuse the existing SuperAmp Si PHA and Magi/Nessie ink formulations with no reformulation required.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces risk of incorrect refilling and supports warranty/service quality.</t>
+          <t>Reduces development time and cost, leverages proven technology.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Quality']</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Requires design of ink tank and bottle interface.</t>
+          <t>PHA and ink compatibility with new system</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Keyed bottle system prevents incorrect installation in lab and field tests.</t>
+          <t>No changes required to ink formulation or PHA; validated in integration tests with new bottles and NOA-F.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -664,9 +684,10 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -676,17 +697,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>Reliability and Characterization Modelling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Develop a consolidated SMB portal for device and fleet management, targeting unmanaged/lightly managed SMBs.</t>
+          <t>Conduct reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Simplifies printer management for non-IT users, improving efficiency and user experience.</t>
+          <t>Ensures system meets performance and reliability standards over product life.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -696,27 +717,28 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing', 'R&amp;D Telemetry']</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires software development, integration with device firmware, and UX design for SMBs.</t>
+          <t>IDS, NOA-F, bottle design</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Portal is functional, user-friendly, and supports management of multiple devices; positive SMB user feedback.</t>
+          <t>Completion of reliability and characterization reports; all metrics meet internal thresholds.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -726,17 +748,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Support for PaaS (Platform as a Service)</t>
+          <t>Ink Stability Modelling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ensure Magellan supports Platform as a Service (PaaS) for cloud-enabled solutions and services.</t>
+          <t>Model ink stability in the tank and assess impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Addresses future-proofing and integration with evolving SMB IT environments.</t>
+          <t>Critical for maintaining consistent print quality and minimizing maintenance issues.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -746,27 +768,28 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'BA']</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Requires cloud connectivity and compliance with HP PaaS ecosystem.</t>
+          <t>Ink, tank design, IDS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Magellan can be registered and managed through HP PaaS platform; passes integration tests.</t>
+          <t>Modeling completed and reviewed; no adverse impact on PQ identified or mitigated.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -776,17 +799,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Non-PDL and PDL SKU Differentiation</t>
+          <t>NOA-F as Service Parts for Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Offer both Non-PDL and PDL SKUs with differentiated features: Non-PDL with SMB2.0 Solutions and Advanced View SMB portal; PDL SKU with improved print speed (25/20 ppm) and PDL/PS support.</t>
+          <t>Provide NOA-F as service parts to support warranty claims and in-warranty repairs.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Addresses different SMB needs and use-cases; expands market coverage.</t>
+          <t>Supports maintenance, reduces downtime, and enhances customer satisfaction.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,27 +819,28 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['Marketing', 'Tech Reg', 'DVAR']</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Requires SKU management, firmware variations, and testing for each variant.</t>
+          <t>NOA-F design, supply chain</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Both SKUs available; features validated as per specifications; performance benchmarks met.</t>
+          <t>NOA-F parts available in service inventory; service documentation updated.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -826,17 +850,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Angel Certification for PDL SKU</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ensure the PDL SKU achieves Blue Angel environmental certification.</t>
+          <t>Integrate Acumen 6 feature on the lid of the printer.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Supports sustainability goals and competitive positioning, especially in regulated markets.</t>
+          <t>Supports advanced features or security as required by new product line.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -846,27 +870,28 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg']</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Requires compliance with Blue Angel criteria and certification process.</t>
+          <t>Lid design, Acumen 6 integration</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PDL SKU receives official Blue Angel certification.</t>
+          <t>Acumen 6 feature functional and validated in system tests.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -876,17 +901,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>High Sustainability (60% RCP)</t>
+          <t>Factory Line Modifications for NOA-F and New Inks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Magellan must achieve 60% Recycled Content Plastic (RCP) in its construction, exceeding key competitors.</t>
+          <t>Modify existing SA14 production line for NOA-F and add Magi ink cartridge and labelling tool in Orcus 5.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Supports HP’s sustainability objectives and provides a market differentiator.</t>
+          <t>Ensures manufacturing capability for new product configuration.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,27 +921,28 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Marketing']</t>
+          <t>Manufacturing, R&amp;D</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Requires sourcing and manufacturing with high RCP; supply chain alignment.</t>
+          <t>Factory line availability, tool integration</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Product BOM and third-party certification confirm 60% RCP; marketing claims substantiated.</t>
+          <t>Line modifications completed and validated in pilot runs.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -926,47 +952,48 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Replaceable Maintenance Box Feature</t>
+          <t>Mold for 1 to 4 New Keyed Caps</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box as a new feature for Magellan.</t>
+          <t>Develop molds for 1 to 4 new keyed caps required for the new bottle system.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Addresses new customer segment needs and reduces service downtime.</t>
+          <t>Keyed caps are necessary for spill-free operation and correct bottle insertion.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality']</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Component design and user documentation; field test validation.</t>
+          <t>Bottle and cap design</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Users can replace maintenance box; feature validated in pilot deployments.</t>
+          <t>Molds produced and validated with new bottles in production tests.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -976,17 +1003,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years (Whichever First)</t>
+          <t>Support Customer-Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Provide a warranty covering 80,000 pages or 2 years, whichever comes first, for Magellan printers.</t>
+          <t>Design system so that PHA (Printhead Assembly) and NOA-F can be replaced by customers.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Meets SMB expectations for reliability and cost control.</t>
+          <t>Improves serviceability, reduces service costs, and enhances user experience.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -996,27 +1023,28 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['Quality', 'Marketing']</t>
+          <t>End Users, Service</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Warranty policy and service infrastructure alignment.</t>
+          <t>Hardware design, documentation</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Warranty terms clearly communicated; support infrastructure in place; tracked in warranty system.</t>
+          <t>Customer instructions provided; &gt;90% success in user replaceability testing.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1026,17 +1054,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Advanced Telemetry Requirements</t>
+          <t>Support New Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Implement advanced telemetry features for remote monitoring, diagnostics, and usage analytics, supporting both HP and SMB customer needs.</t>
+          <t>Ensure printer system supports a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Enables proactive support, fleet management, and product improvement.</t>
+          <t>Aligns with business goals to offer extended reliability and lower TCO.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1046,27 +1074,28 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'BA']</t>
+          <t>Product Management, End Users, Service</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Requires telemetry hardware/software integration; privacy/compliance review.</t>
+          <t>Hardware, consumables, IDS durability</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Telemetry data accessible via portal; supports diagnostics; compliant with regulations.</t>
+          <t>System passes accelerated life testing to 80,000 pages without failure.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 3, 12</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1076,47 +1105,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Support</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing functionality and full support through the HP App.</t>
+          <t>Use EPS foam packaging for the product to ensure safe transport and compliance.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SMBs expect mobile-first solutions and app-based management.</t>
+          <t>Protects product during shipping and meets regulatory/environmental standards.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing']</t>
+          <t>Packaging, Logistics, Compliance</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Requires app integration, firmware support, and user documentation.</t>
+          <t>Packaging design</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Mobile printing tested on major platforms; HP App fully supports Magellan; user acceptance testing passed.</t>
+          <t>Packaging passes drop and vibration tests; meets EPEAT3 and LOT4 requirements.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1126,45 +1156,1984 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ensure product complies with EPEAT3, LOT4, and Blue Angel standards for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mandatory for market access and environmental leadership.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Compliance, Product Management</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Design, materials, documentation</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Product certified under EPEAT3, LOT4, Blue Angel for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Input/Output Tray Changes for Tank Protrusion</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Modify input and output trays to accommodate tank protrusion and optimize size.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ensures physical compatibility and optimal printer footprint.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, End Users</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tray and tank design</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Trays operate without interference; printer passes all fit and function tests.</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4.3” CGD Display</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Enhances user interface and supports advanced features.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Display sourcing, UI software</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Display functional and meets HP UI guidelines; passes usability testing.</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar Tubes and New Tube Routing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Use Sayan Sibstar tubes with new routing and integration for the ink delivery system.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Improves reliability, reduces risk of ink flow issues, and leverages proven technology.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tube design, IDS integration</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>System passes ink flow and reliability tests; tubes meet durability targets.</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management Changes</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Update service station aerosol management with spit platform changes due to new tank design.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Prevents contamination and ensures system reliability with new tank.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Service station design, tank integration</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Aerosol emissions within HP standards; validated with new tank in place.</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Update</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Update carriage dynamic and force model to account for new tube routing and increased weights.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ensures print quality and mechanical reliability with new system configuration.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carriage design, tube integration</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Modeling completed; system passes print quality and durability tests.</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Paper Path Support for Increased Page Life</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Modify paper path components to support increased page life up to 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ensures mechanical durability and reliability for extended warranty.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Paper path design, materials</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Paper path passes durability testing to 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Design ink maintenance as a serviceable part to be replaced at service centers after 80,000 pages.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Supports extended product life and reduces total cost of ownership for users.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ink maintenance part design, service documentation</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Part replacement procedure documented; &gt;90% success in service center trials.</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>New Make-Break and FI Connection for IDS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Implement new make-break and FI (fluidic interconnect) connection for the ink delivery system, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Improves reliability and supports new bottle and tank sizes.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>IDS design, LEBI ink-tank, SHAID integration</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Connections pass reliability and leak testing; system supports new sizes and keying.</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Develop new startup algorithm and air management for the IDS to support new tank and bottle configuration.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ensures system reliability and print quality from first use.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>IDS design, startup sequence</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Startup process completes successfully in &gt;99% of first-use scenarios.</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>New Servicing and Startup Algorithm</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Implement new servicing and startup algorithm to support new consumables and system configuration.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ensures maintainability and reduces service events.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Service, R&amp;D, End Users</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Consumables, IDS, firmware</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Algorithm functional; service events reduced by &gt;10% compared to previous model.</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>New Print Quality Goals and Depletion Definition</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Set new print quality (PQ) goals and depletion metrics to align with new page yield definition.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ensures product performance meets customer expectations and business targets.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>PQ testing, yield definition</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PQ meets or exceeds defined targets in &gt;95% of test cases.</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi Module, Dune FW</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Reuse existing Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi module, and Dune firmware.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Reduces development time, leverages proven hardware and software.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hardware and firmware compatibility</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>All reused components pass integration and system tests.</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Integrate Gauss4.xx hardware and firmware security features into the product.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Meets evolving security standards and protects HP IP.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>R&amp;D, Security, Compliance</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>HW/FW integration, security requirements</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>System passes internal and external security audits.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Business Model and Services Support (PaaS, WorkFromHome, Flexworker)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Support for PaaS (Printing as a Service), WorkFromHome/Flexworker, and onboarding/S&amp;O path for Consumer, HPX, HP One, SMB Portal, and ECP.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Expands addressable market and aligns with strategic business initiatives.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Product Management, Sales, Marketing</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Solution integration, onboarding workflow</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>All target business models and onboarding paths supported and documented.</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Scan Solution and SMB/Enterprise Manageability</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Integrate scan solution, SMB manageability, and Enterprise support including WJA, HPSM, and JAM.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Meets requirements for SMB and Enterprise customers.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Product Management, Enterprise Sales, SMB Customers</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Solution integration, driver support</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>All solutions functional and validated in target environments.</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Clients &amp; Drivers Support (HPX, PSA, SUPD, UPD, EasyStart, USS, UFD)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility and ease of use for all customer segments.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>End Users, IT, Product Management</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Driver and client integration</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>All listed clients and drivers supported and pass installation tests.</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Schedule Adherence (POR and Launch)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Meet program schedule milestones as indicated (Q3'25 POR, HW checkpoints, bottle/NOA-F checkpoints, build stages, etc.).</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Critical for time-to-market and business commitments.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Program Management, R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>All development and integration activities</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>All checkpoints and builds completed on or before scheduled dates.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K Pages</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Supports reliability and reduces service interventions.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, End Users</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>PHA design, consumables</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA passes life testing to 65,000 pages.</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Warranty Life of 80k Pages or 2 Years</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Offer warranty coverage for 80,000 pages or 2 years, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Aligns with market expectations for durability and reliability.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Product Management, End Users, Service</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>System durability, consumables</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Warranty terms published; system passes required life tests.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Throughput 25/20 ppm (PDL: 25/19 ppm)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Printer must achieve throughput of 25/20 ppm (pages per minute), and 25/19 ppm for PDL (Page Description Language) SKU.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Meets competitive performance benchmarks.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Product Management, End Users, Sales</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Print engine, firmware</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Throughput verified in lab and field testing.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1 and 2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Design maintenance box for easy serviceability and replacement.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Reduces service time and cost, improves user experience.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Maintenance box design, documentation</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Maintenance box replaced in &lt;10 minutes in service trials.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SMB Solution Support</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Provide solution features required for SMB customers.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Enables penetration in SMB segment and supports strategic goals.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Solution and feature integration</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SMB features functional and validated in SMB test cases.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK Variant (Flexible Priority)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Consider hosting a 12,000-page CMYK variant as a flexible option.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Provides potential for higher yield offering if market demand justifies.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Market analysis, design feasibility</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Variant defined and business case reviewed if market opportunity arises.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Trade Page Yield of 6K (Flexible Priority)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Consider supporting trade page yield of 6,000 pages as a flexible option.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Allows for SKUs tailored to specific market requirements.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Market analysis, design feasibility</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Trade SKU defined and business case reviewed if needed.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI-powered productivity, scan workflow, and manageability solutions tailored for SMBs into the Magellan printer. This includes features such as automated document handling, smart scan optimization, and AI-driven device management.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Addresses SMB need for efficiency and ease of management, especially where IT resources are limited.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Requires AI software integration, compatible hardware, and SMB portal support.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Demonstrable AI-powered features in the product UI; workflow automation; measurable improvement in management tasks; positive feedback in SMB user testing.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 11</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Design Magellan to deliver HP’s lowest business TCO for SMBs, with minimal intervention required for maintenance and supplies.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SMBs prioritize ROI and cost-efficiency; low TCO is a key differentiator.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Requires efficient consumables, high-yield tanks, and minimal service interventions.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Documented TCO analysis showing Magellan has lowest TCO in HP SMB portfolio; validated by third-party or internal cost models.</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 11</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Customer-Replaceable Components (PHA, Maintenance Box)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Enable customer replaceability for key components (e.g., PHA, maintenance box) to reduce downtime and service costs. If out of warranty, service center support is required.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT; reducing service dependency and downtime is critical.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Component design must allow safe and easy user replacement; service documentation required.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>End users can replace specified components without technical support; replacement process validated in user testing.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Keyed Bottles for Ink Refilling</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Implement keyed bottles for ink refilling to prevent user errors and ensure compatibility.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Reduces risk of incorrect refilling and supports warranty/service quality.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>['Supplies Quality', 'Quality']</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Requires design of ink tank and bottle interface.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Keyed bottle system prevents incorrect installation in lab and field tests.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SMB Portal for Printer Management</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Develop a consolidated SMB portal for device and fleet management, targeting unmanaged/lightly managed SMBs.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Simplifies printer management for non-IT users, improving efficiency and user experience.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>['GXD', 'Marketing', 'R&amp;D Telemetry']</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Requires software development, integration with device firmware, and UX design for SMBs.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Portal is functional, user-friendly, and supports management of multiple devices; positive SMB user feedback.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 10</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Support for PaaS (Platform as a Service)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ensure Magellan supports Platform as a Service (PaaS) for cloud-enabled solutions and services.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Addresses future-proofing and integration with evolving SMB IT environments.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>['Tech Reg', 'BA']</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Requires cloud connectivity and compliance with HP PaaS ecosystem.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Magellan can be registered and managed through HP PaaS platform; passes integration tests.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Non-PDL and PDL SKU Differentiation</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Offer both Non-PDL and PDL SKUs with differentiated features: Non-PDL with SMB2.0 Solutions and Advanced View SMB portal; PDL SKU with improved print speed (25/20 ppm) and PDL/PS support.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Addresses different SMB needs and use-cases; expands market coverage.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Tech Reg', 'DVAR']</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Requires SKU management, firmware variations, and testing for each variant.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Both SKUs available; features validated as per specifications; performance benchmarks met.</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Blue Angel Certification for PDL SKU</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ensure the PDL SKU achieves Blue Angel environmental certification.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Supports sustainability goals and competitive positioning, especially in regulated markets.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Requires compliance with Blue Angel criteria and certification process.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>PDL SKU receives official Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>High Sustainability (60% RCP)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Magellan must achieve 60% Recycled Content Plastic (RCP) in its construction, exceeding key competitors.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Supports HP’s sustainability objectives and provides a market differentiator.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Requires sourcing and manufacturing with high RCP; supply chain alignment.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Product BOM and third-party certification confirm 60% RCP; marketing claims substantiated.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Replaceable Maintenance Box Feature</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Introduce a replaceable maintenance box as a new feature for Magellan.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Addresses new customer segment needs and reduces service downtime.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Component design and user documentation; field test validation.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Users can replace maintenance box; feature validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Warranty: 80k Pages or 2 Years (Whichever First)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Provide a warranty covering 80,000 pages or 2 years, whichever comes first, for Magellan printers.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Meets SMB expectations for reliability and cost control.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>['Quality', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Warranty policy and service infrastructure alignment.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Warranty terms clearly communicated; support infrastructure in place; tracked in warranty system.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Advanced Telemetry Requirements</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Implement advanced telemetry features for remote monitoring, diagnostics, and usage analytics, supporting both HP and SMB customer needs.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Enables proactive support, fleet management, and product improvement.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'BA']</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Requires telemetry hardware/software integration; privacy/compliance review.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Telemetry data accessible via portal; supports diagnostics; compliant with regulations.</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 3, 12</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Support</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Enable seamless mobile printing functionality and full support through the HP App.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SMBs expect mobile-first solutions and app-based management.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>['GXD', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Requires app integration, firmware support, and user documentation.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Mobile printing tested on major platforms; HP App fully supports Magellan; user acceptance testing passed.</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9, 10</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>Perfect Print and Perfect Scan AI Solutions</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Deliver AI-driven 'Perfect Print' and 'Perfect Scan' features for superior print and scan quality, error reduction, and workflow efficiency.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Key differentiator for Magellan; aligns with SMB need for quality and productivity.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>['GXD', 'Marketing', 'R&amp;D Telemetry']</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Requires AI feature development, integration, and validation.</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Features available in product; quality improvements measurable; positive SMB feedback.</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I53" t="n">
         <v>0.92</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Magellan MRD, Page 7, 11</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,17 +493,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with Increased Page Yield</t>
+          <t>NGB Keyed Ink Bottles with Higher Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles supporting 6,000-page yield for black and CMY, with CMY bottle size supporting more than 8,000 pages. Bottles must be compatible with the new NOA-F system and support spill-free reliability.</t>
+          <t>Develop new generation bottle (NGB) keyed ink bottles with 6,000-page yield for black and CMY, and bottle size for CMY to exceed 8,000 pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Higher yield bottles reduce frequency of replacement and operating costs, improving customer satisfaction and competitiveness in the CISS segment.</t>
+          <t>To increase ink yield and reduce frequency of bottle replacement, improving customer satisfaction and competitive positioning against CISS competitors.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -513,17 +513,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Customers</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires NOA-F compatibility, bottle keying design, and reliability validation.</t>
+          <t>Requires compatibility with new or existing ink tanks and IDS system.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bottles are available in the specified yields, pass spill-free reliability testing, and are compatible with the NOA-F system.</t>
+          <t>NGB bottles are available for black and CMY, yield at least 6,000 pages for black, 6,000 for CMY, and CMY bottle size supports &gt;8,000-page yield. Verified by yield testing.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -544,17 +544,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Implement a NOA-F (Next-Gen Output Assembly - Foiled) with a metal foiled labyrinth and a lid label. No change to the click-on push-push and TDF mechanisms.</t>
+          <t>Ensure new ink bottles and filling process are spill-free during installation and use.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Enhances ink delivery system reliability and supports new service part requirements.</t>
+          <t>Spill-free operation is a critical user experience feature, reducing mess and increasing trust in HP’s CISS system.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -564,21 +564,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Manufacturing</t>
+          <t>End Users, R&amp;D, Customer Support</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Must be compatible with existing push-push and TDF mechanisms.</t>
+          <t>Bottle design, IDS, and tank interface.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NOA-F design includes metal foiled labyrinth and lid label, and passes integration and reliability tests.</t>
+          <t>No ink spills during standard bottle installation and use, confirmed via usability and reliability testing.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -595,17 +595,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Support for Customer Replaceable PHA and NOA-F</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Design the printer to allow end customers to replace the Printhead Assembly (PHA) and NOA-F components without requiring service center intervention.</t>
+          <t>Implement NOA-F (non-original ink avoidance filter) with a metal foiled labyrinth and a lid label, maintaining current click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces downtime for end users, enhancing product appeal for SMB and enterprise customers.</t>
+          <t>Enhances ink security, prevents non-original ink usage, and maintains compatibility with existing mechanisms.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -615,21 +615,21 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>End Customers, Service, Product Management</t>
+          <t>R&amp;D, Supplies, Quality Assurance</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Requires modular design for easy replacement and supporting documentation.</t>
+          <t>NOA-F design, bottle interface, TDF mechanism.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>End customers can replace PHA and NOA-F using provided instructions within 10 minutes, with no tools required beyond those supplied in the box.</t>
+          <t>NOA-F with metal foiled labyrinth and lid label passes ink authentication and leak testing, and works with push-push and TDF.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -646,17 +646,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80,000 Pages</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The printer must support a new warranty page life goal of 80,000 pages, aligning with new service and reliability targets.</t>
+          <t>Design printer to allow customers to replace the Printhead Assembly (PHA) and NOA-F without service center intervention.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Extends product life and reduces total cost of ownership for customers, strengthening HP's competitive position.</t>
+          <t>Improves serviceability, reduces downtime and service costs, and aligns with customer expectations for ease of maintenance.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Customers</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Requires reliability validation of all critical components for 80k page life.</t>
+          <t>PHA and NOA-F mechanical design, user documentation.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Printer passes reliability tests and maintains print quality for at least 80,000 pages under normal operating conditions.</t>
+          <t>End users can successfully replace PHA and NOA-F following provided instructions, confirmed by usability tests.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -697,41 +697,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Size Optimization for Increased Tank Protrusion</t>
+          <t>New Warranty Page Life Goal of 80,000 Pages</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Optimize printer chassis and tray design to accommodate increased tank size and protrusion, including necessary changes to input and output trays.</t>
+          <t>Set and support a new warranty page life goal of 80,000 pages for the printer.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ensures that larger ink tanks fit within the device footprint and that paper handling is not compromised.</t>
+          <t>Extends product life, reduces replacement frequency, and increases perceived value for high-volume users.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Product Management</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires coordination with tank and tray suppliers, as well as ID (Industrial Design) team.</t>
+          <t>Component durability, consumables life, warranty policy.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Printer can accommodate new tank size without compromising tray functionality or device stability.</t>
+          <t>Printer operates reliably for 80,000 pages under standard usage conditions; verified via accelerated life testing.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -748,41 +748,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.3” CGD Display Integration</t>
+          <t>EPEAT3, LOT4, Blue Angel Compliance for PDL SKU</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch color graphical display (CGD) into the printer for enhanced user interaction and control.</t>
+          <t>Ensure the PDL SKU meets EPEAT3, LOT4, and Blue Angel environmental and efficiency certifications.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Improves user experience by providing better visibility and interaction for setup, maintenance, and print management.</t>
+          <t>Necessary for regulatory compliance and to meet sustainability goals, especially for institutional and enterprise customers.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>End Users, UI/UX Team, Product Management</t>
+          <t>Compliance, Product Management, Enterprise Customers</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Requires UI software adaptation and mechanical integration.</t>
+          <t>Design, materials, and energy consumption features.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Printer includes a 4.3” CGD, which is fully functional and supports all required workflows.</t>
+          <t>PDL SKU is certified for EPEAT3, LOT4, and Blue Angel; certification documents available.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -799,41 +799,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Input and Output Tray Changes to Align with Tank Protrusion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Implement aerosol management in the service station, including changes to the spit platform to accommodate the new tank design.</t>
+          <t>Modify input and output trays to accommodate changes in printer dimensions due to tank protrusion and size optimization.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Prevents ink aerosol contamination, supporting reliability and compliance with health/safety standards.</t>
+          <t>Ensures reliable paper handling and maintains compact form factor despite larger tanks.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>R&amp;D, Compliance, Service</t>
+          <t>Mechanical Engineering, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Depends on final tank and service station design.</t>
+          <t>Tank design, paper path engineering.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Aerosol management system is in place and passes internal contamination and safety tests.</t>
+          <t>Trays function properly and fit with new tank design; confirmed by fit and functional tests.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -850,41 +850,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paper Path Durability for Increased Page Life</t>
+          <t>4.3-inch CGD Display</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Redesign the paper path to support increased page life, aligning with the new 80k warranty goal.</t>
+          <t>Integrate a 4.3-inch color graphic display (CGD) for improved user interface and control.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ensures consistent print quality and reduces paper jams or wear over the extended device lifecycle.</t>
+          <t>Enhances user experience by providing clear, accessible information and controls.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Product Management</t>
+          <t>End Users, UI/UX, Product Management</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Requires material and design validation for extended use.</t>
+          <t>Electrical design, firmware, UI development.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paper path components show no significant wear or increased jam rate after 80,000 pages in testing.</t>
+          <t>4.3-inch CGD is functional, meets brightness and resolution specs, and passes user acceptance tests.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -901,17 +901,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part Post-80k Life</t>
+          <t>Service Station Aerosol Management for New Tank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Design the ink maintenance system as a serviceable part that can be replaced at a service center after the device reaches 80,000 pages.</t>
+          <t>Redesign service station aerosol management system to accommodate changes from new tank integration.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Extends device life and supports sustainability goals by allowing replacement of high-wear components.</t>
+          <t>Prevents ink aerosol contamination due to new tank design, maintaining print quality and reliability.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -921,21 +921,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Service, Sustainability, End Customers</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Requires modular design and clear service documentation.</t>
+          <t>Service station and tank design.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Ink maintenance part is replaceable at service centers, with process documented and validated.</t>
+          <t>Aerosol containment meets HP standards; verified by environmental and reliability tests.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -952,17 +952,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Develop a new IDS (Ink Delivery System) startup algorithm and air management system to support improved reliability and startup performance.</t>
+          <t>Update paper path design to support increased page life and reliability for high duty cycle usage.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ensures consistent ink flow and minimizes startup issues, enhancing print reliability.</t>
+          <t>Required to ensure reliable operation up to the 80,000-page warranty goal.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -972,21 +972,21 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Firmware, R&amp;D, Service</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Requires integration with IDS hardware and firmware.</t>
+          <t>Paper path engineering, component durability.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Startup algorithm and air management system pass reliability and performance tests.</t>
+          <t>Paper jams and misfeeds remain within HP’s acceptable limits over 80,000 pages; verified by life testing.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid for Authentication</t>
+          <t>Ink Maintenance as a Serviceable Part Post-80K Life</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 authentication feature on the ink bottle lid for enhanced security and anti-counterfeiting.</t>
+          <t>Design ink maintenance components to be serviceable by service centers after 80,000 pages.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Protects HP’s ink revenue and prevents use of unauthorized consumables.</t>
+          <t>Supports extended printer life and cost-effective post-warranty service.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1023,21 +1023,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Security, Supplies, End Customers</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware support for Acumen 6.</t>
+          <t>Component modularity, service documentation.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>All bottles feature Acumen 6 on lid and pass authentication tests.</t>
+          <t>Service centers can replace ink maintenance parts post-80,000 pages; confirmed by service procedure validation.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Blue Angel and EPEAT3/LOT4 Compliance</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ensure printer meets Blue Angel, EPEAT3, and LOT4 environmental requirements for the PDL SKU.</t>
+          <t>Implement new make-break and fluidic interconnect (FI) connections for the IDS (Ink Delivery System), leveraging LEBI ink-tank with increased size and keying.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Supports sustainability goals and required certifications for key markets.</t>
+          <t>Supports higher ink volumes, improved reliability, and security against non-genuine supplies.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1074,21 +1074,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Compliance, Marketing, Product Management</t>
+          <t>R&amp;D, Supplies, Quality Assurance</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Requires coordination with regulatory and certification teams.</t>
+          <t>IDS, bottle, and tank design.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Printer receives Blue Angel, EPEAT3, and LOT4 certifications for PDL SKU.</t>
+          <t>IDS make-break and FI connections function as designed and meet reliability targets; verified by engineering tests.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1105,37 +1105,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SMB Solution and Manageability Support</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Provide SMB manageability features including scan solutions and enterprise support for WJA, HPSM, and JAM.</t>
+          <t>Develop a new IDS startup algorithm and air management system to ensure reliable ink flow and startup performance.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Addresses SMB and enterprise customer needs for device management and integration into existing IT environments.</t>
+          <t>Critical for print quality, reliability, and customer satisfaction, especially with new tank and bottle sizes.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SMB Customers, IT Admins, Product Management</t>
+          <t>R&amp;D, Firmware, Quality Assurance</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Requires software and firmware support for enterprise management tools.</t>
+          <t>Firmware, IDS hardware.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Printer supports WJA, HPSM, JAM, and SMB scan/manageability features.</t>
+          <t>Printer starts up reliably under all operating conditions; confirmed by startup and reliability testing.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1156,37 +1156,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Support for PaaS (Printing as a Service) Business Model</t>
+          <t>New Print Quality (PQ) Goals and Depletion Metrics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Enable device features and software integration to support Printing as a Service (PaaS) for consumer, SMB, and enterprise segments.</t>
+          <t>Establish new print quality goals and depletion metrics to align with increased yield and page life.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aligns with HP’s strategic shift to service-based business models and recurring revenue streams.</t>
+          <t>Ensures print quality is maintained throughout the extended product lifecycle and higher yields.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Business Model, Product Management, IT</t>
+          <t>R&amp;D, Quality Assurance, End Users</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Requires integration with HP’s service platforms and support for remote device management.</t>
+          <t>Ink formulation, IDS, firmware.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Device is compatible with PaaS workflows and passes integration tests with HP service platforms.</t>
+          <t>Print quality remains within HP standards for the defined page yield; validated by print quality and depletion tests.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 ppm (PDL: 25/19 ppm)</t>
+          <t>Support for Consumer, SMB, and Enterprise Business Models</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Printer must achieve throughput speeds of 25 ppm (pages per minute) for standard, and 25/19 ppm for PDL SKUs.</t>
+          <t>Product and solution must support Consumer, SMB, and Enterprise business models, including PaaS, WorkFromHome, and Flexworker services.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Meets market expectations for performance and supports competitive positioning.</t>
+          <t>Expands addressable market and aligns with HP’s strategic intent to protect and grow share across segments.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1227,21 +1227,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>End Customers, Product Management, R&amp;D</t>
+          <t>Business, Product Management, Sales</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware tuning for speed optimization.</t>
+          <t>Firmware, software, solutions integration.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Printer achieves specified throughput in standard and PDL modes in benchmark tests.</t>
+          <t>Product is configurable for all business models and passes acceptance tests for each segment.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1258,37 +1258,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K Flexibility</t>
+          <t>Integration with HPX, PSA, SUPD, UPD, EasyStart, USS, UFD Drivers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Provide flexibility in hosting 12,000-page CMYK and 6,000-page trade SKUs as needed for different markets.</t>
+          <t>Ensure compatibility and integration with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD drivers and client software.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Enables product line customization for different market segments and maximizes addressable market.</t>
+          <t>Critical for seamless deployment, management, and user experience across customer environments.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marketing, Product Management</t>
+          <t>End Users, IT, Product Management</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Requires SKU management and validation of different bottle capacities.</t>
+          <t>Firmware, software development.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Both 12K-CMYK and 6K trade SKUs are available and validated for target markets.</t>
+          <t>All listed drivers and client software are supported and pass integration tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1309,17 +1309,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>Compliance with HP Security Standards (Gauss4.xx)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ensure that all ink bottles provide spill-free reliability during installation and use, in line with new bottle and tank designs.</t>
+          <t>Implement hardware and firmware security features in line with Gauss4.xx standard.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Reduces mess and customer dissatisfaction, improving overall user experience.</t>
+          <t>Protects HP’s intellectual property, customer data, and device security.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1329,21 +1329,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>End Customers, Product Management, R&amp;D</t>
+          <t>Security, IT, Enterprise Customers</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Requires bottle and tank interface redesign, validation testing.</t>
+          <t>Firmware, hardware design.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>All bottle installations pass spill-free reliability testing under normal use conditions.</t>
+          <t>Security features pass HP security audits and meet Gauss4.xx requirements.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>SuperAmp PHA Life at 65,000 Pages</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation in the new product.</t>
+          <t>Ensure SuperAmp Printhead Assembly (PHA) achieves a minimum life of 65,000 pages.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Reduces development time and cost by reusing proven components and consumables.</t>
+          <t>Critical for reducing maintenance frequency and supporting high-volume printing.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Requires compatibility validation with new system.</t>
+          <t>Printhead design, ink compatibility.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks operate reliably in new printer without reformulation.</t>
+          <t>SuperAmp PHA meets or exceeds 65,000-page life in reliability testing.</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1411,17 +1411,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IDS Make-Break and FI Connection Enhancement</t>
+          <t>Warranty Life of 2 Years or Specified Pages</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Enhance IDS (Ink Delivery System) with improved make-break and FI (fluidic interface) connections, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+          <t>Support a warranty life of 2 years or the specified page count, whichever comes first.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Improves reliability and enables support for larger ink tanks and keyed bottles.</t>
+          <t>Aligns with market expectations and supports HP’s competitive positioning.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1431,25 +1431,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Management</t>
+          <t>Service, Product Management, End Users</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Depends on final ink-tank and connection design.</t>
+          <t>Component reliability, warranty policy.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>IDS passes reliability and compatibility testing with new tanks and bottles.</t>
+          <t>Warranty is honored for 2 years or the specified page count; policy is documented and communicated.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1462,37 +1462,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging Integration</t>
+          <t>Throughput of 25/20 ppm (PDL: 25/19 ppm)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Integrate EPS foam packaging for improved product protection during shipment and handling.</t>
+          <t>Achieve print speeds of 25/20 pages per minute (ppm), with PDL variants at 25/19 ppm.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Reduces damage during transit, improving customer satisfaction and reducing returns.</t>
+          <t>Meets performance requirements for target segments and maintains competitiveness.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Logistics, Manufacturing, End Customers</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Requires packaging design update and drop testing.</t>
+          <t>Engine design, firmware.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>EPS foam packaging passes drop and vibration tests according to HP standards.</t>
+          <t>Printer achieves specified throughput in standard benchmark tests.</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1506,173 +1506,173 @@
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>Serviceability of Maintenance Box</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-powered productivity, scan workflow, and manageability solutions into the Magellan printer to simplify business operations for SMB customers.</t>
+          <t>Design maintenance box to be easily serviceable for end users or service centers.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AI solutions address SMB needs for efficiency and ROI, making printer management easier for non-IT users.</t>
+          <t>Reduces downtime and service costs, improving customer satisfaction.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Requires AI software development and integration with SMB portal.</t>
+          <t>Maintenance box design, documentation.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>AI features for print, scan, and device management are fully functional and accessible via the SMB portal; usability testing with target users demonstrates improved efficiency.</t>
+          <t>Maintenance box can be replaced by end users or service centers; confirmed by usability testing.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>SMB Solution and Manageability Features</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Design Magellan to deliver the lowest TCO in HP's business printer portfolio, focusing on cost efficiency for SMBs.</t>
+          <t>Provide solution features and manageability for SMBs, including scan solutions and SMB portal integration.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SMBs prioritize ROI and cost efficiency; lowest TCO is a key differentiator.</t>
+          <t>Addresses SMB segment needs for manageability and workflow integration.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['Marketing', 'BA']</t>
+          <t>SMB Customers, Product Management, IT</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Requires optimization of ink usage, maintenance, and supplies costs.</t>
+          <t>Firmware, software, solutions integration.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Third-party validation or internal analysis confirms Magellan's TCO is lower than competitors and existing HP business printers for target usage profiles.</t>
+          <t>SMB manageability features are functional and pass acceptance tests with SMB customers.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Host 12K-CMYK Trade Page (Flexible)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ensure that at least 60% of the printer's plastic content is from recycled sources, exceeding competitor benchmarks.</t>
+          <t>Design flexibility to host 12,000-page CMYK trade page as a future option.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sustainability is a top customer and corporate priority; differentiates HP from Epson (30%) and others.</t>
+          <t>Allows future scalability and support for higher-yield options as market demands evolve.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Marketing']</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sourcing of recycled materials, regulatory compliance.</t>
+          <t>Tank and bottle design, IDS scalability.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bill of materials and third-party audits confirm 60% RCP in final product.</t>
+          <t>Platform design allows for future 12K-CMYK option without major redesign.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>First Business Ink Tank Printer for HP</t>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Develop and launch HP's first business-class ink tank printer, targeting the CISS PLE Hi segment.</t>
+          <t>Integrate advanced AI-driven productivity features, scan workflow automation, and manageability solutions into the Magellan printer to simplify business operations for SMBs.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Addresses a gap in HP's portfolio and captures new market share in a growing segment.</t>
+          <t>Target SMBs demand efficiency and minimal IT intervention. AI features and manageability are key differentiators for Magellan.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1682,17 +1682,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['Marketing', 'R&amp;D Telemetry']</t>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Tech Reg, Prod Steward, BA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>New hardware platform development; CISS technology integration.</t>
+          <t>Requires AI software integration and compatible hardware.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Product launch with ink tank technology, positioned and marketed as HP's first business ink tank printer.</t>
+          <t>Magellan printer delivers AI-powered scan and print workflows; centralized management portal is functional and accessible for SMB users.</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 6, 7, 12</t>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1713,50 +1713,50 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Replaceable Maintenance Box</t>
+          <t>Lowest Business TCO (Total Cost of Ownership)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Introduce a user-replaceable maintenance box to reduce service intervention and downtime for SMB customers.</t>
+          <t>Design Magellan to deliver HP’s lowest business TCO through optimized ink usage, minimal maintenance, and efficient consumables.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Reduces maintenance costs and complexity for businesses without dedicated IT support.</t>
+          <t>SMBs are highly cost-sensitive and seek maximum ROI; low TCO is a major purchase driver.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['Quality', 'Service', 'Marketing']</t>
+          <t>Marketing, BA, Supplies Quality</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Design and supply chain for replaceable parts; user training materials.</t>
+          <t>Requires efficient ink tank system and durable components.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>End users can replace the maintenance box with minimal tools; documentation and support materials provided.</t>
+          <t>Independent testing confirms Magellan has the lowest TCO in its class compared to competitors.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 11</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1764,17 +1764,17 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SMB Device Management Portal</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Provide a consolidated online portal for SMB customers to manage multiple printers, monitor usage, and access support.</t>
+          <t>Enable the maintenance box to be easily replaceable by customers without technical support.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Simplifies fleet management for non-IT users in SMBs; enhances customer experience.</t>
+          <t>Target SMBs lack dedicated IT support; easy maintenance reduces downtime and support costs.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'Marketing']</t>
+          <t>Quality, R&amp;D Telemetry, DVAR, Tech Reg, Prod Steward</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Integration with device firmware, cloud infrastructure.</t>
+          <t>Design for tool-less replacement and clear instructions.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Portal is accessible, supports multi-device management, and passes usability tests with target users.</t>
+          <t>User can replace maintenance box within 5 minutes using included instructions, with no tools required.</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1815,17 +1815,17 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Customer Replaceable Keyed Bottles</t>
+          <t>Serviceability: PHA and MINK at Service Centre</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles for easy, error-proof refilling by customers, minimizing service calls and spillage.</t>
+          <t>Implement serviceability protocols: PHA (customer replaceable) and MINK (service center replaceable) for key components, prioritizing customer replaceable where possible.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Supports SMBs without IT staff; reduces user errors and maintenance needs.</t>
+          <t>Reduces service costs and downtime for SMBs, aligning with limited IT resources.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Service']</t>
+          <t>Quality, DVAR, Tech Reg, Prod Steward</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Design and manufacturing of keyed bottles; compatibility with printer hardware.</t>
+          <t>Component design and documentation.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bottles can only fit the correct tank; user testing confirms ease of use and prevention of errors.</t>
+          <t>At least 80% of serviceable parts are customer-replaceable; others are service center replaceable.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1866,41 +1866,41 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>Keyed Bottles for Ink Refilling</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Offer a warranty covering either 80,000 pages printed or 2 years, whichever comes first.</t>
+          <t>Design ink bottles with unique keying to prevent misfilling and ensure proper use with Magellan printers.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Builds customer trust and supports the SMB use case for reliability and durability.</t>
+          <t>Prevents user error, reduces support calls, and protects printer integrity.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['Quality', 'Service', 'Marketing']</t>
+          <t>Supplies Quality, Quality, BA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Service infrastructure and warranty policy alignment.</t>
+          <t>Bottle and tank design.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Warranty terms are clearly stated in product materials and honored in all supported markets.</t>
+          <t>Only correct bottle fits the corresponding tank; user testing shows zero misfills in 100 attempts.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1917,50 +1917,50 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PHA – Customer Replaceable and MINK at Service Centre</t>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Design for customer replaceable PHA (Primary Handling Assembly) and MINK (maintenance kit) at service centers, with a target for customer replaceability if out of warranty.</t>
+          <t>Offer a non-PDL SKU that supports SMB2.0 solutions and integrates with the Advanced View SMB portal for device management.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Minimizes downtime and service costs for SMBs; aligns with low-intervention goals.</t>
+          <t>Addresses needs of unmanaged/lightly managed SMBs for centralized management without complex IT.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['Service', 'Quality']</t>
+          <t>GXD, Marketing, R&amp;D Telemetry</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Design for serviceability; training and documentation.</t>
+          <t>Portal software availability and integration.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>PHA is customer replaceable; MINK replaceable at service centers; instructions provided.</t>
+          <t>Non-PDL SKU ships with SMB2.0 and portal access enabled; portal manages all connected devices.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1968,17 +1968,17 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB 2.0 Solutions and Advanced View SMB Portal</t>
+          <t>PDL SKU: Higher Print Speeds and PDL/PS Support</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ensure non-PDL SKUs support SMB 2.0 Solutions and provide access to the Advanced View SMB portal.</t>
+          <t>Provide a PDL SKU with improved print speeds (target 25/20 ppm) and support for PDL/PS (Page Description Language/PostScript).</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Delivers differentiated experience for SMBs via software and services.</t>
+          <t>Meets business needs for faster printing and compatibility with advanced workflows.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1988,21 +1988,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'Marketing']</t>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Software integration; portal development.</t>
+          <t>Hardware capability and firmware support.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Non-PDL SKUs ship with SMB 2.0 Solutions and portal access enabled.</t>
+          <t>PDL SKU achieves 25/20 ppm; passes compatibility tests with PDL/PS workflows.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2019,37 +2019,37 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PDL SKU: Increased Print Speed and PDL/PS Support</t>
+          <t>Blue Angel Certification for PDL SKU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PDL SKUs must support print speeds of at least 25/20 ppm (improvement over current 25/19), and include PDL/PS (Page Description Language/PostScript) support.</t>
+          <t>Ensure the PDL SKU meets Blue Angel environmental certification requirements.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Meets needs of higher-end SMBs and competitive positioning.</t>
+          <t>Environmental compliance is increasingly required in tenders and valued by SMBs.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Marketing']</t>
+          <t>Prod Steward, Tech Reg, Quality</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hardware and firmware capability; PDL/PS licensing.</t>
+          <t>Design and materials selection.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>PDL SKU achieves target speeds in lab tests; PDL/PS support verified by print job compatibility.</t>
+          <t>PDL SKU receives Blue Angel certification prior to launch.</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2070,50 +2070,50 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Blue Angel Certification for PDL SKU</t>
+          <t>First OJ Pro with Ink Tanks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Obtain Blue Angel environmental certification for the PDL SKU.</t>
+          <t>Magellan to be the first HP OfficeJet Pro product with ink tank technology, targeting CISS PLE Hi segment.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Addresses environmental and regulatory requirements; enhances sustainability credentials.</t>
+          <t>Fills a gap in HP’s portfolio and addresses market shift toward CISS in SMB segment.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Prod Steward']</t>
+          <t>Marketing, GXD, BA, R&amp;D Telemetry</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Design and documentation for certification process.</t>
+          <t>New product development and positioning.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>PDL SKU receives Blue Angel certification prior to launch.</t>
+          <t>Product is launched as HP’s first OJ Pro with ink tanks; marketing materials reflect this.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 6</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2121,50 +2121,50 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>Perfect Print and Perfect Scan AI Solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing through the HP App for Magellan users.</t>
+          <t>Incorporate AI-powered features for optimal print and scan quality, including error correction and workflow automation.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mobile printing is a key use case for modern SMBs; increases product appeal.</t>
+          <t>AI features differentiate Magellan and address SMB needs for efficiency and quality.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing']</t>
+          <t>GXD, Marketing, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HP App integration; testing across platforms.</t>
+          <t>AI algorithm development and integration.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Users can print from mobile devices using the HP App; compatibility with iOS and Android confirmed.</t>
+          <t>AI-driven print/scan features demonstrably improve quality and reduce errors in independent tests.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9</t>
+          <t>Magellan MRD, Page 7, 11</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2172,50 +2172,305 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
+          <t>Consolidated SMB Portal for Device Management</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Develop a consolidated portal for SMBs to manage all Magellan printers and related devices from a single interface.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Simplifies device management for businesses without dedicated IT.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Portal software development and cloud infrastructure.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Portal enables registration, monitoring, and management of all connected devices; user satisfaction &gt;90% in pilot.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Maintenance-Free or Less Maintenance Design</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Engineer Magellan for maintenance-free or minimal maintenance operation, with fewer parts requiring replacement over product life.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Reduces operational burden and cost for SMBs with little IT support.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Quality, Prod Steward, Tech Reg, DVAR</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Component reliability and design innovation.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Over 80% of units require no major maintenance during 2-year warranty period.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% Recycled Content Plastic (RCP)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Magellan to be manufactured using at least 60% recycled content plastic, exceeding competitors’ sustainability benchmarks.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Prod Steward, Tech Reg, Marketing, Quality</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Supply chain readiness and material sourcing.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bill of materials and certification confirm 60% RCP in all relevant parts.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Enable seamless mobile printing capabilities through the HP App for Magellan users.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Supports modern SMB workflows and BYOD environments.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>App integration and printer firmware support.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Users can print from mobile devices via HP App with &gt;95% success rate in testing.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PaaS (Platform as a Service) Support</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Magellan must support HP’s PaaS offerings, enabling integration with cloud-based solutions and services.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Aligns with HP’s strategic goals for PaaS acceleration and recurring revenue.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>PaaS platform readiness and printer compatibility.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Magellan is certified for PaaS integration and supports all required APIs.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Telemetry Requirements</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Implement telemetry features for remote monitoring, diagnostics, and usage analytics.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Supports proactive support, serviceability, and product improvement initiatives.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>['R&amp;D Telemetry', 'Service', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Firmware and cloud integration; privacy compliance.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Telemetry data is securely collected, transmitted, and accessible for authorized support and analytics.</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Implement telemetry features to monitor device health, usage, and proactively identify issues for Magellan printers.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Enables predictive maintenance, supports quality assurance, and improves customer support.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, DVAR, BA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Telemetry software and hardware integration.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Telemetry data is reliably collected and accessible for 99% of shipped devices.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
         <v>0.9</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>14</t>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,17 +493,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Ink Bottles with Higher Yield</t>
+          <t>NGB Keyed Bottles with Enhanced Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new generation bottle (NGB) keyed ink bottles with 6,000-page yield for black and CMY, and bottle size for CMY to exceed 8,000 pages.</t>
+          <t>Develop and integrate NGB keyed ink bottles supporting 6K Black and 6K CMY page yield. CMY bottles must have a size supporting &gt;8K pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To increase ink yield and reduce frequency of bottle replacement, improving customer satisfaction and competitive positioning against CISS competitors.</t>
+          <t>Addresses market demand for higher yield consumables and competitive positioning against CISS systems.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -513,17 +513,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Product Management, End Customers</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires compatibility with new or existing ink tanks and IDS system.</t>
+          <t>Bottle design, Tank size optimization, IDS integration</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NGB bottles are available for black and CMY, yield at least 6,000 pages for black, 6,000 for CMY, and CMY bottle size supports &gt;8,000-page yield. Verified by yield testing.</t>
+          <t>Bottles must be keyed, Black yield &gt;= 6000 pages, CMY yield &gt;= 6000 pages, CMY bottle size supports &gt;8000 pages, validated via yield testing.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -544,17 +544,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>Spill-Free Bottle Reliability</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure new ink bottles and filling process are spill-free during installation and use.</t>
+          <t>Ensure the new ink bottle system provides spill-free operation during all customer interactions and refills.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Spill-free operation is a critical user experience feature, reducing mess and increasing trust in HP’s CISS system.</t>
+          <t>Minimizes mess and customer complaints, critical for CISS market acceptance.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -564,21 +564,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Customer Support</t>
+          <t>End Customers, R&amp;D, Service</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle design, IDS, and tank interface.</t>
+          <t>Bottle design, IDS, NOA-F</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No ink spills during standard bottle installation and use, confirmed via usability and reliability testing.</t>
+          <t>During user testing, no ink spills observed in 100 consecutive refill operations.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -600,12 +600,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Implement NOA-F (non-original ink avoidance filter) with a metal foiled labyrinth and a lid label, maintaining current click-on push-push and TDF mechanisms.</t>
+          <t>Integrate a new NOA-F (Non-OEM Authentication Filter) featuring a metal foiled labyrinth and lid label, with no change to click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enhances ink security, prevents non-original ink usage, and maintains compatibility with existing mechanisms.</t>
+          <t>Enhances anti-counterfeit and authentication measures while maintaining current user experience.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -615,17 +615,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Supplies, Quality Assurance</t>
+          <t>R&amp;D, Security, Product Management</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOA-F design, bottle interface, TDF mechanism.</t>
+          <t>NOA-F part design, integration with bottle and printer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F with metal foiled labyrinth and lid label passes ink authentication and leak testing, and works with push-push and TDF.</t>
+          <t>NOA-F passes security validation, metal foil and lid label present, click-on push-push and TDF unchanged.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -646,17 +646,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Support for Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Design printer to allow customers to replace the Printhead Assembly (PHA) and NOA-F without service center intervention.</t>
+          <t>Enable customer replaceability for PHA (Printhead Assembly) and NOA-F components.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Improves serviceability, reduces downtime and service costs, and aligns with customer expectations for ease of maintenance.</t>
+          <t>Improves serviceability, reduces support costs, and meets market expectation for user-maintainable printers.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>End Customers, Service, R&amp;D</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>PHA and NOA-F mechanical design, user documentation.</t>
+          <t>Mechanical design, documentation, training</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>End users can successfully replace PHA and NOA-F following provided instructions, confirmed by usability tests.</t>
+          <t>Customers can successfully replace PHA and NOA-F in field tests without technical intervention.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -697,17 +697,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New Warranty Page Life Goal of 80,000 Pages</t>
+          <t>Warranty Page Life Goal of 80,000 Pages</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Set and support a new warranty page life goal of 80,000 pages for the printer.</t>
+          <t>The printer must support a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Extends product life, reduces replacement frequency, and increases perceived value for high-volume users.</t>
+          <t>Aligns with competitive market offerings and reduces total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,21 +717,21 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>Product Management, End Customers, Service</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Component durability, consumables life, warranty policy.</t>
+          <t>Component durability, maintenance schedule, consumables yield</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Printer operates reliably for 80,000 pages under standard usage conditions; verified via accelerated life testing.</t>
+          <t>Device warranty supports 80,000 pages as measured by internal page count and verified through accelerated life testing.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -748,17 +748,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, Blue Angel Compliance for PDL SKU</t>
+          <t>Speed: 25/20ppm (PDL: 25/19ppm)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ensure the PDL SKU meets EPEAT3, LOT4, and Blue Angel environmental and efficiency certifications.</t>
+          <t>Printer must achieve print speeds of 25 pages per minute (ppm) and 20 ppm, with PDL (Page Description Language) speeds at 25/19 ppm.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Necessary for regulatory compliance and to meet sustainability goals, especially for institutional and enterprise customers.</t>
+          <t>Meets market standards for throughput and competitive positioning.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -768,21 +768,21 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Compliance, Product Management, Enterprise Customers</t>
+          <t>R&amp;D, Product Management, Customers</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Design, materials, and energy consumption features.</t>
+          <t>Engine design, firmware optimization</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PDL SKU is certified for EPEAT3, LOT4, and Blue Angel; certification documents available.</t>
+          <t>Printer achieves specified speeds in ISO standard print tests.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -799,17 +799,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes to Align with Tank Protrusion</t>
+          <t>4.3” CGD Touch Panel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Modify input and output trays to accommodate changes in printer dimensions due to tank protrusion and size optimization.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphics Display) touch panel for user interface.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ensures reliable paper handling and maintains compact form factor despite larger tanks.</t>
+          <t>Improves user interaction and aligns with contemporary printer UI expectations.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -819,21 +819,21 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, End Users</t>
+          <t>End Customers, UX/UI, Product Management</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tank design, paper path engineering.</t>
+          <t>UI software, panel hardware integration</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Trays function properly and fit with new tank design; confirmed by fit and functional tests.</t>
+          <t>4.3” CGD is responsive, displays all required functions, and passes usability testing.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -850,17 +850,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.3-inch CGD Display</t>
+          <t>Service Station Aerosol Management for Tank Platform</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch color graphic display (CGD) for improved user interface and control.</t>
+          <t>Implement aerosol management in the service station to accommodate changes due to the ink tank platform.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Enhances user experience by providing clear, accessible information and controls.</t>
+          <t>Prevents contamination and maintains print quality and reliability.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -870,17 +870,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>End Users, UI/UX, Product Management</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Electrical design, firmware, UI development.</t>
+          <t>Service station design, tank integration</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.3-inch CGD is functional, meets brightness and resolution specs, and passes user acceptance tests.</t>
+          <t>Aerosol levels remain within HP safety and quality limits during extended operation.</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -901,41 +901,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management for New Tank</t>
+          <t>Paper Path for Increased Page Life</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Redesign service station aerosol management system to accommodate changes from new tank integration.</t>
+          <t>Redesign the paper path to support increased page life requirements, in line with new warranty goals.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Prevents ink aerosol contamination due to new tank design, maintaining print quality and reliability.</t>
+          <t>Ensures hardware durability and consistent print quality over extended use.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Service, End Customers</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Service station and tank design.</t>
+          <t>Mechanical design, material selection</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Aerosol containment meets HP standards; verified by environmental and reliability tests.</t>
+          <t>Paper path components pass durability tests for 80,000 pages without failure.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -952,37 +952,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>Ink Maintenance as Serviceable Part Post 80k Life</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Update paper path design to support increased page life and reliability for high duty cycle usage.</t>
+          <t>Design ink maintenance components to be serviceable at service centers after 80,000 page life is reached.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Required to ensure reliable operation up to the 80,000-page warranty goal.</t>
+          <t>Extends product lifespan, reduces e-waste, and supports post-warranty service models.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>Service, End Customers, Product Management</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Paper path engineering, component durability.</t>
+          <t>Component modularity, service documentation</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paper jams and misfeeds remain within HP’s acceptable limits over 80,000 pages; verified by life testing.</t>
+          <t>Service centers can replace ink maintenance parts in under 30 minutes with standard tools.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1003,41 +1003,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ink Maintenance as a Serviceable Part Post-80K Life</t>
+          <t>IDS with New Make-break and FI Connection</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Design ink maintenance components to be serviceable by service centers after 80,000 pages.</t>
+          <t>Implement new make-break and fluidic interface (FI) connection in the IDS (Ink Delivery System), leveraging LEBI ink-tank with increased size, keying, and LOI (Level of Ink) One SHAID.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Supports extended printer life and cost-effective post-warranty service.</t>
+          <t>Improves reliability, prevents cross-contamination, and supports larger tanks.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Component modularity, service documentation.</t>
+          <t>IDS design, tank design</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance parts post-80,000 pages; confirmed by service procedure validation.</t>
+          <t>IDS passes reliability and compatibility tests, supports new tank and bottle sizes.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1054,37 +1054,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Implement new make-break and fluidic interconnect (FI) connections for the IDS (Ink Delivery System), leveraging LEBI ink-tank with increased size and keying.</t>
+          <t>Develop a new startup algorithm for the IDS that includes improved air management.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Supports higher ink volumes, improved reliability, and security against non-genuine supplies.</t>
+          <t>Ensures consistent print quality and reduces startup failures.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>R&amp;D, Supplies, Quality Assurance</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>IDS, bottle, and tank design.</t>
+          <t>Firmware, IDS hardware</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>IDS make-break and FI connections function as designed and meet reliability targets; verified by engineering tests.</t>
+          <t>Startup success rate &gt;99% and air bubble incidents &lt;0.1% during validation.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1105,17 +1105,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>New Print Quality Goals and Depletion Metrics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Develop a new IDS startup algorithm and air management system to ensure reliable ink flow and startup performance.</t>
+          <t>Set new print quality (PQ) goals and depletion metrics to align with updated page yield definitions.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Critical for print quality, reliability, and customer satisfaction, especially with new tank and bottle sizes.</t>
+          <t>Ensures competitive print quality and accurate consumable life predictions.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1125,21 +1125,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware, Quality Assurance</t>
+          <t>R&amp;D, Product Management, End Customers</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Firmware, IDS hardware.</t>
+          <t>Firmware, consumables, IDS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Printer starts up reliably under all operating conditions; confirmed by startup and reliability testing.</t>
+          <t>Print quality meets or exceeds HP PQ standards; depletion metrics align with 6K/8K yield claims.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New Print Quality (PQ) Goals and Depletion Metrics</t>
+          <t>Compliance with EPEAT3, LOT4, and Blue Angel (PDL SKU)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Establish new print quality goals and depletion metrics to align with increased yield and page life.</t>
+          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel certifications for environmental and energy requirements, specifically for PDL SKU.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ensures print quality is maintained throughout the extended product lifecycle and higher yields.</t>
+          <t>Required for market access and sustainability commitments.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1176,21 +1176,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, End Users</t>
+          <t>Regulatory, Product Management, Sustainability</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ink formulation, IDS, firmware.</t>
+          <t>Design, materials, documentation</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Print quality remains within HP standards for the defined page yield; validated by print quality and depletion tests.</t>
+          <t>Product certified for EPEAT3, LOT4, and Blue Angel prior to launch.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1207,41 +1207,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Support for Consumer, SMB, and Enterprise Business Models</t>
+          <t>Input/Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Product and solution must support Consumer, SMB, and Enterprise business models, including PaaS, WorkFromHome, and Flexworker services.</t>
+          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall device size.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Expands addressable market and aligns with HP’s strategic intent to protect and grow share across segments.</t>
+          <t>Ensures paper handling reliability and compact footprint.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Business, Product Management, Sales</t>
+          <t>R&amp;D, Mechanical Design, End Customers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Firmware, software, solutions integration.</t>
+          <t>Tank design, mechanical integration</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Product is configurable for all business models and passes acceptance tests for each segment.</t>
+          <t>Trays operate reliably with tank protrusion; device size meets optimization targets.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1258,37 +1258,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Integration with HPX, PSA, SUPD, UPD, EasyStart, USS, UFD Drivers</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ensure compatibility and integration with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD drivers and client software.</t>
+          <t>Use EPS foam packaging for product shipment.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Critical for seamless deployment, management, and user experience across customer environments.</t>
+          <t>Provides adequate protection during shipping and supports cost-effective packaging.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>End Users, IT, Product Management</t>
+          <t>Manufacturing, Logistics</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Firmware, software development.</t>
+          <t>Packaging design</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>All listed drivers and client software are supported and pass integration tests.</t>
+          <t>Product passes drop and vibration tests with EPS foam packaging.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1309,41 +1309,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Compliance with HP Security Standards (Gauss4.xx)</t>
+          <t>Support for SMB and Enterprise Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Implement hardware and firmware security features in line with Gauss4.xx standard.</t>
+          <t>Integrate SMB manageability and enterprise support features including WJA, HPSM, and JAM solutions.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Protects HP’s intellectual property, customer data, and device security.</t>
+          <t>Meets business customer requirements and enables fleet management.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Security, IT, Enterprise Customers</t>
+          <t>SMB Customers, Enterprise IT, Product Management</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Firmware, hardware design.</t>
+          <t>Firmware, solution integration</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Security features pass HP security audits and meet Gauss4.xx requirements.</t>
+          <t>Device is compatible with WJA, HPSM, JAM and passes solution interoperability tests.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1360,45 +1360,45 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65,000 Pages</t>
+          <t>Support for PaaS and WorkFromHome/Flexworker Services</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ensure SuperAmp Printhead Assembly (PHA) achieves a minimum life of 65,000 pages.</t>
+          <t>Enable Platform-as-a-Service (PaaS) and support for WorkFromHome/Flexworker business models.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Critical for reducing maintenance frequency and supporting high-volume printing.</t>
+          <t>Expands addressable market and supports new business models.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>Product Management, Sales, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Printhead design, ink compatibility.</t>
+          <t>Service platform integration</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SuperAmp PHA meets or exceeds 65,000-page life in reliability testing.</t>
+          <t>PaaS and WorkFromHome/Flexworker services are available and functional at launch.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1411,37 +1411,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years or Specified Pages</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Support a warranty life of 2 years or the specified page count, whichever comes first.</t>
+          <t>Integrate Acumen 6 technology on the printer lid.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Aligns with market expectations and supports HP’s competitive positioning.</t>
+          <t>Supports advanced authentication and/or analytics features.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Service, Product Management, End Users</t>
+          <t>Security, Product Management</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Component reliability, warranty policy.</t>
+          <t>Lid design, electronics integration</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Warranty is honored for 2 years or the specified page count; policy is documented and communicated.</t>
+          <t>Acumen 6 functionality verified in system integration tests.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 ppm (PDL: 25/19 ppm)</t>
+          <t>Reuse of Marconi Hi PDL and Associated Electronics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Achieve print speeds of 25/20 pages per minute (ppm), with PDL variants at 25/19 ppm.</t>
+          <t>Leverage the Marconi Hi PDL platform and associated electronics (Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi module, Dune FW, Gauss4.xx security).</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Meets performance requirements for target segments and maintains competitiveness.</t>
+          <t>Reduces development cost and risk; accelerates time-to-market.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1482,21 +1482,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Engine design, firmware.</t>
+          <t>Component compatibility, firmware integration</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Printer achieves specified throughput in standard benchmark tests.</t>
+          <t>All electronics reused from Marconi Hi PDL operate as expected in Magellan platform.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1513,17 +1513,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Serviceability of Maintenance Box</t>
+          <t>Support for Customer Onboarding Paths</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Design maintenance box to be easily serviceable for end users or service centers.</t>
+          <t>Enable onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs, improving customer satisfaction.</t>
+          <t>Facilitates a seamless onboarding experience for all customer segments.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1533,25 +1533,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>Product Management, Sales, End Customers</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Maintenance box design, documentation.</t>
+          <t>Onboarding software, documentation</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by end users or service centers; confirmed by usability testing.</t>
+          <t>Customers can onboard via all specified paths without errors.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1564,17 +1564,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SMB Solution and Manageability Features</t>
+          <t>Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD Clients &amp; Drivers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Provide solution features and manageability for SMBs, including scan solutions and SMB portal integration.</t>
+          <t>Ensure compatibility and support for HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Addresses SMB segment needs for manageability and workflow integration.</t>
+          <t>Maximizes interoperability and ease of use for customers.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1584,21 +1584,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SMB Customers, Product Management, IT</t>
+          <t>End Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Firmware, software, solutions integration.</t>
+          <t>Firmware, driver validation</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SMB manageability features are functional and pass acceptance tests with SMB customers.</t>
+          <t>All listed clients and drivers function correctly with the device.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1608,71 +1608,71 @@
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK Trade Page (Flexible)</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Design flexibility to host 12,000-page CMYK trade page as a future option.</t>
+          <t>Integrate advanced AI-powered productivity features, including scan workflow automation and manageability solutions, to simplify business operations for SMB customers.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Allows future scalability and support for higher-yield options as market demands evolve.</t>
+          <t>Target customers lack dedicated IT staff and require easy-to-use, automated productivity tools to maximize efficiency and ROI.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management</t>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Tech Reg, Prod Steward, BA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tank and bottle design, IDS scalability.</t>
+          <t>Requires integration with SMB portal and device firmware.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Platform design allows for future 12K-CMYK option without major redesign.</t>
+          <t>AI-powered scan workflow and manageability features are available, functional, and accessible via the SMB portal; user testing confirms ease of use and productivity improvement.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity features, scan workflow automation, and manageability solutions into the Magellan printer to simplify business operations for SMBs.</t>
+          <t>Design the Magellan printer to deliver HP’s lowest business TCO for SMBs, including minimal intervention and efficient consumable usage.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Target SMBs demand efficiency and minimal IT intervention. AI features and manageability are key differentiators for Magellan.</t>
+          <t>SMBs are highly cost-sensitive and require solutions that minimize ongoing costs and maintenance.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1682,30 +1682,30 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Marketing, GXD, Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Tech Reg, Prod Steward, BA</t>
+          <t>Marketing, GXD, BA, Quality</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Requires AI software integration and compatible hardware.</t>
+          <t>Keyed bottles, sustainability requirements, efficient ink tank design.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Magellan printer delivers AI-powered scan and print workflows; centralized management portal is functional and accessible for SMB users.</t>
+          <t>TCO calculations demonstrate lowest cost compared to prior HP business models and key competitors in SMB segment; validated by independent testing or cost analysis.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1713,17 +1713,17 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lowest Business TCO (Total Cost of Ownership)</t>
+          <t>Sustainable SMB Tank Printer (60% RCP)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Design Magellan to deliver HP’s lowest business TCO through optimized ink usage, minimal maintenance, and efficient consumables.</t>
+          <t>Develop the printer with a sustainability target of at least 60% recycled content plastic (RCP), exceeding competitors like Epson (30%).</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SMBs are highly cost-sensitive and seek maximum ROI; low TCO is a major purchase driver.</t>
+          <t>Sustainability is a key differentiator for HP and valued by SMB customers; regulatory and corporate responsibility drivers.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1733,21 +1733,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Marketing, BA, Supplies Quality</t>
+          <t>Prod Steward, Marketing, Quality, Tech Reg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Requires efficient ink tank system and durable components.</t>
+          <t>Material sourcing and supply chain capabilities.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Independent testing confirms Magellan has the lowest TCO in its class compared to competitors.</t>
+          <t>Material composition reports verify 60%+ RCP in product plastics; sustainability claims validated by third-party certification.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1764,17 +1764,17 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Customer-Replaceable Maintenance Box</t>
+          <t>Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Enable the maintenance box to be easily replaceable by customers without technical support.</t>
+          <t>Introduce a replaceable maintenance box that can be serviced by the customer, reducing downtime and service costs.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Target SMBs lack dedicated IT support; easy maintenance reduces downtime and support costs.</t>
+          <t>Target SMBs lack IT support; customer-replaceable parts minimize disruption and maintenance expense.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1784,21 +1784,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Quality, R&amp;D Telemetry, DVAR, Tech Reg, Prod Steward</t>
+          <t>Quality, R&amp;D Telemetry, Supplies Quality, Service</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Design for tool-less replacement and clear instructions.</t>
+          <t>Serviceability design, warranty policy, PHA/MINK criteria.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>User can replace maintenance box within 5 minutes using included instructions, with no tools required.</t>
+          <t>Maintenance box can be replaced by end-users with clear instructions; field tests confirm &lt;15 min replacement time and &lt;5% service calls for related issues.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1815,17 +1815,17 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Serviceability: PHA and MINK at Service Centre</t>
+          <t>Keyed Bottles for Consumables</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Implement serviceability protocols: PHA (customer replaceable) and MINK (service center replaceable) for key components, prioritizing customer replaceable where possible.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and reduce user errors.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Reduces service costs and downtime for SMBs, aligning with limited IT resources.</t>
+          <t>Ensures correct consumable usage, reduces support calls, and improves user experience for non-technical SMB users.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Quality, DVAR, Tech Reg, Prod Steward</t>
+          <t>Supplies Quality, Quality, Service</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Component design and documentation.</t>
+          <t>Ink system design, supply chain for keyed bottles.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>At least 80% of serviceable parts are customer-replaceable; others are service center replaceable.</t>
+          <t>All consumable bottles are uniquely keyed; user testing shows &lt;2% error rate in refilling.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1866,50 +1866,50 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Refilling</t>
+          <t>Consolidated SMB Portal for Device Management</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Design ink bottles with unique keying to prevent misfilling and ensure proper use with Magellan printers.</t>
+          <t>Provide a unified portal for SMBs to manage all printers, monitor usage, access AI solutions, and receive support.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Prevents user error, reduces support calls, and protects printer integrity.</t>
+          <t>Unmanaged/lightly managed SMBs require simple, centralized tools for device management due to lack of IT staff.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Supplies Quality, Quality, BA</t>
+          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bottle and tank design.</t>
+          <t>Integration with AI solutions, device firmware, and support systems.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Only correct bottle fits the corresponding tank; user testing shows zero misfills in 100 attempts.</t>
+          <t>Portal is accessible, supports multi-device management, integrates AI features, and receives positive feedback in SMB user testing.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1917,17 +1917,17 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
+          <t>Perfect Print and Perfect Scan AI Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Offer a non-PDL SKU that supports SMB2.0 solutions and integrates with the Advanced View SMB portal for device management.</t>
+          <t>Develop and integrate 'Perfect Print' and 'Perfect Scan' features leveraging AI to optimize output quality and workflow efficiency.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Addresses needs of unmanaged/lightly managed SMBs for centralized management without complex IT.</t>
+          <t>Differentiates HP from competitors and addresses SMB need for high-quality, efficient document handling with minimal intervention.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1937,30 +1937,30 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GXD, Marketing, R&amp;D Telemetry</t>
+          <t>GXD, R&amp;D Telemetry, Marketing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Portal software availability and integration.</t>
+          <t>AI software development, hardware compatibility, SMB portal integration.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Non-PDL SKU ships with SMB2.0 and portal access enabled; portal manages all connected devices.</t>
+          <t>AI-driven print/scan features function as specified; quality benchmarks met or exceeded; user testing confirms improved workflow efficiency.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan MRD, Page 7, 11</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1968,41 +1968,41 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PDL SKU: Higher Print Speeds and PDL/PS Support</t>
+          <t>Warranty: 80k Pages or 2 Years</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Provide a PDL SKU with improved print speeds (target 25/20 ppm) and support for PDL/PS (Page Description Language/PostScript).</t>
+          <t>Offer a warranty covering either 80,000 printed pages or 2 years, whichever comes first.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Meets business needs for faster printing and compatibility with advanced workflows.</t>
+          <t>SMBs require predictable, reliable coverage for budgeting and risk mitigation.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+          <t>Quality, Marketing, Service</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hardware capability and firmware support.</t>
+          <t>Service and support planning, warranty terms documentation.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>PDL SKU achieves 25/20 ppm; passes compatibility tests with PDL/PS workflows.</t>
+          <t>Warranty terms included in product documentation; service systems configured to track usage and time; customers receive warranty support as specified.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2019,17 +2019,17 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Blue Angel Certification for PDL SKU</t>
+          <t>PHA and MINK Serviceability Thresholds</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ensure the PDL SKU meets Blue Angel environmental certification requirements.</t>
+          <t>Design the product for 'Planned Hardware Architecture' (PHA) customer replaceable parts and 'Minimum Intervention Needed by Knowledgeable' (MINK) at service centers for out-of-warranty repairs, targeting maximum customer replaceability.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Environmental compliance is increasingly required in tenders and valued by SMBs.</t>
+          <t>Reduces downtime, improves user experience, and lowers service costs for SMBs without IT staff.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2039,21 +2039,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Prod Steward, Tech Reg, Quality</t>
+          <t>Quality, Service, R&amp;D Telemetry</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Design and materials selection.</t>
+          <t>Hardware design, service documentation, training materials.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>PDL SKU receives Blue Angel certification prior to launch.</t>
+          <t>Service documentation specifies PHA and MINK parts; &gt;80% of common repairs are customer-replaceable; field data shows reduced service center visits.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2070,17 +2070,17 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>First OJ Pro with Ink Tanks</t>
+          <t>PDL and Non-PDL SKU Differentiation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Magellan to be the first HP OfficeJet Pro product with ink tank technology, targeting CISS PLE Hi segment.</t>
+          <t>Release both PDL (Page Description Language) and Non-PDL SKUs, with PDL supporting higher print speeds (target 25/20 ppm), PDL/PS support, and Blue Angel certification; Non-PDL supports SMB 2.0 Solutions and Advanced View SMB portal, and PaaS.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fills a gap in HP’s portfolio and addresses market shift toward CISS in SMB segment.</t>
+          <t>Addresses varied SMB needs and regulatory requirements, enables market segmentation and compliance.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2090,30 +2090,30 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Marketing, GXD, BA, R&amp;D Telemetry</t>
+          <t>Marketing, Tech Reg, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>New product development and positioning.</t>
+          <t>Firmware/software development, certification processes, SKU management.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Product is launched as HP’s first OJ Pro with ink tanks; marketing materials reflect this.</t>
+          <t>Both SKUs available with specified features; print speed and certification targets met; portal and PaaS support functional.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 6</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2121,50 +2121,50 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
+          <t>Mobile Printing via HP App</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Incorporate AI-powered features for optimal print and scan quality, including error correction and workflow automation.</t>
+          <t>Enable seamless mobile printing capabilities through the HP App for SMB users.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AI features differentiate Magellan and address SMB needs for efficiency and quality.</t>
+          <t>Supports modern workstyles and increases convenience for SMBs with mobile-centric workflows.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GXD, Marketing, R&amp;D Telemetry, BA</t>
+          <t>GXD, Marketing, BA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>AI algorithm development and integration.</t>
+          <t>App development, printer firmware compatibility.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>AI-driven print/scan features demonstrably improve quality and reduce errors in independent tests.</t>
+          <t>Mobile printing works reliably with HP App; user testing confirms &lt;2 min setup and successful print from mobile devices.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -2172,50 +2172,50 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Consolidated SMB Portal for Device Management</t>
+          <t>Support for PaaS (Platform as a Service)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Develop a consolidated portal for SMBs to manage all Magellan printers and related devices from a single interface.</t>
+          <t>Ensure the printer and associated software support PaaS business models, enabling solutions monetization and service delivery.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Simplifies device management for businesses without dedicated IT.</t>
+          <t>Aligns with HP’s strategic intent to accelerate PaaS and opens new revenue streams.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>GXD, Marketing, R&amp;D Telemetry, BA</t>
+          <t>Marketing, BA, Tech Reg, GXD</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Portal software development and cloud infrastructure.</t>
+          <t>Software platform integration, licensing, and billing systems.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Portal enables registration, monitoring, and management of all connected devices; user satisfaction &gt;90% in pilot.</t>
+          <t>Printer integrates with PaaS platform; SMBs can subscribe to and utilize services via portal.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -2223,17 +2223,17 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Maintenance-Free or Less Maintenance Design</t>
+          <t>Blue Angel Certification for PDL SKU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Engineer Magellan for maintenance-free or minimal maintenance operation, with fewer parts requiring replacement over product life.</t>
+          <t>Achieve Blue Angel environmental certification for PDL SKU to meet regulatory and customer sustainability expectations.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Reduces operational burden and cost for SMBs with little IT support.</t>
+          <t>Satisfies regulatory and market requirements in key regions; supports HP’s sustainability positioning.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2243,30 +2243,30 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Quality, Prod Steward, Tech Reg, DVAR</t>
+          <t>Tech Reg, Prod Steward, Marketing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Component reliability and design innovation.</t>
+          <t>Product design, certification testing, documentation.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Over 80% of units require no major maintenance during 2-year warranty period.</t>
+          <t>PDL SKU passes Blue Angel certification and is listed in relevant registries.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -2274,203 +2274,50 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sustainability: 60% Recycled Content Plastic (RCP)</t>
+          <t>Telemetry Requirements</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Magellan to be manufactured using at least 60% recycled content plastic, exceeding competitors’ sustainability benchmarks.</t>
+          <t>Implement telemetry capabilities for remote monitoring, diagnostics, and usage tracking to support SMB manageability and service.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Addresses growing customer and regulatory demand for sustainable products.</t>
+          <t>Enables proactive support, reduces downtime, and provides data for continuous improvement.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Prod Steward, Tech Reg, Marketing, Quality</t>
+          <t>R&amp;D Telemetry, Service, GXD, Quality</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Supply chain readiness and material sourcing.</t>
+          <t>Firmware, portal integration, data privacy compliance.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Bill of materials and certification confirm 60% RCP in all relevant parts.</t>
+          <t>Telemetry data is securely collected, accessible to support teams, and actionable insights are generated; privacy compliance validated.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Mobile Printing via HP App</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Enable seamless mobile printing capabilities through the HP App for Magellan users.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Supports modern SMB workflows and BYOD environments.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>GXD, Marketing, R&amp;D Telemetry, BA</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>App integration and printer firmware support.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Users can print from mobile devices via HP App with &gt;95% success rate in testing.</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
           <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>PaaS (Platform as a Service) Support</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Magellan must support HP’s PaaS offerings, enabling integration with cloud-based solutions and services.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Aligns with HP’s strategic goals for PaaS acceleration and recurring revenue.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>PaaS platform readiness and printer compatibility.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Magellan is certified for PaaS integration and supports all required APIs.</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Telemetry Requirements</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Implement telemetry features to monitor device health, usage, and proactively identify issues for Magellan printers.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Enables predictive maintenance, supports quality assurance, and improves customer support.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>R&amp;D Telemetry, Quality, DVAR, BA</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Telemetry software and hardware integration.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Telemetry data is reliably collected and accessible for 99% of shipped devices.</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 3, 12</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Requirement ID</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -477,11 +477,6 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>citation</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -493,17 +488,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with Enhanced Page Yield</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop and integrate NGB keyed ink bottles supporting 6K Black and 6K CMY page yield. CMY bottles must have a size supporting &gt;8K pages.</t>
+          <t>The printer must support new NGB keyed bottles, with 6K Black and 6K CMY page yield, and CMY bottle size greater than 8K.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Addresses market demand for higher yield consumables and competitive positioning against CISS systems.</t>
+          <t>To increase ink capacity and reduce user intervention, supporting higher yield and competitive differentiation.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -513,17 +508,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Customers</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bottle design, Tank size optimization, IDS integration</t>
+          <t>Requires compatibility with NOA-F, IDS, and bottle keying system.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bottles must be keyed, Black yield &gt;= 6000 pages, CMY yield &gt;= 6000 pages, CMY bottle size supports &gt;8000 pages, validated via yield testing.</t>
+          <t>Printer accepts and recognizes new NGB keyed bottles; achieves 6K Black and 6K CMY page yield; supports CMY bottle size &gt;8K.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -534,7 +529,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,17 +538,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Bottle Reliability</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure the new ink bottle system provides spill-free operation during all customer interactions and refills.</t>
+          <t>The system must ensure spill-free reliability when users replace ink bottles.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Minimizes mess and customer complaints, critical for CISS market acceptance.</t>
+          <t>To enhance user experience and minimize mess or damage during bottle changes.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -564,17 +558,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Customers, R&amp;D, Service</t>
+          <t>End Users, Service, R&amp;D</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle design, IDS, NOA-F</t>
+          <t>NGB keyed bottle design, IDS system.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>During user testing, no ink spills observed in 100 consecutive refill operations.</t>
+          <t>No ink spill occurs in &gt;99.5% of bottle replacement events during testing.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -585,7 +579,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -600,12 +593,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Integrate a new NOA-F (Non-OEM Authentication Filter) featuring a metal foiled labyrinth and lid label, with no change to click-on push-push and TDF mechanisms.</t>
+          <t>The NOA-F (Next-Gen Output Assembly - F) must include a metal foiled labyrinth and lid label, with no change to click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enhances anti-counterfeit and authentication measures while maintaining current user experience.</t>
+          <t>Improved reliability and security for ink delivery and assembly.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -615,28 +608,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Product Management</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOA-F part design, integration with bottle and printer</t>
+          <t>NOA-F design, compatibility with existing assembly mechanisms.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F passes security validation, metal foil and lid label present, click-on push-push and TDF unchanged.</t>
+          <t>NOA-F includes specified features and passes reliability and assembly tests without modification to push-push and TDF.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -646,17 +638,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Support for Customer Replaceable PHA and NOA-F</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Enable customer replaceability for PHA (Printhead Assembly) and NOA-F components.</t>
+          <t>The printer must reuse the SuperAmp Si Printhead Assembly (PHA) and Magi/Nessie pigment inks without reformulation.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Improves serviceability, reduces support costs, and meets market expectation for user-maintainable printers.</t>
+          <t>To leverage proven components, reduce development cost, and ensure supply chain efficiency.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -666,28 +658,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>End Customers, Service, R&amp;D</t>
+          <t>R&amp;D, Supply Chain, Product Management</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mechanical design, documentation, training</t>
+          <t>Compatibility with new bottle and ink system.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Customers can successfully replace PHA and NOA-F in field tests without technical intervention.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie inks function without reformulation in the new printer system.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -697,17 +688,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80,000 Pages</t>
+          <t>Reliability and IDS Characterization &amp; Modelling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The printer must support a new warranty page life goal of 80,000 pages.</t>
+          <t>Reliability, Water Vapor Transmission Rate (WVTR), air gain, flow rate, and IDS (Ink Delivery System) must be characterized and modeled, including startup and NOA-F end-of-life.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aligns with competitive market offerings and reduces total cost of ownership for customers.</t>
+          <t>Ensures robust performance and predictive maintenance capability.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,28 +708,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Product Management, End Customers, Service</t>
+          <t>R&amp;D, Quality, Service</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Component durability, maintenance schedule, consumables yield</t>
+          <t>IDS, NOA-F, ink system.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Device warranty supports 80,000 pages as measured by internal page count and verified through accelerated life testing.</t>
+          <t>Characterization and models completed; meet reliability targets over product lifecycle.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -748,48 +738,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Speed: 25/20ppm (PDL: 25/19ppm)</t>
+          <t>Ink Stability Modelling (Tank &amp; PQ Impact)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Printer must achieve print speeds of 25 pages per minute (ppm) and 20 ppm, with PDL (Page Description Language) speeds at 25/19 ppm.</t>
+          <t>Ink stability in the tank must be modeled and assessed for impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Meets market standards for throughput and competitive positioning.</t>
+          <t>To prevent print quality degradation over time due to ink instability.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Customers</t>
+          <t>R&amp;D, Quality</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Engine design, firmware optimization</t>
+          <t>Ink system, IDS, tank design.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Printer achieves specified speeds in ISO standard print tests.</t>
+          <t>Stability model completed; PQ is within spec after prolonged tank storage.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -799,48 +788,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.3” CGD Touch Panel</t>
+          <t>NOA-F as Service Part in Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphics Display) touch panel for user interface.</t>
+          <t>NOA-F must be available as a service part for warranty support.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Improves user interaction and aligns with contemporary printer UI expectations.</t>
+          <t>Improves serviceability and reduces downtime for customers.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>End Customers, UX/UI, Product Management</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UI software, panel hardware integration</t>
+          <t>NOA-F part logistics and support systems.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.3” CGD is responsive, displays all required functions, and passes usability testing.</t>
+          <t>NOA-F can be ordered and replaced under warranty service procedures.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -850,17 +838,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management for Tank Platform</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Implement aerosol management in the service station to accommodate changes due to the ink tank platform.</t>
+          <t>The printer lid must integrate Acumen 6 (presumably a sensor or feature).</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Prevents contamination and maintains print quality and reliability.</t>
+          <t>To enable advanced features or compliance as required by Acumen 6.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -870,28 +858,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Service station design, tank integration</t>
+          <t>Lid design, Acumen 6 compatibility.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Aerosol levels remain within HP safety and quality limits during extended operation.</t>
+          <t>Acumen 6 is integrated and passes functional validation.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -901,17 +888,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Paper Path for Increased Page Life</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Redesign the paper path to support increased page life requirements, in line with new warranty goals.</t>
+          <t>Modify existing SA14 line for NOA-F and add Magi ink cart and labelling tool in Orcus 5. Mold for 1 to 4 new keyed caps.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ensures hardware durability and consistent print quality over extended use.</t>
+          <t>To support new components in manufacturing.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -921,17 +908,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Customers</t>
+          <t>Manufacturing, R&amp;D</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mechanical design, material selection</t>
+          <t>SA14 line, Orcus 5, new cap molds.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paper path components pass durability tests for 80,000 pages without failure.</t>
+          <t>Factory lines modified and validated for new parts and processes.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -942,7 +929,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -952,48 +938,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part Post 80k Life</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design ink maintenance components to be serviceable at service centers after 80,000 page life is reached.</t>
+          <t>Design the printer for customer-replaceable Printhead Assembly (PHA) and NOA-F.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Extends product lifespan, reduces e-waste, and supports post-warranty service models.</t>
+          <t>Improves user convenience and reduces service costs.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Service, End Customers, Product Management</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Component modularity, service documentation</t>
+          <t>PHA, NOA-F design, user documentation.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance parts in under 30 minutes with standard tools.</t>
+          <t>End users can replace PHA and NOA-F without service intervention; validated by usability testing.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1003,17 +988,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IDS with New Make-break and FI Connection</t>
+          <t>Warranty Page Life Goal of 80K Pages</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Implement new make-break and fluidic interface (FI) connection in the IDS (Ink Delivery System), leveraging LEBI ink-tank with increased size, keying, and LOI (Level of Ink) One SHAID.</t>
+          <t>The printer must meet a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Improves reliability, prevents cross-contamination, and supports larger tanks.</t>
+          <t>Extends product life and reduces warranty claims.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1023,28 +1008,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management</t>
+          <t>Quality, Warranty, End Users</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>IDS design, tank design</t>
+          <t>Component durability, ink system, IDS.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>IDS passes reliability and compatibility tests, supports new tank and bottle sizes.</t>
+          <t>Printer passes accelerated life testing for 80,000 pages without failure.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1054,17 +1038,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Support PaaS (Print-as-a-Service) Model</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop a new startup algorithm for the IDS that includes improved air management.</t>
+          <t>Enable the printer to support Print-as-a-Service (PaaS) business model, including consumer, SMB, and enterprise onboarding paths.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ensures consistent print quality and reduces startup failures.</t>
+          <t>Expands business opportunities and adapts to modern service models.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1074,17 +1058,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>Business Model, Product Management, IT</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Firmware, IDS hardware</t>
+          <t>Software, onboarding solutions, service integration.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Startup success rate &gt;99% and air bubble incidents &lt;0.1% during validation.</t>
+          <t>Printer can be provisioned and managed under PaaS model for all target segments.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1095,7 +1079,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1105,17 +1088,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Metrics</t>
+          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and depletion metrics to align with updated page yield definitions.</t>
+          <t>Ensure the PDL SKU meets EPEAT3, LOT4, and Blue Angel environmental requirements.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ensures competitive print quality and accurate consumable life predictions.</t>
+          <t>Compliance with global eco-labels and regulatory requirements.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1125,28 +1108,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Customers</t>
+          <t>Regulatory, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Firmware, consumables, IDS</t>
+          <t>PDL SKU design, certification process.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Print quality meets or exceeds HP PQ standards; depletion metrics align with 6K/8K yield claims.</t>
+          <t>Product is certified for EPEAT3, LOT4, and Blue Angel prior to launch.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1156,48 +1138,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Compliance with EPEAT3, LOT4, and Blue Angel (PDL SKU)</t>
+          <t>Input/Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel certifications for environmental and energy requirements, specifically for PDL SKU.</t>
+          <t>Modify input and output trays to align with the increased tank protrusion and optimize overall size.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Required for market access and sustainability commitments.</t>
+          <t>Ensures product usability and maintains compact footprint despite larger tank.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Sustainability</t>
+          <t>R&amp;D, Industrial Design, End Users</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Design, materials, documentation</t>
+          <t>Tank design, tray design.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Product certified for EPEAT3, LOT4, and Blue Angel prior to launch.</t>
+          <t>Trays function correctly with tank protrusion; product size is minimized within constraints.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1207,17 +1188,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Input/Output Tray Changes for Tank Protrusion</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall device size.</t>
+          <t>Integrate a 4.3-inch color graphical display (CGD) into the printer.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ensures paper handling reliability and compact footprint.</t>
+          <t>Enhances user interface and accessibility.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1227,28 +1208,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Design, End Customers</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tank design, mechanical integration</t>
+          <t>Display sourcing, UI software.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Trays operate reliably with tank protrusion; device size meets optimization targets.</t>
+          <t>4.3” CGD is functional and passes usability tests.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1258,48 +1238,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Leverage Sayan Sibstar Tubes with New Routing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Use EPS foam packaging for product shipment.</t>
+          <t>Use Sayan Sibstar tubes for ink delivery with new tube routing and integration.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Provides adequate protection during shipping and supports cost-effective packaging.</t>
+          <t>Improves ink flow and system reliability.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Manufacturing, Logistics</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Packaging design</t>
+          <t>Tube sourcing, routing design.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Product passes drop and vibration tests with EPS foam packaging.</t>
+          <t>Sayan Sibstar tubes are integrated and pass reliability and performance tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1309,17 +1288,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Support for SMB and Enterprise Solutions</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Integrate SMB manageability and enterprise support features including WJA, HPSM, and JAM solutions.</t>
+          <t>Update service station for improved aerosol management due to new tank design.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Meets business customer requirements and enables fleet management.</t>
+          <t>Prevents aerosol-related issues and maintains print quality.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1329,17 +1308,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SMB Customers, Enterprise IT, Product Management</t>
+          <t>R&amp;D, Quality, Service</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Firmware, solution integration</t>
+          <t>Service station design, tank integration.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Device is compatible with WJA, HPSM, JAM and passes solution interoperability tests.</t>
+          <t>Aerosol levels are within safe limits during operation and maintenance.</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1350,7 +1329,6 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1360,17 +1338,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Support for PaaS and WorkFromHome/Flexworker Services</t>
+          <t>Carriage Dynamic and Force Model with New Weights</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Enable Platform-as-a-Service (PaaS) and support for WorkFromHome/Flexworker business models.</t>
+          <t>Model and validate carriage dynamics and force with new tube routing and weights.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Expands addressable market and supports new business models.</t>
+          <t>Ensures reliable printhead movement and print quality.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1380,28 +1358,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Product Management, Sales, SMB/Enterprise Customers</t>
+          <t>R&amp;D, Quality</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service platform integration</t>
+          <t>Carriage design, tube integration.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>PaaS and WorkFromHome/Flexworker services are available and functional at launch.</t>
+          <t>Carriage system operates within force and dynamic tolerances under new configuration.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1411,48 +1388,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Paper Path for Increased Page Life</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 technology on the printer lid.</t>
+          <t>Design paper path to support increased page life and durability.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Supports advanced authentication and/or analytics features.</t>
+          <t>Supports new 80K page life warranty goal.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Security, Product Management</t>
+          <t>R&amp;D, Quality, Service</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lid design, electronics integration</t>
+          <t>Paper path design, component durability.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Acumen 6 functionality verified in system integration tests.</t>
+          <t>Paper path passes endurance testing for 80,000 pages.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1462,48 +1438,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Reuse of Marconi Hi PDL and Associated Electronics</t>
+          <t>Ink Maintenance Serviceable Part Post-80K Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Leverage the Marconi Hi PDL platform and associated electronics (Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi module, Dune FW, Gauss4.xx security).</t>
+          <t>Designate ink maintenance as a serviceable part at service centers after 80K page life.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Reduces development cost and risk; accelerates time-to-market.</t>
+          <t>Facilitates extended printer use and serviceability.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Component compatibility, firmware integration</t>
+          <t>Ink maintenance design, service logistics.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>All electronics reused from Marconi Hi PDL operate as expected in Magellan platform.</t>
+          <t>Ink maintenance can be replaced at service centers post-80K pages.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1513,48 +1488,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Support for Customer Onboarding Paths</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Enable onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths.</t>
+          <t>Develop new make-break and fluidic interconnect (FI) connection for the ink delivery system.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Facilitates a seamless onboarding experience for all customer segments.</t>
+          <t>Ensures reliable and easy ink system assembly and maintenance.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Product Management, Sales, End Customers</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Onboarding software, documentation</t>
+          <t>IDS design, NOA-F, bottle system.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Customers can onboard via all specified paths without errors.</t>
+          <t>New connections pass reliability and user assembly tests.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1564,64 +1538,67 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD Clients &amp; Drivers</t>
+          <t>Leverage LEBI Ink-Tank with Increased Size, Keying, and LOI SHAID</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ensure compatibility and support for HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>Use LEBI ink-tank with increased size, keying, and LOI SHAID for enhanced security and compatibility.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Maximizes interoperability and ease of use for customers.</t>
+          <t>Improves ink system security and prevents incorrect installation.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>End Customers, IT, Product Management</t>
+          <t>R&amp;D, Quality, Service</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Firmware, driver validation</t>
+          <t>LEBI tank design, SHAID implementation.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>All listed clients and drivers function correctly with the device.</t>
+          <t>Tank passes size, keying, and LOI SHAID validation tests.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-powered productivity features, including scan workflow automation and manageability solutions, to simplify business operations for SMB customers.</t>
+          <t>Implement a new startup algorithm and air management for the ink delivery system.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Target customers lack dedicated IT staff and require easy-to-use, automated productivity tools to maximize efficiency and ROI.</t>
+          <t>Improves startup reliability and print quality.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1631,48 +1608,47 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Marketing, GXD, Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Tech Reg, Prod Steward, BA</t>
+          <t>R&amp;D, Quality</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Requires integration with SMB portal and device firmware.</t>
+          <t>IDS, NOA-F, ink system.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>AI-powered scan workflow and manageability features are available, functional, and accessible via the SMB portal; user testing confirms ease of use and productivity improvement.</t>
+          <t>Startup passes reliability and print quality benchmarks.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>New Print Quality Goals &amp; Depletion Definition</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Design the Magellan printer to deliver HP’s lowest business TCO for SMBs, including minimal intervention and efficient consumable usage.</t>
+          <t>Establish new print quality (PQ) goals and depletion definition to match page yield specifications.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SMBs are highly cost-sensitive and require solutions that minimize ongoing costs and maintenance.</t>
+          <t>Ensures output meets user expectations and competitive benchmarks.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1682,17 +1658,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Marketing, GXD, BA, Quality</t>
+          <t>Quality, Product Management, End Users</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Keyed bottles, sustainability requirements, efficient ink tank design.</t>
+          <t>IDS, ink system, firmware.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>TCO calculations demonstrate lowest cost compared to prior HP business models and key competitors in SMB segment; validated by independent testing or cost analysis.</t>
+          <t>PQ meets or exceeds targets at specified depletion points.</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1700,30 +1676,29 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sustainable SMB Tank Printer (60% RCP)</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Develop the printer with a sustainability target of at least 60% recycled content plastic (RCP), exceeding competitors like Epson (30%).</t>
+          <t>Reuse Marconi Tux digital ASIC, Hannibal analog ASIC, and Raccoon power supply unit in the new platform.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sustainability is a key differentiator for HP and valued by SMB customers; regulatory and corporate responsibility drivers.</t>
+          <t>Reduces cost and leverages proven components.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1733,476 +1708,467 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prod Steward, Marketing, Quality, Tech Reg</t>
+          <t>R&amp;D, Supply Chain, Product Management</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Material sourcing and supply chain capabilities.</t>
+          <t>Platform compatibility, component sourcing.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Material composition reports verify 60%+ RCP in product plastics; sustainability claims validated by third-party certification.</t>
+          <t>Components function as required in new system without modification.</t>
         </is>
       </c>
       <c r="I26" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module Integration</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Enables modern wireless features for end users.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>End Users, Product Management, IT</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Wi-Fi module sourcing, firmware integration.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Wi-Fi module passes connectivity, throughput, and security tests.</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>0.9</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 11</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Customer Replaceable Maintenance Box</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Introduce a replaceable maintenance box that can be serviced by the customer, reducing downtime and service costs.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Target SMBs lack IT support; customer-replaceable parts minimize disruption and maintenance expense.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Quality, R&amp;D Telemetry, Supplies Quality, Service</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Serviceability design, warranty policy, PHA/MINK criteria.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Maintenance box can be replaced by end-users with clear instructions; field tests confirm &lt;15 min replacement time and &lt;5% service calls for related issues.</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FW Dune Firmware Platform</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Use Dune as the firmware platform for the printer.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Standardizes software stack and leverages existing firmware capabilities.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>R&amp;D, Software, Product Management</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hardware compatibility, feature support.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Firmware is stable and all required features are functional on Dune platform.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Integrate Gauss4.xx hardware and firmware security features.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ensures compliance with HP security standards and protects against threats.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Security, IT, Product Management</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hardware and firmware integration.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Security features pass internal and external security audits.</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>25/20ppm Print Speed (PDL: 25/19ppm)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Printer must achieve print speeds of 25/20 pages per minute (PPM), with PDL at 25/19 PPM.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Maintains competitive performance for target segments.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>End Users, Marketing, Product Management</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Firmware, print engine, IDS.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Printer achieves specified print speeds in standard test environments.</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Support for SMB and Enterprise Solutions</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM).</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Expands addressable market and enhances feature set for business customers.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Business Customers, IT, Product Management</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Software integration, platform support.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Printer integrates with required business solutions and passes interoperability tests.</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Client &amp; Driver Support (HPX, PSA, SUPD, UPD, EasyStart, USS, UFD)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Support a wide range of clients and drivers including HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Maximizes compatibility with various operating environments and user needs.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>End Users, IT, Product Management</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Driver development, OS compatibility.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>All listed drivers are available and pass installation and functional tests.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Serviceability: Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Design for serviceable maintenance box to enable easy upkeep and reduce downtime.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces total cost of ownership.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Maintenance box design, user documentation.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Maintenance box is user/service replaceable and passes serviceability tests.</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>0.85</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Keyed Bottles for Consumables</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and reduce user errors.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Ensures correct consumable usage, reduces support calls, and improves user experience for non-technical SMB users.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Supplies Quality, Quality, Service</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Ink system design, supply chain for keyed bottles.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>All consumable bottles are uniquely keyed; user testing shows &lt;2% error rate in refilling.</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Consolidated SMB Portal for Device Management</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Provide a unified portal for SMBs to manage all printers, monitor usage, access AI solutions, and receive support.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Unmanaged/lightly managed SMBs require simple, centralized tools for device management due to lack of IT staff.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>GXD, R&amp;D Telemetry, Marketing, BA</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Integration with AI solutions, device firmware, and support systems.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Portal is accessible, supports multi-device management, integrates AI features, and receives positive feedback in SMB user testing.</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Develop and integrate 'Perfect Print' and 'Perfect Scan' features leveraging AI to optimize output quality and workflow efficiency.</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Differentiates HP from competitors and addresses SMB need for high-quality, efficient document handling with minimal intervention.</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>GXD, R&amp;D Telemetry, Marketing</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>AI software development, hardware compatibility, SMB portal integration.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>AI-driven print/scan features function as specified; quality benchmarks met or exceeded; user testing confirms improved workflow efficiency.</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Protect Micro/SMB Segments and Ink/Laser Profit Pool</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Product must be positioned and designed to protect HP's Micro/SMB segments and safeguard traditional ink/laser profit pools from competitors.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Strategic market defense and revenue protection.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management, Marketing</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Product positioning, feature set.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Market share in target segments is maintained or improved post-launch.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>0.9</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 7, 11</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Offer a warranty covering either 80,000 printed pages or 2 years, whichever comes first.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SMBs require predictable, reliable coverage for budgeting and risk mitigation.</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Quality, Marketing, Service</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Service and support planning, warranty terms documentation.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Warranty terms included in product documentation; service systems configured to track usage and time; customers receive warranty support as specified.</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>PHA and MINK Serviceability Thresholds</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Design the product for 'Planned Hardware Architecture' (PHA) customer replaceable parts and 'Minimum Intervention Needed by Knowledgeable' (MINK) at service centers for out-of-warranty repairs, targeting maximum customer replaceability.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Reduces downtime, improves user experience, and lowers service costs for SMBs without IT staff.</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Quality, Service, R&amp;D Telemetry</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Hardware design, service documentation, training materials.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Service documentation specifies PHA and MINK parts; &gt;80% of common repairs are customer-replaceable; field data shows reduced service center visits.</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>PDL and Non-PDL SKU Differentiation</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Release both PDL (Page Description Language) and Non-PDL SKUs, with PDL supporting higher print speeds (target 25/20 ppm), PDL/PS support, and Blue Angel certification; Non-PDL supports SMB 2.0 Solutions and Advanced View SMB portal, and PaaS.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Addresses varied SMB needs and regulatory requirements, enables market segmentation and compliance.</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Marketing, Tech Reg, R&amp;D Telemetry, BA</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Firmware/software development, certification processes, SKU management.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Both SKUs available with specified features; print speed and certification targets met; portal and PaaS support functional.</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Mobile Printing via HP App</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Enable seamless mobile printing capabilities through the HP App for SMB users.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Supports modern workstyles and increases convenience for SMBs with mobile-centric workflows.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>GXD, Marketing, BA</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>App development, printer firmware compatibility.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Mobile printing works reliably with HP App; user testing confirms &lt;2 min setup and successful print from mobile devices.</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>0.85</v>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Support for PaaS (Platform as a Service)</t>
+          <t>Lead with LaserJet, Flank with PDL in Medium &amp; Enterprise Segments</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ensure the printer and associated software support PaaS business models, enabling solutions monetization and service delivery.</t>
+          <t>Strategy must prioritize LaserJet leadership and PDL flanking for medium and enterprise segments to win over competitors as CISS grows.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Aligns with HP’s strategic intent to accelerate PaaS and opens new revenue streams.</t>
+          <t>Strengthens competitive position in growing CISS market.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Marketing, BA, Tech Reg, GXD</t>
+          <t>Business Leadership, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Software platform integration, licensing, and billing systems.</t>
+          <t>Product portfolio, go-to-market strategy.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Printer integrates with PaaS platform; SMBs can subscribe to and utilize services via portal.</t>
+          <t>Product adoption in medium/enterprise segments meets strategic goals.</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2210,114 +2176,1007 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Grow CISS Profitable Share in New Segments</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>The product must enable HP to grow profitable share in new segments with CISS.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Business growth through market expansion.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Business Leadership, Product Management, Marketing</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Product features, market entry strategy.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Increased market share and profitability in new CISS segments.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K (Constrain)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must have a life rating of 65,000 pages, considered a hard constraint.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Ensures reliability and aligns with constrained priorities.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality, Service</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>PHA design, IDS, ink system.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PHA passes 65K page life testing under standard conditions.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years (Optimize)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>The printer must support a warranty life of 2 years.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Aligns with market expectations and competitive offerings.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Warranty, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Component reliability, service model.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Product warranty is valid for 2 years with failure rates within target limits.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK (Flexible)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Printer should support hosting 12K page yield for CMYK as a flexible (non-mandatory) goal.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Provides future scalability and differentiation.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ink system, IDS, firmware.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Product supports 12K CMYK configuration if required by market.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Trade Page 6K (Flexible)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Printer should support trade page yield of 6K as a flexible (non-mandatory) goal.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Allows for market-driven product variations.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ink system, IDS, firmware.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Product supports 6K trade page configuration if required by market.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AI Productivity Solutions for Print and Scan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI-powered productivity features for print and scan workflows, including automated document classification, error correction, and workflow optimization.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Addresses SMB need for efficiency and ROI with minimal IT support, and differentiates Magellan from competitors with unique AI capabilities.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Requires robust processing hardware and software integration; may depend on SMB portal and telemetry features.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>AI features are available out-of-box; users can complete common scanning/printing tasks with at least 20% less manual intervention compared to prior HP SMB solutions; user satisfaction &gt;80% in pilot.</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SMB Portal for Device Management</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Develop a consolidated web-based portal tailored for unmanaged/lightly managed SMBs to manage multiple printers, monitor usage, perform troubleshooting, and access support resources.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Target customers lack dedicated IT; central, user-friendly management is critical for operational efficiency and reduces support burden.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Integration with device firmware and telemetry systems; must support both PDL and non-PDL SKUs.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Portal supports registration, monitoring, basic troubleshooting, and reporting for all Magellan printers in a customer’s fleet; usability score &gt;80% in user testing.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 10, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO in Segment</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Design Magellan to deliver the lowest total cost of ownership (TCO) for SMB color printing, including consumables, maintenance, and energy efficiency.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TCO is a top decision factor for SMBs and a key differentiator against competitors like Epson and Canon.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'Supplies Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Requires use of high-capacity ink tanks, optimized energy consumption, and minimal scheduled maintenance.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Independent TCO analysis confirms Magellan’s TCO is at least 10% lower than leading competitor models in target geographies.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 6, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Customer Replaceable Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Introduce a replaceable maintenance box that end-users (not just technicians) can easily swap, reducing downtime and service costs.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SMBs lack IT staff and require minimal-intervention solutions; this is a new feature for HP in this segment.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Design must ensure ease-of-access and minimal risk of incorrect installation; may impact warranty/service processes.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Maintenance box replacement can be completed by a non-technical user in &lt;5 minutes with no tools; instructional material provided.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles for Refilling</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and reduce user error, supporting both environmental and operational goals.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Prevents costly errors for SMBs and supports sustainability and serviceability goals.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Supplies Quality', 'Prod Steward']</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Requires compatible tank and bottle design; must be supported by supply chain.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Ink bottles cannot be inserted into the wrong tank; error rate &lt;1% in field trials.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Warranty: 80k Pages or 2 Years</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Offer a warranty covering either 80,000 pages printed or 2 years, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Meets SMB expectations for reliability and supports value proposition.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Requires reliability engineering and warranty process updates.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Warranty terms published and honored; field failure rate within agreed thresholds for covered period.</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PHA and MINK Serviceability Model</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Implement a service model where PHA parts are customer-replaceable and MINK parts are serviced at centers, with a target to maximize customer-replaceable components.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Minimizes downtime and cost for SMBs with limited IT resources.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Requires clear documentation and design for user accessibility.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>At least 80% of common field-replaceable parts are customer-replaceable; service documentation available.</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Support for PaaS (Printing as a Service)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Enable Magellan to support HP’s PaaS offerings, including remote management, usage-based billing, and integration with HP’s cloud services.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Aligns with HP’s strategic goal of accelerating PaaS adoption and recurring revenue.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'DVAR', 'Tech Reg', 'BA']</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Requires integration with HP cloud and billing systems; must meet security and privacy standards.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Magellan can be enrolled in HP PaaS and managed remotely; meets HP’s PaaS compliance checklist.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 6, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PDL SKU: Enhanced Print Speed and PDL/PS Support</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PDL SKUs must deliver print speeds of at least 25/20 ppm (improvement over current 25/19) and support PDL/PS (Page Description Languages/PostScript).</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Addresses needs of more demanding SMBs and competitive parity.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'DVAR']</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Requires hardware capable of higher speeds and appropriate firmware.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves 25/20 ppm in standard test conditions; passes compatibility testing with major PDL/PS workflows.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Blue Angel Certification for PDL SKU</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ensure PDL SKU meets Blue Angel environmental certification requirements.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Environmental compliance is increasingly a purchase criterion for SMBs and required in some regions.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Prod Steward', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Requires design to meet power, emissions, and material standards.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>PDL SKU receives Blue Angel certification prior to launch.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% Recycled Content Plastic (RCP)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Design Magellan with at least 60% recycled content plastic, exceeding competitor benchmarks (Epson 30%).</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Supports HP’s sustainability goals and provides competitive differentiation.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Prod Steward', 'Quality']</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Supply chain and materials sourcing must support high RCP.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bill of materials confirms 60% RCP; verified by third-party audit.</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Blue Angel Certification for PDL SKU</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Achieve Blue Angel environmental certification for PDL SKU to meet regulatory and customer sustainability expectations.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Satisfies regulatory and market requirements in key regions; supports HP’s sustainability positioning.</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Enable robust mobile printing capabilities through the HP App, supporting iOS and Android platforms.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SMBs require flexibility and mobile workflows; aligns with customer use cases.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tech Reg, Prod Steward, Marketing</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Product design, certification testing, documentation.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>PDL SKU passes Blue Angel certification and is listed in relevant registries.</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD']</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Requires app integration and firmware support.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Users can print from mobile devices with &lt;2 steps; passes compatibility testing with major mobile OS versions.</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9, 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Advanced Telemetry for Fleet Management</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Implement advanced telemetry for monitoring device health, usage, and predictive maintenance, accessible via the SMB portal and for HP support teams.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Enables proactive support, reduces downtime, and supports PaaS and managed print services.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Requires secure data transmission and integration with HP backend systems.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Telemetry data is updated in real-time, actionable insights provided to users and HP support; meets HP security standards.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 3, 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Perfect Print and Perfect Scan Solutions</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Integrate ‘Perfect Print’ and ‘Perfect Scan’ solutions leveraging AI for optimal print quality and automated scan enhancements.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Key differentiator for Magellan; directly addresses SMB needs for quality and productivity.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality']</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Requires AI solution integration and hardware support.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Print and scan outputs meet or exceed predefined quality benchmarks in &gt;95% of test cases.</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Support for Advanced View SMB Portal (Non-PDL SKU)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Non-PDL SKUs must support SMB2.0 Solutions and Advanced View SMB portal for enhanced manageability and reporting.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Ensures all product variants offer value-added management features.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'BA']</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Requires software/firmware development and integration.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Non-PDL SKUs are compatible with Advanced View SMB portal at launch.</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Telemetry Requirements</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Implement telemetry capabilities for remote monitoring, diagnostics, and usage tracking to support SMB manageability and service.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Enables proactive support, reduces downtime, and provides data for continuous improvement.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>R&amp;D Telemetry, Service, GXD, Quality</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Firmware, portal integration, data privacy compliance.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Telemetry data is securely collected, accessible to support teams, and actionable insights are generated; privacy compliance validated.</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 3, 12</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -425,58 +425,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Stakeholders</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Stakeholders</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>citation</t>
         </is>
       </c>
     </row>
@@ -488,17 +493,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>NGB Keyed Bottles with Increased Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The printer must support new NGB keyed bottles, with 6K Black and 6K CMY page yield, and CMY bottle size greater than 8K.</t>
+          <t>Develop new NGB keyed bottles supporting 6K Black and 6K CMY page yield, with CMY bottle size exceeding 8K.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To increase ink capacity and reduce user intervention, supporting higher yield and competitive differentiation.</t>
+          <t>To increase consumable yield, reducing frequency of replacement and supporting higher volume printing environments.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -508,17 +513,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Consumables, Product Management</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires compatibility with NOA-F, IDS, and bottle keying system.</t>
+          <t>Ink formulation compatibility, printer tank design, bottle manufacturing.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Printer accepts and recognizes new NGB keyed bottles; achieves 6K Black and 6K CMY page yield; supports CMY bottle size &gt;8K.</t>
+          <t>Bottles are keyed, support 6K Black and 6K CMY yields, and CMY bottle size is &gt;8K; validated in printer system with no compatibility or reliability issues.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -529,6 +534,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -538,17 +544,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>Spill-Free Bottle Reliability</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The system must ensure spill-free reliability when users replace ink bottles.</t>
+          <t>Ensure new bottles and tank system deliver spill-free operation during all user interactions.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To enhance user experience and minimize mess or damage during bottle changes.</t>
+          <t>To improve user experience and reduce mess/errors during ink refilling.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -558,17 +564,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, Service, R&amp;D</t>
+          <t>End Users, Customer Support, R&amp;D</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NGB keyed bottle design, IDS system.</t>
+          <t>Bottle and tank interface design.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No ink spill occurs in &gt;99.5% of bottle replacement events during testing.</t>
+          <t>No ink spillage during normal use and refilling, verified by user testing and reliability assessments.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -579,6 +585,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -593,12 +600,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The NOA-F (Next-Gen Output Assembly - F) must include a metal foiled labyrinth and lid label, with no change to click-on push-push and TDF mechanisms.</t>
+          <t>Integrate NOA-F (Next-Gen Output Assembly-Filter) with a metal foiled labyrinth and lid label, maintaining existing click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Improved reliability and security for ink delivery and assembly.</t>
+          <t>Enhances filtration and identification while maintaining established user interface.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -608,27 +615,28 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>R&amp;D, Product Engineering, QA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOA-F design, compatibility with existing assembly mechanisms.</t>
+          <t>NOA-F part design, assembly process.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F includes specified features and passes reliability and assembly tests without modification to push-push and TDF.</t>
+          <t>NOA-F includes metal foiled labyrinth, lid label, and passes functional and assembly tests.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -638,17 +646,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>Support Customer-Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The printer must reuse the SuperAmp Si Printhead Assembly (PHA) and Magi/Nessie pigment inks without reformulation.</t>
+          <t>Design system so that both PHA (Printhead Assembly) and NOA-F are customer-replaceable parts.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>To leverage proven components, reduce development cost, and ensure supply chain efficiency.</t>
+          <t>Reduces service costs and downtime, improves customer satisfaction.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -658,27 +666,28 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Product Management</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility with new bottle and ink system.</t>
+          <t>Component design, user documentation.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks function without reformulation in the new printer system.</t>
+          <t>End users can replace PHA and NOA-F with no tools, as validated in usability studies.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -688,17 +697,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability and IDS Characterization &amp; Modelling</t>
+          <t>Warranty Page Life Goal of 80K Pages</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reliability, Water Vapor Transmission Rate (WVTR), air gain, flow rate, and IDS (Ink Delivery System) must be characterized and modeled, including startup and NOA-F end-of-life.</t>
+          <t>Printer and consumables must support a warranty page life of 80,000 pages.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ensures robust performance and predictive maintenance capability.</t>
+          <t>Supports high-usage environments and competitive positioning.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -708,27 +717,28 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Service</t>
+          <t>Product Management, Service, QA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IDS, NOA-F, ink system.</t>
+          <t>Component durability, consumable yield.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Characterization and models completed; meet reliability targets over product lifecycle.</t>
+          <t>Printer and consumables achieve 80K page life in accelerated life testing.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -738,17 +748,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ink Stability Modelling (Tank &amp; PQ Impact)</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ink stability in the tank must be modeled and assessed for impact on print quality (PQ).</t>
+          <t>Implement Reddington industrial design (ID) with increased tank size; no changes to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>To prevent print quality degradation over time due to ink instability.</t>
+          <t>Accommodates higher ink volumes while maintaining familiar design language.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -758,17 +768,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality</t>
+          <t>Industrial Design, R&amp;D, Marketing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ink system, IDS, tank design.</t>
+          <t>Tank and chassis design, ID approval.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Stability model completed; PQ is within spec after prolonged tank storage.</t>
+          <t>Printer meets Reddington ID guidelines and increased tank capacity is verified by physical measurement.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -779,6 +789,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -788,17 +799,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NOA-F as Service Part in Warranty Support</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NOA-F must be available as a service part for warranty support.</t>
+          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel environmental requirements for PDL SKU.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces downtime for customers.</t>
+          <t>Required for market access and environmental certifications.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -808,27 +819,28 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>Regulatory, Product Management</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NOA-F part logistics and support systems.</t>
+          <t>Design for compliance, documentation.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F can be ordered and replaced under warranty service procedures.</t>
+          <t>Product passes third-party EPEAT3, LOT4, and Blue Angel audits.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -838,17 +850,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Input/Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The printer lid must integrate Acumen 6 (presumably a sensor or feature).</t>
+          <t>Modify input and output trays to accommodate tank protrusion and optimize overall size.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>To enable advanced features or compliance as required by Acumen 6.</t>
+          <t>Ensures physical compatibility and user convenience.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -858,27 +870,28 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management</t>
+          <t>Mechanical Engineering, Industrial Design</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lid design, Acumen 6 compatibility.</t>
+          <t>Tank and tray design integration.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Acumen 6 is integrated and passes functional validation.</t>
+          <t>Trays fit with tank protrusion, validated in prototype builds.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -888,37 +901,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+          <t>4.3” Color Graphic Display (CGD)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Modify existing SA14 line for NOA-F and add Magi ink cart and labelling tool in Orcus 5. Mold for 1 to 4 new keyed caps.</t>
+          <t>Integrate a 4.3-inch color graphic display as the user interface.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To support new components in manufacturing.</t>
+          <t>Enhances user experience and supports advanced features.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, R&amp;D</t>
+          <t>End Users, UX/UI, Product Management</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SA14 line, Orcus 5, new cap molds.</t>
+          <t>UI design, display sourcing.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Factory lines modified and validated for new parts and processes.</t>
+          <t>4.3” CGD is functional and passes usability and reliability tests.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -929,6 +942,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -938,17 +952,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design the printer for customer-replaceable Printhead Assembly (PHA) and NOA-F.</t>
+          <t>Update service station aerosol management to accommodate changes from increased tank size and new spit platform.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Improves user convenience and reduces service costs.</t>
+          <t>Prevents contamination and maintains print quality.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -958,27 +972,28 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>R&amp;D, Service, QA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PHA, NOA-F design, user documentation.</t>
+          <t>Service station design, environmental testing.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>End users can replace PHA and NOA-F without service intervention; validated by usability testing.</t>
+          <t>Aerosol emissions within safe limits, validated in lab tests.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -988,17 +1003,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80K Pages</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The printer must meet a new warranty page life goal of 80,000 pages.</t>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Extends product life and reduces warranty claims.</t>
+          <t>Ensures reliable printhead movement and print quality.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1008,27 +1023,28 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Quality, Warranty, End Users</t>
+          <t>Mechanical Engineering, R&amp;D</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Component durability, ink system, IDS.</t>
+          <t>Tube and carriage design.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Printer passes accelerated life testing for 80,000 pages without failure.</t>
+          <t>Carriage operates within specified force limits and passes stress testing.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1038,47 +1054,48 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Support PaaS (Print-as-a-Service) Model</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Enable the printer to support Print-as-a-Service (PaaS) business model, including consumer, SMB, and enterprise onboarding paths.</t>
+          <t>Design paper path to support increased page life of 80K pages.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Expands business opportunities and adapts to modern service models.</t>
+          <t>Ensures durability and reliability over extended printer use.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Business Model, Product Management, IT</t>
+          <t>Mechanical Engineering, QA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Software, onboarding solutions, service integration.</t>
+          <t>Paper path component selection and testing.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Printer can be provisioned and managed under PaaS model for all target segments.</t>
+          <t>Paper path components show no significant wear after 80K pages in accelerated testing.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1088,47 +1105,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
+          <t>Ink Maintenance Serviceable Part (Post-80K Life)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ensure the PDL SKU meets EPEAT3, LOT4, and Blue Angel environmental requirements.</t>
+          <t>Provide an ink maintenance part that is serviceable at service centers after 80K page life.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Compliance with global eco-labels and regulatory requirements.</t>
+          <t>Supports continued printer operation beyond warranty period.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Marketing</t>
+          <t>Service, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>PDL SKU design, certification process.</t>
+          <t>Part design, service documentation.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Product is certified for EPEAT3, LOT4, and Blue Angel prior to launch.</t>
+          <t>Service centers can replace ink maintenance part post-80K life; validated by service procedure tests.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1138,37 +1156,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Input/Output Tray Changes for Tank Protrusion</t>
+          <t>IDS New Make-Break and FI Connection</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Modify input and output trays to align with the increased tank protrusion and optimize overall size.</t>
+          <t>Implement new make-break and fluidic interconnect (FI) connection in IDS (Ink Delivery System).</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ensures product usability and maintains compact footprint despite larger tank.</t>
+          <t>Improves reliability and ease of assembly/servicing.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R&amp;D, Industrial Design, End Users</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tank design, tray design.</t>
+          <t>IDS design, connector sourcing.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Trays function correctly with tank protrusion; product size is minimized within constraints.</t>
+          <t>IDS make-break and FI connections are robust, leak-free, and pass assembly tests.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1179,6 +1197,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1188,37 +1207,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.3” CGD Display Integration</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch color graphical display (CGD) into the printer.</t>
+          <t>Develop a new IDS startup algorithm and air management system.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Enhances user interface and accessibility.</t>
+          <t>Ensures consistent startup performance and print quality.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>Firmware, R&amp;D, QA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Display sourcing, UI software.</t>
+          <t>IDS hardware and firmware integration.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.3” CGD is functional and passes usability tests.</t>
+          <t>Startup algorithm initializes IDS without airlocks or print defects, as verified in system tests.</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1229,6 +1248,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1238,37 +1258,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar Tubes with New Routing</t>
+          <t>New Print Quality Goals &amp; Depletion Definitions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Use Sayan Sibstar tubes for ink delivery with new tube routing and integration.</t>
+          <t>Define new print quality (PQ) goals and ink depletion criteria to align with new page yield definitions.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Improves ink flow and system reliability.</t>
+          <t>Ensures customer expectations are met for print quality and consumable life.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Product Management, QA, R&amp;D</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tube sourcing, routing design.</t>
+          <t>PQ testing, yield analysis.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sayan Sibstar tubes are integrated and pass reliability and performance tests.</t>
+          <t>PQ and depletion goals are documented and met in system tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1279,6 +1299,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1288,17 +1309,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Reuse of Marconi Hi PDL and Tux dASIC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Update service station for improved aerosol management due to new tank design.</t>
+          <t>Leverage existing Marconi Hi PDL and Tux dASIC for the Magellan platform.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Prevents aerosol-related issues and maintains print quality.</t>
+          <t>Reduces development time and leverages proven technology.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1308,27 +1329,28 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Service</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Service station design, tank integration.</t>
+          <t>Compatibility testing, firmware integration.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Aerosol levels are within safe limits during operation and maintenance.</t>
+          <t>Marconi Hi PDL and Tux dASIC are integrated and functional in Magellan platform.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1338,17 +1360,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model with New Weights</t>
+          <t>Integration of Stingray Wi-Fi Module and Dune FW</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Model and validate carriage dynamics and force with new tube routing and weights.</t>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity and system control.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ensures reliable printhead movement and print quality.</t>
+          <t>Supports modern connectivity and feature set.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1358,17 +1380,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality</t>
+          <t>R&amp;D, Connectivity, QA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carriage design, tube integration.</t>
+          <t>Module sourcing, firmware compatibility.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Carriage system operates within force and dynamic tolerances under new configuration.</t>
+          <t>Wi-Fi and firmware function as specified in all supported use cases.</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1379,6 +1401,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1388,17 +1411,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Paper Path for Increased Page Life</t>
+          <t>Gauss4.xx Security Implementation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Design paper path to support increased page life and durability.</t>
+          <t>Implement Gauss4.xx security features in hardware and firmware.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Supports new 80K page life warranty goal.</t>
+          <t>Ensures device security and compliance with HP standards.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1408,17 +1431,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Service</t>
+          <t>Security, IT, QA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Paper path design, component durability.</t>
+          <t>HW/FW development, security testing.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paper path passes endurance testing for 80,000 pages.</t>
+          <t>All Gauss4.xx security requirements are met and verified by security audit.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1429,6 +1452,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1438,47 +1462,48 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part Post-80K Life</t>
+          <t>PaaS (Printing as a Service) Enablement</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Designate ink maintenance as a serviceable part at service centers after 80K page life.</t>
+          <t>Enable PaaS business model, supporting consumer, SMB, and enterprise service paths.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Facilitates extended printer use and serviceability.</t>
+          <t>Expands revenue streams and adapts to evolving customer needs.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>Business, Service, IT</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ink maintenance design, service logistics.</t>
+          <t>Service integration, platform readiness.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ink maintenance can be replaced at service centers post-80K pages.</t>
+          <t>PaaS is operational for all targeted customer segments, validated by service onboarding tests.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1488,47 +1513,48 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>SMB and Enterprise Solution Support</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Develop new make-break and fluidic interconnect (FI) connection for the ink delivery system.</t>
+          <t>Integrate SMB manageability and enterprise support, including WJA, HPSM, and JAM solutions.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ensures reliable and easy ink system assembly and maintenance.</t>
+          <t>Meets requirements of business customers for device management and integration.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>SMB/Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>IDS design, NOA-F, bottle system.</t>
+          <t>Solution integration, software development.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>New connections pass reliability and user assembly tests.</t>
+          <t>Solutions are integrated and pass customer acceptance tests.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1538,47 +1564,48 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Leverage LEBI Ink-Tank with Increased Size, Keying, and LOI SHAID</t>
+          <t>Client &amp; Driver Support Expansion</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Use LEBI ink-tank with increased size, keying, and LOI SHAID for enhanced security and compatibility.</t>
+          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Improves ink system security and prevents incorrect installation.</t>
+          <t>Ensures broad compatibility with user environments.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Service</t>
+          <t>End Users, IT, Support</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>LEBI tank design, SHAID implementation.</t>
+          <t>Driver development, certification.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tank passes size, keying, and LOI SHAID validation tests.</t>
+          <t>All listed clients and drivers function with Magellan printer as specified.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1588,17 +1615,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Speed: 25/20 ppm (PDL: 25/19 ppm)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Implement a new startup algorithm and air management for the ink delivery system.</t>
+          <t>Achieve print speeds of 25/20 pages per minute (ppm), with PDL speeds of 25/19 ppm.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Improves startup reliability and print quality.</t>
+          <t>Competitive performance for target market segments.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1608,17 +1635,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality</t>
+          <t>Product Management, Marketing, End Users</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>IDS, NOA-F, ink system.</t>
+          <t>Engine design, firmware optimization.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Startup passes reliability and print quality benchmarks.</t>
+          <t>Printer achieves specified speeds in standardized print tests.</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1629,6 +1656,7 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1638,17 +1666,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New Print Quality Goals &amp; Depletion Definition</t>
+          <t>SuperAmp PHA Life at 65K Pages</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Establish new print quality (PQ) goals and depletion definition to match page yield specifications.</t>
+          <t>SuperAmp Printhead Assembly (PHA) must achieve a life of 65,000 pages.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ensures output meets user expectations and competitive benchmarks.</t>
+          <t>Ensures reliability and reduces maintenance for high-volume users.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1658,17 +1686,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Quality, Product Management, End Users</t>
+          <t>R&amp;D, Service, Product Management</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>IDS, ink system, firmware.</t>
+          <t>PHA design, materials.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PQ meets or exceeds targets at specified depletion points.</t>
+          <t>SuperAmp PHA passes 65K page life tests without failure.</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1676,9 +1704,10 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1688,17 +1717,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Warranty Life: 2 Years or Page Count</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux digital ASIC, Hannibal analog ASIC, and Raccoon power supply unit in the new platform.</t>
+          <t>Provide a warranty life of 2 years or specified page count, whichever comes first.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Reduces cost and leverages proven components.</t>
+          <t>Aligns with market expectations and competitive offerings.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1708,27 +1737,28 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Product Management</t>
+          <t>Product Management, Service, Customers</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Platform compatibility, component sourcing.</t>
+          <t>Durability testing, warranty policy.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Components function as required in new system without modification.</t>
+          <t>Warranty terms are documented and validated by compliance team.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1738,17 +1768,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>Serviceability: Maintenance Box</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+          <t>Ensure maintenance box is serviceable for routine maintenance and part replacement.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Enables modern wireless features for end users.</t>
+          <t>Facilitates easy servicing and reduces downtime.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1758,47 +1788,44 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>End Users, Product Management, IT</t>
+          <t>Service, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Wi-Fi module sourcing, firmware integration.</t>
+          <t>Maintenance box design, service documentation.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Wi-Fi module passes connectivity, throughput, and security tests.</t>
+          <t>Maintenance box can be replaced or serviced by trained personnel; validated by service procedure tests.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FW Dune Firmware Platform</t>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Use Dune as the firmware platform for the printer.</t>
+          <t>Integrate advanced AI-powered productivity features, scan workflow automation, and manageability solutions to simplify business operations for SMB customers.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Standardizes software stack and leverages existing firmware capabilities.</t>
+          <t>SMBs require ease of management and efficiency due to limited IT resources; AI-driven features will differentiate the product and address key pain points.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1808,47 +1835,48 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>R&amp;D, Software, Product Management</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hardware compatibility, feature support.</t>
+          <t>Requires integration with SMB portal and AI solution modules.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Firmware is stable and all required features are functional on Dune platform.</t>
+          <t>Product demonstrates AI-powered productivity, scan workflow, and manageability features in customer use cases; validated via usability studies with SMB users.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Integrate Gauss4.xx hardware and firmware security features.</t>
+          <t>Design the printer to deliver HP's lowest business TCO for SMBs, including minimal intervention and cost-effective supplies.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ensures compliance with HP security standards and protects against threats.</t>
+          <t>SMBs are cost-sensitive and seek ROI and efficiency; low TCO is a key differentiator.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1858,17 +1886,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Security, IT, Product Management</t>
+          <t>['Marketing', 'GXD', 'Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hardware and firmware integration.</t>
+          <t>Requires cost analysis, supply chain optimization, and support for keyed bottles.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Security features pass internal and external security audits.</t>
+          <t>TCO analysis demonstrates lowest cost compared to HP's other business printers and key competitors.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1876,29 +1904,30 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 11</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>25/20ppm Print Speed (PDL: 25/19ppm)</t>
+          <t>Sustainable SMB Tank Printer (60% RCP)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Printer must achieve print speeds of 25/20 pages per minute (PPM), with PDL at 25/19 PPM.</t>
+          <t>Ensure the printer is the most sustainable SMB tank printer, targeting 60% recycled content plastic (RCP) in device construction.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Maintains competitive performance for target segments.</t>
+          <t>Sustainability is a growing customer priority and a competitive differentiator (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1908,47 +1937,48 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>End Users, Marketing, Product Management</t>
+          <t>['Marketing', 'Prod Steward', 'Quality']</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Firmware, print engine, IDS.</t>
+          <t>Material sourcing and manufacturing process changes required.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Printer achieves specified print speeds in standard test environments.</t>
+          <t>Printer BOM and certifications confirm minimum 60% RCP; third-party audit or certification obtained.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 11</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Support for SMB and Enterprise Solutions</t>
+          <t>Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM).</t>
+          <t>Introduce a customer-replaceable maintenance box to minimize downtime and service intervention for SMBs.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Expands addressable market and enhances feature set for business customers.</t>
+          <t>Reduces maintenance complexity and cost for businesses without dedicated IT support.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1958,47 +1988,48 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Business Customers, IT, Product Management</t>
+          <t>['Quality', 'DVAR', 'Tech Reg', 'BA']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Software integration, platform support.</t>
+          <t>Design and service documentation updates; training materials for customers.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Printer integrates with required business solutions and passes interoperability tests.</t>
+          <t>SMB users can replace maintenance box without HP service intervention; validated by usability testing.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Client &amp; Driver Support (HPX, PSA, SUPD, UPD, EasyStart, USS, UFD)</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Support a wide range of clients and drivers including HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
+          <t>Use keyed ink bottles to prevent incorrect refilling and ensure ease of use for SMB customers.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Maximizes compatibility with various operating environments and user needs.</t>
+          <t>Reduces user errors, improves reliability, and supports cost efficiency.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2008,17 +2039,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>End Users, IT, Product Management</t>
+          <t>['Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Driver development, OS compatibility.</t>
+          <t>Supply chain and packaging updates.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>All listed drivers are available and pass installation and functional tests.</t>
+          <t>Keyed bottles prevent incorrect installation in &gt;99% of test cases.</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2026,199 +2057,203 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Serviceability: Maintenance Box</t>
+          <t>SMB Portal for Printer Management</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Design for serviceable maintenance box to enable easy upkeep and reduce downtime.</t>
+          <t>Provide a consolidated SMB portal for device management, supporting both unmanaged and lightly managed SMB environments.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces total cost of ownership.</t>
+          <t>Non-IT decision makers need simple, centralized management tools for multiple devices.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Integration with device firmware and cloud services.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Portal supports all key management functions and is positively rated by SMB user testers (&gt;80% satisfaction).</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 10</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Support for PaaS (Platform as a Service)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Enable the printer to support HP's Platform as a Service (PaaS) offerings, including advanced monitoring and billing features.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Supports HP's business model evolution and customer demand for managed print services.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Service, End Users, Product Management</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Maintenance box design, user documentation.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Maintenance box is user/service replaceable and passes serviceability tests.</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'R&amp;D Telemetry']</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Requires integration with HP PaaS backend.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Printer can be enrolled and managed via HP PaaS; billing and telemetry data are correctly reported.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>0.85</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Protect Micro/SMB Segments and Ink/Laser Profit Pool</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Product must be positioned and designed to protect HP's Micro/SMB segments and safeguard traditional ink/laser profit pools from competitors.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Strategic market defense and revenue protection.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Business Leadership, Product Management, Marketing</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Product positioning, feature set.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Market share in target segments is maintained or improved post-launch.</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Warranty of 80k Pages or 2 Years</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Provides assurance to SMB customers and supports HP's value proposition.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>['Quality', 'Tech Reg', 'BA']</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Service and support readiness; warranty terms documentation.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Warranty terms are published and enforced in all supported regions.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>0.9</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Lead with LaserJet, Flank with PDL in Medium &amp; Enterprise Segments</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Strategy must prioritize LaserJet leadership and PDL flanking for medium and enterprise segments to win over competitors as CISS grows.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Strengthens competitive position in growing CISS market.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Business Leadership, Product Management, Marketing</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Product portfolio, go-to-market strategy.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Product adoption in medium/enterprise segments meets strategic goals.</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>0.85</v>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Grow CISS Profitable Share in New Segments</t>
+          <t>Serviceability: PHA and MINK at Service Centre</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>The product must enable HP to grow profitable share in new segments with CISS.</t>
+          <t>Design for serviceability, allowing customer replaceable parts (PHA) and MINK servicing at service centers if out of warranty.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Business growth through market expansion.</t>
+          <t>Reduces downtime and total cost of ownership for SMB customers.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Business Leadership, Product Management, Marketing</t>
+          <t>['Quality', 'DVAR', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Product features, market entry strategy.</t>
+          <t>Parts availability and service training.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Increased market share and profitability in new CISS segments.</t>
+          <t>Parts are customer replaceable or serviceable at centers in &gt;90% of cases; documented in service manuals.</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2226,99 +2261,101 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K (Constrain)</t>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SuperAmp PHA must have a life rating of 65,000 pages, considered a hard constraint.</t>
+          <t>Provide a non-PDL SKU that includes SMB2.0 solutions and the Advanced View SMB portal.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ensures reliability and aligns with constrained priorities.</t>
+          <t>Addresses varying customer needs and supports segmentation.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Service</t>
+          <t>['Marketing', 'GXD', 'R&amp;D Telemetry']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PHA design, IDS, ink system.</t>
+          <t>Feature differentiation between PDL and non-PDL SKUs.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>PHA passes 65K page life testing under standard conditions.</t>
+          <t>Non-PDL SKU ships with SMB2.0 and Advanced View SMB portal enabled.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years (Optimize)</t>
+          <t>PDL SKU: Speed and PS Support</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>The printer must support a warranty life of 2 years.</t>
+          <t>PDL SKU must deliver improved speeds (target 25/20 ppm) and support for PDL/PS.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Aligns with market expectations and competitive offerings.</t>
+          <t>Meets performance expectations for higher-end SMB customers and competitive positioning.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Warranty, End Users, Product Management</t>
+          <t>['Marketing', 'GXD', 'R&amp;D Telemetry']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Component reliability, service model.</t>
+          <t>Hardware and firmware support for PDL/PS and speed improvements.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Product warranty is valid for 2 years with failure rates within target limits.</t>
+          <t>PDL SKU achieves 25/20 ppm in standard test conditions and passes PDL/PS compatibility tests.</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2326,129 +2363,132 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK (Flexible)</t>
+          <t>Blue Angel Certification for PDL SKU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Printer should support hosting 12K page yield for CMYK as a flexible (non-mandatory) goal.</t>
+          <t>Ensure the PDL SKU meets Blue Angel environmental certification requirements.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Provides future scalability and differentiation.</t>
+          <t>Environmental certifications are increasingly important for business customers and regulatory compliance.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D</t>
+          <t>['Prod Steward', 'Tech Reg', 'Quality']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ink system, IDS, firmware.</t>
+          <t>Design and documentation compliance with Blue Angel standards.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Product supports 12K CMYK configuration if required by market.</t>
+          <t>PDL SKU is certified by Blue Angel prior to launch.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Trade Page 6K (Flexible)</t>
+          <t>Perfect Print and Perfect Scan Features</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Printer should support trade page yield of 6K as a flexible (non-mandatory) goal.</t>
+          <t>Implement 'Perfect Print' and 'Perfect Scan' features leveraging AI to optimize output quality and workflow efficiency.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Allows for market-driven product variations.</t>
+          <t>Enhances user experience and differentiates product in the market.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D</t>
+          <t>['Marketing', 'GXD', 'R&amp;D Telemetry']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ink system, IDS, firmware.</t>
+          <t>AI solution integration; hardware and software alignment.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Product supports 6K trade page configuration if required by market.</t>
+          <t>Feature demos show significant improvement in print/scan quality and workflow efficiency as measured by user testing.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 7, 11</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AI Productivity Solutions for Print and Scan</t>
+          <t>Mobile Printing via HP App</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-powered productivity features for print and scan workflows, including automated document classification, error correction, and workflow optimization.</t>
+          <t>Enable seamless mobile printing through the HP App, supporting both Android and iOS platforms.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Addresses SMB need for efficiency and ROI with minimal IT support, and differentiates Magellan from competitors with unique AI capabilities.</t>
+          <t>Mobile printing is a key use case for SMBs and enhances flexibility.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2458,47 +2498,48 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Requires robust processing hardware and software integration; may depend on SMB portal and telemetry features.</t>
+          <t>App integration and compatibility testing.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>AI features are available out-of-box; users can complete common scanning/printing tasks with at least 20% less manual intervention compared to prior HP SMB solutions; user satisfaction &gt;80% in pilot.</t>
+          <t>Mobile printing is available and functional on HP App for both major mobile OS; passes interoperability tests.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan MRD, Page 9, 10</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SMB Portal for Device Management</t>
+          <t>Advanced Telemetry Requirements</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Develop a consolidated web-based portal tailored for unmanaged/lightly managed SMBs to manage multiple printers, monitor usage, perform troubleshooting, and access support resources.</t>
+          <t>Implement advanced telemetry to enable proactive support, usage analytics, and remote monitoring for SMBs.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Target customers lack dedicated IT; central, user-friendly management is critical for operational efficiency and reduces support burden.</t>
+          <t>Supports manageability, service, and PaaS offerings.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2508,675 +2549,30 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['R&amp;D Telemetry', 'GXD', 'Quality']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Integration with device firmware and telemetry systems; must support both PDL and non-PDL SKUs.</t>
+          <t>Cloud and firmware integration; privacy compliance.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Portal supports registration, monitoring, basic troubleshooting, and reporting for all Magellan printers in a customer’s fleet; usability score &gt;80% in user testing.</t>
+          <t>Telemetry data is accurate, secure, and accessible via the SMB portal and HP PaaS backend.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Lowest Business TCO in Segment</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Design Magellan to deliver the lowest total cost of ownership (TCO) for SMB color printing, including consumables, maintenance, and energy efficiency.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TCO is a top decision factor for SMBs and a key differentiator against competitors like Epson and Canon.</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>['Marketing', 'Quality', 'Supplies Quality', 'BA']</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Requires use of high-capacity ink tanks, optimized energy consumption, and minimal scheduled maintenance.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Independent TCO analysis confirms Magellan’s TCO is at least 10% lower than leading competitor models in target geographies.</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 6, 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Customer Replaceable Maintenance Box</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Introduce a replaceable maintenance box that end-users (not just technicians) can easily swap, reducing downtime and service costs.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SMBs lack IT staff and require minimal-intervention solutions; this is a new feature for HP in this segment.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>['Marketing', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Design must ensure ease-of-access and minimal risk of incorrect installation; may impact warranty/service processes.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Maintenance box replacement can be completed by a non-technical user in &lt;5 minutes with no tools; instructional material provided.</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Keyed Ink Bottles for Refilling</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and reduce user error, supporting both environmental and operational goals.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Prevents costly errors for SMBs and supports sustainability and serviceability goals.</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>['Marketing', 'Supplies Quality', 'Prod Steward']</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Requires compatible tank and bottle design; must be supported by supply chain.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Ink bottles cannot be inserted into the wrong tank; error rate &lt;1% in field trials.</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Offer a warranty covering either 80,000 pages printed or 2 years, whichever comes first.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Meets SMB expectations for reliability and supports value proposition.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>['Marketing', 'Quality', 'Tech Reg']</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Requires reliability engineering and warranty process updates.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Warranty terms published and honored; field failure rate within agreed thresholds for covered period.</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>PHA and MINK Serviceability Model</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Implement a service model where PHA parts are customer-replaceable and MINK parts are serviced at centers, with a target to maximize customer-replaceable components.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Minimizes downtime and cost for SMBs with limited IT resources.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Requires clear documentation and design for user accessibility.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>At least 80% of common field-replaceable parts are customer-replaceable; service documentation available.</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Support for PaaS (Printing as a Service)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Enable Magellan to support HP’s PaaS offerings, including remote management, usage-based billing, and integration with HP’s cloud services.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Aligns with HP’s strategic goal of accelerating PaaS adoption and recurring revenue.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'DVAR', 'Tech Reg', 'BA']</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Requires integration with HP cloud and billing systems; must meet security and privacy standards.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Magellan can be enrolled in HP PaaS and managed remotely; meets HP’s PaaS compliance checklist.</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 6, 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>PDL SKU: Enhanced Print Speed and PDL/PS Support</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>PDL SKUs must deliver print speeds of at least 25/20 ppm (improvement over current 25/19) and support PDL/PS (Page Description Languages/PostScript).</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Addresses needs of more demanding SMBs and competitive parity.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'DVAR']</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Requires hardware capable of higher speeds and appropriate firmware.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>PDL SKU achieves 25/20 ppm in standard test conditions; passes compatibility testing with major PDL/PS workflows.</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Blue Angel Certification for PDL SKU</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ensure PDL SKU meets Blue Angel environmental certification requirements.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Environmental compliance is increasingly a purchase criterion for SMBs and required in some regions.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>['Marketing', 'Prod Steward', 'Tech Reg']</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Requires design to meet power, emissions, and material standards.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>PDL SKU receives Blue Angel certification prior to launch.</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Sustainability: 60% Recycled Content Plastic (RCP)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Design Magellan with at least 60% recycled content plastic, exceeding competitor benchmarks (Epson 30%).</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Supports HP’s sustainability goals and provides competitive differentiation.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>['Marketing', 'Prod Steward', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Supply chain and materials sourcing must support high RCP.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bill of materials confirms 60% RCP; verified by third-party audit.</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Mobile Printing via HP App</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Enable robust mobile printing capabilities through the HP App, supporting iOS and Android platforms.</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SMBs require flexibility and mobile workflows; aligns with customer use cases.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD']</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Requires app integration and firmware support.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Users can print from mobile devices with &lt;2 steps; passes compatibility testing with major mobile OS versions.</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9, 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Advanced Telemetry for Fleet Management</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Implement advanced telemetry for monitoring device health, usage, and predictive maintenance, accessible via the SMB portal and for HP support teams.</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Enables proactive support, reduces downtime, and supports PaaS and managed print services.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Requires secure data transmission and integration with HP backend systems.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Telemetry data is updated in real-time, actionable insights provided to users and HP support; meets HP security standards.</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
           <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Perfect Print and Perfect Scan Solutions</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Integrate ‘Perfect Print’ and ‘Perfect Scan’ solutions leveraging AI for optimal print quality and automated scan enhancements.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Key differentiator for Magellan; directly addresses SMB needs for quality and productivity.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Requires AI solution integration and hardware support.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Print and scan outputs meet or exceed predefined quality benchmarks in &gt;95% of test cases.</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 7, 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Support for Advanced View SMB Portal (Non-PDL SKU)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Non-PDL SKUs must support SMB2.0 Solutions and Advanced View SMB portal for enhanced manageability and reporting.</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Ensures all product variants offer value-added management features.</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Requires software/firmware development and integration.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Non-PDL SKUs are compatible with Advanced View SMB portal at launch.</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,17 +493,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with Increased Yield</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed bottles supporting 6K Black and 6K CMY page yield, with CMY bottle size exceeding 8K.</t>
+          <t>Develop and implement NGB keyed ink bottles supporting 6,000 pages for Black and 6,000 pages for CMY, with CMY bottle size &gt;8,000 pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To increase consumable yield, reducing frequency of replacement and supporting higher volume printing environments.</t>
+          <t>To support high-volume printing and reduce frequency of bottle replacement, enhancing user convenience and competitiveness against rivals.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -513,17 +513,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Consumables, Product Management</t>
+          <t>R&amp;D, Product Management, End Users, Operations</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ink formulation compatibility, printer tank design, bottle manufacturing.</t>
+          <t>Bottle design, tank size, IDS integration, ink compatibility</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bottles are keyed, support 6K Black and 6K CMY yields, and CMY bottle size is &gt;8K; validated in printer system with no compatibility or reliability issues.</t>
+          <t>NGB keyed bottles are validated to deliver at least 6,000 pages (Black, CMY) and CMY bottle size supports &gt;8,000 pages as per ISO standards in field and lab tests.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -544,17 +544,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Bottle Reliability</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure new bottles and tank system deliver spill-free operation during all user interactions.</t>
+          <t>Ensure new ink bottles are designed for spill-free operation during user refills, leveraging metal foiled labyrinth and lid label technologies.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To improve user experience and reduce mess/errors during ink refilling.</t>
+          <t>To minimize mess and improve user satisfaction, reducing support calls and warranty claims.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -564,17 +564,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, Customer Support, R&amp;D</t>
+          <t>R&amp;D, End Users, Support</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle and tank interface design.</t>
+          <t>Bottle design, NOA-F integration, manufacturing process</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No ink spillage during normal use and refilling, verified by user testing and reliability assessments.</t>
+          <t>Refill process achieves &lt;1% spill rate in user testing across 100+ cycles; zero major leakage incidents in warranty period.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -600,12 +600,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Integrate NOA-F (Next-Gen Output Assembly-Filter) with a metal foiled labyrinth and lid label, maintaining existing click-on push-push and TDF mechanisms.</t>
+          <t>Integrate NOA-F (New Output Assembly - Fill) with a metal foiled labyrinth and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enhances filtration and identification while maintaining established user interface.</t>
+          <t>Improves reliability and traceability while maintaining user familiarity with existing mechanisms.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -615,17 +615,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Engineering, QA</t>
+          <t>R&amp;D, Operations, Quality Assurance</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOA-F part design, assembly process.</t>
+          <t>Existing NOA-F design, click-on push-push, TDF mechanism</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F includes metal foiled labyrinth, lid label, and passes functional and assembly tests.</t>
+          <t>NOA-F assembly passes reliability and traceability tests, and is compatible with current push-push and TDF features.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -646,17 +646,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Support Customer-Replaceable PHA and NOA-F</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Design system so that both PHA (Printhead Assembly) and NOA-F are customer-replaceable parts.</t>
+          <t>Leverage existing SuperAmp Si PHA hardware and Magi/Nessie pigment inks without reformulation for the Magellan printer series.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces service costs and downtime, improves customer satisfaction.</t>
+          <t>Reduces R&amp;D cost, speeds time to market, and leverages proven technology.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>R&amp;D, Operations, Product Management</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Component design, user documentation.</t>
+          <t>Compatibility with new system architecture, ink delivery system</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>End users can replace PHA and NOA-F with no tools, as validated in usability studies.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie inks are integrated and pass all functional and reliability tests in Magellan platform.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -697,17 +697,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80K Pages</t>
+          <t>Reliability, WVTR, Air Gain, Flow Rate, and IDS Characterization</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Printer and consumables must support a warranty page life of 80,000 pages.</t>
+          <t>Perform comprehensive modeling and characterization for reliability, Water Vapor Transmission Rate (WVTR), air gain, flow rate, and Ink Delivery System (IDS), including startup and NOA-F end-of-life.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Supports high-usage environments and competitive positioning.</t>
+          <t>Ensures long-term performance, reliability, and consistent print quality throughout the printer's lifespan.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,21 +717,21 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Product Management, Service, QA</t>
+          <t>R&amp;D, Quality Assurance, Service</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Component durability, consumable yield.</t>
+          <t>IDS design, ink/tank architecture, NOA-F lifecycle</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Printer and consumables achieve 80K page life in accelerated life testing.</t>
+          <t>All parameters (WVTR, air gain, flow rate) meet specified targets in lab and simulated field environments for startup and EOL scenarios.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -748,17 +748,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Reddington ID with Increased Tank Size</t>
+          <t>Ink Stability Modeling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Implement Reddington industrial design (ID) with increased tank size; no changes to Marconi-HI ADF.</t>
+          <t>Model ink stability in both tank and print system, assessing impact to print quality (PQ) over time.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Accommodates higher ink volumes while maintaining familiar design language.</t>
+          <t>Prevents print quality degradation and ensures reliable operation over extended use.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Industrial Design, R&amp;D, Marketing</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tank and chassis design, ID approval.</t>
+          <t>Ink chemistry, tank design, IDS parameters</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Printer meets Reddington ID guidelines and increased tank capacity is verified by physical measurement.</t>
+          <t>Ink stability models predict PQ within defined tolerances for 2-year/80k page warranty period.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -799,17 +799,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
+          <t>Support for Service Parts and Warranty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel environmental requirements for PDL SKU.</t>
+          <t>NOA-F should be available as a service part for in-warranty support, enabling field replacement as needed.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Required for market access and environmental certifications.</t>
+          <t>Improves serviceability and reduces downtime for end users.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management</t>
+          <t>Service, Support, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Design for compliance, documentation.</t>
+          <t>Parts logistics, NOA-F modularity, documentation</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Product passes third-party EPEAT3, LOT4, and Blue Angel audits.</t>
+          <t>NOA-F service parts are stocked and field-replaceable within standard warranty procedures.</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -850,41 +850,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Input/Output Tray Changes for Tank Protrusion</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cartridges</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Modify input and output trays to accommodate tank protrusion and optimize overall size.</t>
+          <t>Modify existing SA14 factory line for NOA-F integration; add Magi ink cartridge and labeling tool to Orcus 5 line; provision molds for 1-4 new keyed caps.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ensures physical compatibility and user convenience.</t>
+          <t>Ensures manufacturing readiness for new components and reduces production bottlenecks.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Industrial Design</t>
+          <t>Manufacturing, Operations, R&amp;D</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tank and tray design integration.</t>
+          <t>Factory layout, tooling, supply chain</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Trays fit with tank protrusion, validated in prototype builds.</t>
+          <t>SA14 and Orcus 5 lines are validated for new components with no production delays; molds for new caps are operational.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -901,41 +901,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.3” Color Graphic Display (CGD)</t>
+          <t>Page Yield and Warranty Life Targets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch color graphic display as the user interface.</t>
+          <t>Support new warranty page life goal of 80,000 pages and 2-year warranty, with throughput of 25/20 ppm (PDL: 25/19 ppm).</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Enhances user experience and supports advanced features.</t>
+          <t>Aligns with competitive benchmarks and customer expectations for reliability and value.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>End Users, UX/UI, Product Management</t>
+          <t>Product Management, End Users, Service</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UI design, display sourcing.</t>
+          <t>Hardware reliability, ink/tank capacity, IDS, service model</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.3” CGD is functional and passes usability and reliability tests.</t>
+          <t>All units meet 80,000 page yield and 2-year warranty targets in accelerated life and field tests; throughput verified at specified PPM.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -952,17 +952,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Update service station aerosol management to accommodate changes from increased tank size and new spit platform.</t>
+          <t>Design PHA (Print Head Assembly) and NOA-F to be customer-replaceable, supporting self-serviceability for users.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Prevents contamination and maintains print quality.</t>
+          <t>Reduces service costs and printer downtime, improving customer satisfaction.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, QA</t>
+          <t>End Users, Service, Support</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Service station design, environmental testing.</t>
+          <t>Modular design, user documentation, parts availability</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Aerosol emissions within safe limits, validated in lab tests.</t>
+          <t>Users can replace PHA and NOA-F with no tools or with simple instructions; &gt;95% success rate in usability tests.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1003,37 +1003,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>Product Size Optimization</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
+          <t>Increase tank size (Reddington ID) with no change to Marconi-HI ADF; optimize input and output trays to accommodate tank protrusion while minimizing overall footprint.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ensures reliable printhead movement and print quality.</t>
+          <t>Supports higher ink capacity while maintaining compact form factor for competitive advantage.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, R&amp;D</t>
+          <t>Product Design, End Users, Marketing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tube and carriage design.</t>
+          <t>Tank and tray design, mechanical integration</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Carriage operates within specified force limits and passes stress testing.</t>
+          <t>Final product dimensions meet tank capacity and fit within defined size envelope; trays function reliably with new tank design.</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1054,41 +1054,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>Sayan Sibstar Tube Integration and New Routing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Design paper path to support increased page life of 80K pages.</t>
+          <t>Leverage Sayan Sibstar tubes for 4-tube platform with new routing and integration to support increased tank size and optimized carriage movement.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ensures durability and reliability over extended printer use.</t>
+          <t>Ensures reliable ink delivery and efficient internal layout for new tank configuration.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, QA</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Paper path component selection and testing.</t>
+          <t>Tube sourcing, routing design, carriage compatibility</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paper path components show no significant wear after 80K pages in accelerated testing.</t>
+          <t>Tube integration passes reliability and flow rate tests; carriage operates within specified dynamic and force parameters.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Post-80K Life)</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Provide an ink maintenance part that is serviceable at service centers after 80K page life.</t>
+          <t>Update service station aerosol management and spit platform to accommodate changes due to new tank design.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Supports continued printer operation beyond warranty period.</t>
+          <t>Prevents contamination and ensures long-term reliability as tank and ink system change.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1125,17 +1125,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Service, R&amp;D, End Users</t>
+          <t>R&amp;D, Service, Quality Assurance</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Part design, service documentation.</t>
+          <t>Service station design, tank configuration</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance part post-80K life; validated by service procedure tests.</t>
+          <t>Aerosol management system passes environmental and reliability tests, with no increased contamination over current platform.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1156,41 +1156,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IDS New Make-Break and FI Connection</t>
+          <t>Carriage Dynamics and Force Model Update</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Implement new make-break and fluidic interconnect (FI) connection in IDS (Ink Delivery System).</t>
+          <t>Update carriage dynamic and force modeling to account for new tube routing and increased weights from larger tanks.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Improves reliability and ease of assembly/servicing.</t>
+          <t>Maintains print quality and mechanical reliability with new system configuration.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>IDS design, connector sourcing.</t>
+          <t>Carriage design, tube integration, tank weight</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>IDS make-break and FI connections are robust, leak-free, and pass assembly tests.</t>
+          <t>Carriage dynamics meet print quality and reliability specs under all operational scenarios.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1207,41 +1207,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Paperpath Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Develop a new IDS startup algorithm and air management system.</t>
+          <t>Update paperpath design to support increased page life target (80k pages).</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ensures consistent startup performance and print quality.</t>
+          <t>Ensures durability and reliability for higher page count over printer lifespan.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Firmware, R&amp;D, QA</t>
+          <t>R&amp;D, Service, Quality Assurance</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>IDS hardware and firmware integration.</t>
+          <t>Paperpath materials, mechanical design, service model</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Startup algorithm initializes IDS without airlocks or print defects, as verified in system tests.</t>
+          <t>Paperpath passes accelerated wear tests for 80k page life with no major failures.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1258,37 +1258,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New Print Quality Goals &amp; Depletion Definitions</t>
+          <t>Ink Maintenance Serviceable Part (Service Center)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Define new print quality (PQ) goals and ink depletion criteria to align with new page yield definitions.</t>
+          <t>Design ink maintenance system as a serviceable part, to be replaced post-80k page life at service centers.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ensures customer expectations are met for print quality and consumable life.</t>
+          <t>Enables continued printer operation beyond warranty period and supports service revenue.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Product Management, QA, R&amp;D</t>
+          <t>Service, Support, End Users</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PQ testing, yield analysis.</t>
+          <t>Modular ink maintenance design, service documentation</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>PQ and depletion goals are documented and met in system tests.</t>
+          <t>Ink maintenance part is replaceable in service center in under 30 minutes; documented in service manuals.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1309,41 +1309,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reuse of Marconi Hi PDL and Tux dASIC</t>
+          <t>New Make-break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Hi PDL and Tux dASIC for the Magellan platform.</t>
+          <t>Implement new make-break and fluidic interconnect (FI) connection in IDS, leveraging LEBI ink-tank with increased size, keying, and LOI (Level of Ink) One SHAID.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Reduces development time and leverages proven technology.</t>
+          <t>Supports new tank architecture, ensures secure ink delivery, and prevents misinstallation.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Compatibility testing, firmware integration.</t>
+          <t>IDS design, LEBI tank development, SHAID integration</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Marconi Hi PDL and Tux dASIC are integrated and functional in Magellan platform.</t>
+          <t>IDS connections pass leak, misinstallation, and reliability tests; SHAID correctly identifies tank and ink level.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1360,41 +1360,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Integration of Stingray Wi-Fi Module and Dune FW</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity and system control.</t>
+          <t>Develop new startup algorithm and air management for IDS to ensure reliable operation and prevent air ingress.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Supports modern connectivity and feature set.</t>
+          <t>Maintains print quality and system reliability, especially with new tank and ink system.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Connectivity, QA</t>
+          <t>R&amp;D, Service, Quality Assurance</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Module sourcing, firmware compatibility.</t>
+          <t>IDS hardware, firmware update, air management components</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Wi-Fi and firmware function as specified in all supported use cases.</t>
+          <t>Startup algorithm passes reliability and startup time tests; air management prevents air bubbles in &gt;99% of test cycles.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1411,17 +1411,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security Implementation</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in hardware and firmware.</t>
+          <t>Develop new algorithms for servicing and startup to optimize performance, reliability, and user experience with new ink/tank system.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ensures device security and compliance with HP standards.</t>
+          <t>Ensures seamless user experience and supports new hardware features.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Security, IT, QA</t>
+          <t>R&amp;D, Service, Support</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HW/FW development, security testing.</t>
+          <t>Firmware development, hardware integration</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>All Gauss4.xx security requirements are met and verified by security audit.</t>
+          <t>New algorithms pass functional and reliability tests, and reduce startup/service time by at least 20%.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1462,41 +1462,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PaaS (Printing as a Service) Enablement</t>
+          <t>New Print Quality (PQ) Goals and Depletion Tracking</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Enable PaaS business model, supporting consumer, SMB, and enterprise service paths.</t>
+          <t>Define and implement new print quality goals and depletion tracking to align with new page yield definition and tank capacity.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Expands revenue streams and adapts to evolving customer needs.</t>
+          <t>Ensures consistent output and accurate yield reporting for end users.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Business, Service, IT</t>
+          <t>Product Management, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Service integration, platform readiness.</t>
+          <t>Firmware, IDS, ink/tank design</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PaaS is operational for all targeted customer segments, validated by service onboarding tests.</t>
+          <t>PQ and depletion tracking meet accuracy targets in &gt;95% of test scenarios; yields reported match ISO standards.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1513,17 +1513,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SMB and Enterprise Solution Support</t>
+          <t>Reuse Marconi Hi PDL and Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Integrate SMB manageability and enterprise support, including WJA, HPSM, and JAM solutions.</t>
+          <t>Leverage existing Marconi Hi PDL, Tux dASIC, Hannibal aASIC, and Raccoon PSU modules in the Magellan platform.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Meets requirements of business customers for device management and integration.</t>
+          <t>Reduces development cost and risk by using proven, reliable components.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1533,21 +1533,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SMB/Enterprise Customers, IT, Product Management</t>
+          <t>R&amp;D, Operations</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Solution integration, software development.</t>
+          <t>Compatibility with new platform architecture</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Solutions are integrated and pass customer acceptance tests.</t>
+          <t>All reused modules pass integration and functional validation in Magellan system.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1564,17 +1564,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Client &amp; Driver Support Expansion</t>
+          <t>Stingray Wi-Fi Module and Dune Firmware</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware for enhanced connectivity and system performance.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ensures broad compatibility with user environments.</t>
+          <t>Supports modern wireless standards and improves user experience.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1584,17 +1584,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>End Users, IT, Support</t>
+          <t>R&amp;D, End Users, IT</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Driver development, certification.</t>
+          <t>Firmware integration, Wi-Fi certification</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>All listed clients and drivers function with Magellan printer as specified.</t>
+          <t>Wi-Fi module and firmware pass connectivity and performance tests in all supported regions.</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Speed: 25/20 ppm (PDL: 25/19 ppm)</t>
+          <t>Gauss4.xx Security for Hardware and Firmware</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Achieve print speeds of 25/20 pages per minute (ppm), with PDL speeds of 25/19 ppm.</t>
+          <t>Implement Gauss4.xx security features in both hardware and firmware for the Magellan platform.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Competitive performance for target market segments.</t>
+          <t>Protects against security threats and meets enterprise requirements.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1635,17 +1635,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, End Users</t>
+          <t>IT, Enterprise Customers, Security Team</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Engine design, firmware optimization.</t>
+          <t>HW/FW integration, security certification</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Printer achieves specified speeds in standardized print tests.</t>
+          <t>System passes internal and third-party security audits for Gauss4.xx compliance.</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1666,17 +1666,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SuperAmp Printhead Assembly (PHA) must achieve a life of 65,000 pages.</t>
+          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel environmental requirements for PDL SKU.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ensures reliability and reduces maintenance for high-volume users.</t>
+          <t>Supports sustainability goals and enables sales in regulated markets.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1686,17 +1686,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Product Management</t>
+          <t>Product Management, Regulatory, Marketing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PHA design, materials.</t>
+          <t>Design for environment, supply chain compliance</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SuperAmp PHA passes 65K page life tests without failure.</t>
+          <t>Product is certified for EPEAT3, LOT4, and Blue Angel for all target markets.</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1717,45 +1717,45 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Warranty Life: 2 Years or Page Count</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Provide a warranty life of 2 years or specified page count, whichever comes first.</t>
+          <t>Use EPS foam packaging to protect the product during shipping and handling.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aligns with market expectations and competitive offerings.</t>
+          <t>Reduces damage in transit and supports product reliability.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Product Management, Service, Customers</t>
+          <t>Logistics, Operations, End Users</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Durability testing, warranty policy.</t>
+          <t>Packaging design, supply chain</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Warranty terms are documented and validated by compliance team.</t>
+          <t>&lt;0.5% damage rate in shipping tests; packaging passes drop and vibration tests.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -1768,37 +1768,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Serviceability: Maintenance Box</t>
+          <t>Business Model and Solution Support</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ensure maintenance box is serviceable for routine maintenance and part replacement.</t>
+          <t>Support Consumer, SMB, and Enterprise business models with solutions including PaaS, WorkFromHome/Flexworker, onboarding paths (Consumer/HPX, HP One, SMB Portal, ECP), scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM).</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Facilitates easy servicing and reduces downtime.</t>
+          <t>Expands market reach and addresses diverse customer needs.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Service, R&amp;D, End Users</t>
+          <t>Product Management, Sales, End Users</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Maintenance box design, service documentation.</t>
+          <t>Software solutions, onboarding flows, support infrastructure</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced or serviced by trained personnel; validated by service procedure tests.</t>
+          <t>All business model features are available and tested for respective customer segments at launch.</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1806,230 +1806,230 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Client and Driver Compatibility</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Facilitates easy setup and broad compatibility across user environments.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>End Users, IT, Support</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Driver development, client integration</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>All listed clients and drivers are fully functional and pass compatibility tests with Magellan platform.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Schedule and SuperAmp PHA Life Constraint</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Adhere to project schedule and maintain SuperAmp PHA life at 65,000 pages as a hard constraint.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ensures timely delivery and reliable component lifespan.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Program Management, R&amp;D, Operations</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>PHA testing, project management</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Project milestones are met; SuperAmp PHA achieves 65,000 page life in reliability tests.</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Integrate advanced AI-powered productivity features, scan workflow automation, and manageability solutions to simplify business operations for SMB customers.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>SMBs require ease of management and efficiency due to limited IT resources; AI-driven features will differentiate the product and address key pain points.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Requires integration with SMB portal and AI solution modules.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Product demonstrates AI-powered productivity, scan workflow, and manageability features in customer use cases; validated via usability studies with SMB users.</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Design the printer to deliver HP's lowest business TCO for SMBs, including minimal intervention and cost-effective supplies.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SMBs are cost-sensitive and seek ROI and efficiency; low TCO is a key differentiator.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'Quality', 'Supplies Quality', 'BA']</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Requires cost analysis, supply chain optimization, and support for keyed bottles.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>TCO analysis demonstrates lowest cost compared to HP's other business printers and key competitors.</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 11</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sustainable SMB Tank Printer (60% RCP)</t>
+          <t>Serviceability - Maintenance Box</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ensure the printer is the most sustainable SMB tank printer, targeting 60% recycled content plastic (RCP) in device construction.</t>
+          <t>Implement a serviceable maintenance box to support easy replacement and reduce service time.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sustainability is a growing customer priority and a competitive differentiator (Epson 30%, Canon TBC).</t>
+          <t>Improves field serviceability and reduces total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['Marketing', 'Prod Steward', 'Quality']</t>
+          <t>Service, End Users, Support</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Material sourcing and manufacturing process changes required.</t>
+          <t>Maintenance box design, service documentation</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Printer BOM and certifications confirm minimum 60% RCP; third-party audit or certification obtained.</t>
+          <t>Maintenance box is field-replaceable in under 15 minutes by service personnel; &gt;95% success rate in field tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>Host 12K-CMYK and Trade Page 6K Flexibility</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Introduce a customer-replaceable maintenance box to minimize downtime and service intervention for SMBs.</t>
+          <t>Provide flexibility to host 12K-CMYK and trade page 6K yields as a lower-priority, customer-driven feature.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Reduces maintenance complexity and cost for businesses without dedicated IT support.</t>
+          <t>Allows adaptation to specific market or customer requirements as needed.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['Quality', 'DVAR', 'Tech Reg', 'BA']</t>
+          <t>Product Management, Sales</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Design and service documentation updates; training materials for customers.</t>
+          <t>Ink/tank capacity, firmware, market feedback</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SMB users can replace maintenance box without HP service intervention; validated by usability testing.</t>
+          <t>Product can be configured for 12K-CMYK and 6K trade page yields if required by market.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Use keyed ink bottles to prevent incorrect refilling and ensure ease of use for SMB customers.</t>
+          <t>Integrate advanced AI-powered productivity and manageability solutions into the Magellan printer, including AI-driven print and scan workflows, and support for future AI enhancements.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Reduces user errors, improves reliability, and supports cost efficiency.</t>
+          <t>SMBs require efficient, easy-to-manage solutions to reduce manual intervention and improve business workflows. AI solutions are a key differentiator and a top customer need.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2039,30 +2039,30 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'BA']</t>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Supply chain and packaging updates.</t>
+          <t>SMB portal, hardware support for AI features</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Keyed bottles prevent incorrect installation in &gt;99% of test cases.</t>
+          <t>AI-driven print and scan workflows are available and functional; user feedback indicates improved productivity; solution is integrated with SMB portal.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Provide a consolidated SMB portal for device management, supporting both unmanaged and lightly managed SMB environments.</t>
+          <t>Develop a consolidated portal specifically for SMBs to manage their printers, enabling device management, monitoring, and support for multiple devices in a small office environment.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Non-IT decision makers need simple, centralized management tools for multiple devices.</t>
+          <t>Unmanaged and lightly managed SMBs lack dedicated IT teams and need a simple, consolidated interface for managing their print infrastructure.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2090,17 +2090,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Integration with device firmware and cloud services.</t>
+          <t>Integration with AI solutions, telemetry requirements</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Portal supports all key management functions and is positively rated by SMB user testers (&gt;80% satisfaction).</t>
+          <t>Portal is available for SMB customers, supports management of multiple printers, provides monitoring and support features, and is user-friendly for non-IT staff.</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2121,50 +2121,50 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Support for PaaS (Platform as a Service)</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Enable the printer to support HP's Platform as a Service (PaaS) offerings, including advanced monitoring and billing features.</t>
+          <t>Engineer Magellan to deliver HP’s lowest business TCO through efficient ink usage, minimal maintenance, and cost-effective supplies.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Supports HP's business model evolution and customer demand for managed print services.</t>
+          <t>Cost efficiency is a top priority for SMBs, directly impacting purchasing decisions and competitive positioning.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'R&amp;D Telemetry']</t>
+          <t>Marketing, Supplies Quality, DVAR, BA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Requires integration with HP PaaS backend.</t>
+          <t>Keyed bottles, maintenance features, sustainability features</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Printer can be enrolled and managed via HP PaaS; billing and telemetry data are correctly reported.</t>
+          <t>Independent benchmarking confirms lowest TCO compared to competitors; customer feedback validates cost savings.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2172,37 +2172,37 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Warranty of 80k Pages or 2 Years</t>
+          <t>High Sustainability with 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first.</t>
+          <t>Ensure that at least 60% of the plastic content in the Magellan printer is made from recycled materials, surpassing key competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Provides assurance to SMB customers and supports HP's value proposition.</t>
+          <t>Sustainability is a key differentiator and increasingly important for SMB customers and regulatory compliance.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['Quality', 'Tech Reg', 'BA']</t>
+          <t>Prod Steward, Tech Reg, Marketing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Service and support readiness; warranty terms documentation.</t>
+          <t>Supply chain capability, regulatory compliance</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Warranty terms are published and enforced in all supported regions.</t>
+          <t>Material certification verifies 60% RCP; documentation available for regulatory and marketing use.</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2223,37 +2223,37 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Serviceability: PHA and MINK at Service Centre</t>
+          <t>Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Design for serviceability, allowing customer replaceable parts (PHA) and MINK servicing at service centers if out of warranty.</t>
+          <t>Design the Magellan printer with a maintenance box that customers can easily replace themselves, reducing downtime and service costs.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Reduces downtime and total cost of ownership for SMB customers.</t>
+          <t>Unmanaged SMBs lack IT support and need minimal intervention solutions to keep printers operational.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['Quality', 'DVAR', 'Tech Reg']</t>
+          <t>Quality, Supplies Quality, DVAR</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parts availability and service training.</t>
+          <t>Serviceability standards, warranty policy</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Parts are customer replaceable or serviceable at centers in &gt;90% of cases; documented in service manuals.</t>
+          <t>End-users can replace the maintenance box without technical assistance; instructional materials are clear; field testing validates ease of replacement.</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2274,41 +2274,41 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal</t>
+          <t>Keyed Ink Bottles</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Provide a non-PDL SKU that includes SMB2.0 solutions and the Advanced View SMB portal.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Addresses varying customer needs and supports segmentation.</t>
+          <t>Reduces user errors, improves reliability, and protects the printer from damage due to incorrect supplies.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'R&amp;D Telemetry']</t>
+          <t>Supplies Quality, Quality, Marketing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Feature differentiation between PDL and non-PDL SKUs.</t>
+          <t>Printer design, supply chain</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Non-PDL SKU ships with SMB2.0 and Advanced View SMB portal enabled.</t>
+          <t>Ink bottles are uniquely keyed; only compatible bottles fit Magellan printers; field tests confirm effectiveness.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2325,37 +2325,37 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PDL SKU: Speed and PS Support</t>
+          <t>Warranty: 80k Pages or 2 Years (Whichever First)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PDL SKU must deliver improved speeds (target 25/20 ppm) and support for PDL/PS.</t>
+          <t>Offer a warranty covering either 80,000 printed pages or 2 years, whichever comes first, for the Magellan printer.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Meets performance expectations for higher-end SMB customers and competitive positioning.</t>
+          <t>Provides assurance of durability and reliability to SMB customers, a key purchase consideration.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'R&amp;D Telemetry']</t>
+          <t>Quality, DVAR, Marketing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hardware and firmware support for PDL/PS and speed improvements.</t>
+          <t>Product durability, support infrastructure</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>PDL SKU achieves 25/20 ppm in standard test conditions and passes PDL/PS compatibility tests.</t>
+          <t>Warranty terms are clearly documented; warranty claims process is established; customers are informed at purchase.</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2376,17 +2376,17 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Blue Angel Certification for PDL SKU</t>
+          <t>PHA and MINK Serviceability</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ensure the PDL SKU meets Blue Angel environmental certification requirements.</t>
+          <t>Design for serviceability such that PHA (customer replaceable) and MINK (service center replaceable) components are clearly defined, with a target for most components to be customer replaceable if out of warranty.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Environmental certifications are increasingly important for business customers and regulatory compliance.</t>
+          <t>Reduces downtime, service costs, and improves customer satisfaction among SMBs with limited IT support.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg', 'Quality']</t>
+          <t>Quality, Supplies Quality, DVAR</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Design and documentation compliance with Blue Angel standards.</t>
+          <t>Component design, service process documentation</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PDL SKU is certified by Blue Angel prior to launch.</t>
+          <t>Service manual identifies PHA and MINK components; field testing confirms ease of replacement; customer support materials are available.</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2427,50 +2427,50 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan Features</t>
+          <t>Support for PDL/PS (Page Description Language/PostScript)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Implement 'Perfect Print' and 'Perfect Scan' features leveraging AI to optimize output quality and workflow efficiency.</t>
+          <t>Ensure Magellan supports PDL and PostScript printing for the PDL SKU, targeting business users with advanced printing needs.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Enhances user experience and differentiates product in the market.</t>
+          <t>Business customers often require advanced print compatibility with enterprise software and workflows.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'R&amp;D Telemetry']</t>
+          <t>GXD, R&amp;D Telemetry, DVAR</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>AI solution integration; hardware and software alignment.</t>
+          <t>Firmware, hardware compatibility</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Feature demos show significant improvement in print/scan quality and workflow efficiency as measured by user testing.</t>
+          <t>PDL/PS printing is available and passes compatibility tests with common business applications.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2478,50 +2478,50 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>Improved Print Speed for PDL SKU</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing through the HP App, supporting both Android and iOS platforms.</t>
+          <t>Increase print speed for PDL SKU to at least 25/20 ppm (pages per minute), improving over current 25/19 ppm.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mobile printing is a key use case for SMBs and enhances flexibility.</t>
+          <t>Faster print speeds are essential for productivity in SMB environments and a competitive differentiator.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
+          <t>GXD, R&amp;D Telemetry, DVAR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>App integration and compatibility testing.</t>
+          <t>Hardware design, firmware optimization</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Mobile printing is available and functional on HP App for both major mobile OS; passes interoperability tests.</t>
+          <t>Print speed for PDL SKU meets or exceeds 25/20 ppm in standard tests.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2529,48 +2529,252 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
+          <t>Blue Angel Certification Support</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ensure Magellan printer meets Blue Angel environmental certification requirements for relevant SKUs.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Environmental certifications are important for regulatory compliance and as a marketing differentiator in some regions.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tech Reg, Prod Steward, Marketing</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Design, materials, documentation</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Certification is achieved; documentation is available for marketing and regulatory use.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Support for PaaS (Platform as a Service)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Magellan must support Platform as a Service (PaaS) offerings, enabling integration with cloud-based solutions and services.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PaaS support aligns with HP’s strategic goals for solution monetization and enhanced value for SMBs.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SMB portal, firmware, cloud integration</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PaaS integration is tested and functional; customers can access cloud-based services through Magellan.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Perfect Print and Perfect Scan Features</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Deliver advanced print and scan quality features branded as 'Perfect Print' and 'Perfect Scan', leveraging AI to optimize output and user experience.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>High quality and reliability in print/scan operations are key differentiators for SMB customers.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AI solutions, hardware capabilities</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Print and scan quality meets or exceeds defined benchmarks; user feedback confirms improved experience.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 11</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mobile Printing with HP App</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Enable seamless mobile printing capabilities via the HP App, supporting common mobile operating systems and workflows.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Mobile printing is a standard expectation for SMBs and supports flexible work environments.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, Marketing</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>App integration, firmware support</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Users can print from mobile devices using the HP App with no major issues reported in field tests.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9, 10</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>Advanced Telemetry Requirements</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Implement advanced telemetry to enable proactive support, usage analytics, and remote monitoring for SMBs.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Supports manageability, service, and PaaS offerings.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Implement advanced telemetry to capture printer usage, health, and performance data for remote monitoring, diagnostics, and support.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Telemetry enables proactive support, maintenance, and solution enhancements, reducing downtime for SMBs.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>['R&amp;D Telemetry', 'GXD', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Cloud and firmware integration; privacy compliance.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Telemetry data is accurate, secure, and accessible via the SMB portal and HP PaaS backend.</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Quality, BA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SMB portal, firmware, data privacy compliance</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Telemetry data is accurate, securely transmitted, and accessible via SMB portal; privacy requirements are met.</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
         <v>0.9</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>15</t>
         </is>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,61 +413,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Requirement ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -493,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>NGB Keyed Bottles with Increased Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop and implement NGB keyed ink bottles supporting 6,000 pages for Black and 6,000 pages for CMY, with CMY bottle size &gt;8,000 pages.</t>
+          <t>Develop new generation (NGB) keyed ink bottles supporting 6,000-page yield for Black and 6,000-page yield for CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To support high-volume printing and reduce frequency of bottle replacement, enhancing user convenience and competitiveness against rivals.</t>
+          <t>Higher yield reduces customer intervention and supports market demand for longer-lasting consumables.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -513,17 +501,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users, Operations</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bottle design, tank size, IDS integration, ink compatibility</t>
+          <t>Ink formulation compatibility, bottle design, IDS integration</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NGB keyed bottles are validated to deliver at least 6,000 pages (Black, CMY) and CMY bottle size supports &gt;8,000 pages as per ISO standards in field and lab tests.</t>
+          <t>NGB bottles are available and pass page yield tests: 6K for Black, 6K (min) for CMY, with CMY size supporting &gt;8K pages. Bottles must be keyed to prevent incorrect installation.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -544,17 +532,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>Spill-Free Reliability for Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure new ink bottles are designed for spill-free operation during user refills, leveraging metal foiled labyrinth and lid label technologies.</t>
+          <t>Ensure that new ink bottles and tank integration deliver spill-free operation during installation and refilling.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To minimize mess and improve user satisfaction, reducing support calls and warranty claims.</t>
+          <t>Spill-free operation is critical for customer satisfaction and to reduce warranty/service costs.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -564,17 +552,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>R&amp;D, End Users, Support</t>
+          <t>End Users, R&amp;D, Service</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle design, NOA-F integration, manufacturing process</t>
+          <t>Bottle and tank interface design, IDS system</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Refill process achieves &lt;1% spill rate in user testing across 100+ cycles; zero major leakage incidents in warranty period.</t>
+          <t>Bottles and tanks pass spill-free reliability tests under all use conditions defined in the test plan.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -600,12 +588,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Integrate NOA-F (New Output Assembly - Fill) with a metal foiled labyrinth and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
+          <t>Implement NOA-F (Next-Gen Output Assembly-Filter) with a metal foiled labyrinth and lid label, with no change to click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Improves reliability and traceability while maintaining user familiarity with existing mechanisms.</t>
+          <t>Enhanced filtration and product differentiation, while maintaining compatibility with existing mechanisms.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -615,17 +603,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Operations, Quality Assurance</t>
+          <t>R&amp;D, Product Engineering</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Existing NOA-F design, click-on push-push, TDF mechanism</t>
+          <t>NOA-F design, existing push-push and TDF compatibility</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F assembly passes reliability and traceability tests, and is compatible with current push-push and TDF features.</t>
+          <t>NOA-F assemblies pass functional and reliability validation, and are compatible with existing mechanisms.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -646,17 +634,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>Reuse of Superamp Si PHA and Magi/Nessie Inks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leverage existing SuperAmp Si PHA hardware and Magi/Nessie pigment inks without reformulation for the Magellan printer series.</t>
+          <t>Leverage existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation for Magellan.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces R&amp;D cost, speeds time to market, and leverages proven technology.</t>
+          <t>Reduces development time and cost, ensures proven performance.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -666,17 +654,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Operations, Product Management</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility with new system architecture, ink delivery system</t>
+          <t>Compatibility with new bottle/tank system, supply chain alignment</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks are integrated and pass all functional and reliability tests in Magellan platform.</t>
+          <t>No ink reformulation required; Superamp Si PHA and Magi/Nessie inks perform to existing specifications in Magellan system.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -697,17 +685,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability, WVTR, Air Gain, Flow Rate, and IDS Characterization</t>
+          <t>Reliability, WVTR, Air Gain, Flow Rate, IDS Characterization</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Perform comprehensive modeling and characterization for reliability, Water Vapor Transmission Rate (WVTR), air gain, flow rate, and Ink Delivery System (IDS), including startup and NOA-F end-of-life.</t>
+          <t>Model and characterize reliability, water vapor transmission rate (WVTR), air gain, flow rate, and IDS (Ink Delivery System) for startup and NOA-F end-of-life (EOL).</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ensures long-term performance, reliability, and consistent print quality throughout the printer's lifespan.</t>
+          <t>Ensures system robustness and supports warranty claims.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,21 +705,21 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Service</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IDS design, ink/tank architecture, NOA-F lifecycle</t>
+          <t>Testing infrastructure, IDS design</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>All parameters (WVTR, air gain, flow rate) meet specified targets in lab and simulated field environments for startup and EOL scenarios.</t>
+          <t>Complete reliability and IDS models; pass defined reliability, WVTR, air gain, and flow rate tests for startup and NOA-F EOL.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -753,17 +741,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Model ink stability in both tank and print system, assessing impact to print quality (PQ) over time.</t>
+          <t>Develop and validate ink stability modeling for tank storage and its impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Prevents print quality degradation and ensures reliable operation over extended use.</t>
+          <t>Critical to ensure long-term ink stability and consistent print quality over product life.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -773,16 +761,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ink chemistry, tank design, IDS parameters</t>
+          <t>Ink chemistry, tank material, environmental testing</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ink stability models predict PQ within defined tolerances for 2-year/80k page warranty period.</t>
+          <t>Ink stability model is documented and validated; PQ meets defined standards after long-term storage in tank.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -799,37 +787,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Support for Service Parts and Warranty</t>
+          <t>NOA-F as Service Parts in Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NOA-F should be available as a service part for in-warranty support, enabling field replacement as needed.</t>
+          <t>NOA-F to be available as service parts for warranty support.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces downtime for end users.</t>
+          <t>Enables effective field service and warranty fulfillment.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service, Support, End Users</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parts logistics, NOA-F modularity, documentation</t>
+          <t>Parts catalog update, logistics</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F service parts are stocked and field-replaceable within standard warranty procedures.</t>
+          <t>NOA-F is listed as a service part and available within warranty support channels.</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -850,41 +838,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cartridges</t>
+          <t>Acumen 6 on Lid Integration</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Modify existing SA14 factory line for NOA-F integration; add Magi ink cartridge and labeling tool to Orcus 5 line; provision molds for 1-4 new keyed caps.</t>
+          <t>Integrate Acumen 6 (presumed security/ID feature) on the lid of the product.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ensures manufacturing readiness for new components and reduces production bottlenecks.</t>
+          <t>Enhances product security and traceability.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations, R&amp;D</t>
+          <t>Security, Product Management</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Factory layout, tooling, supply chain</t>
+          <t>Lid design, Acumen 6 module compatibility</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SA14 and Orcus 5 lines are validated for new components with no production delays; molds for new caps are operational.</t>
+          <t>Acumen 6 is integrated and functional on all production lids.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -901,17 +889,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Page Yield and Warranty Life Targets</t>
+          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Support new warranty page life goal of 80,000 pages and 2-year warranty, with throughput of 25/20 ppm (PDL: 25/19 ppm).</t>
+          <t>Modify SA14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5. Mold 1-4 new keyed caps.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aligns with competitive benchmarks and customer expectations for reliability and value.</t>
+          <t>Factory readiness for new components and processes.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -921,21 +909,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Service</t>
+          <t>Manufacturing, R&amp;D</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hardware reliability, ink/tank capacity, IDS, service model</t>
+          <t>Factory engineering, tooling procurement</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>All units meet 80,000 page yield and 2-year warranty targets in accelerated life and field tests; throughput verified at specified PPM.</t>
+          <t>SA14 and Orcus 5 lines are modified and validated for production of NOA-F and Magi ink carts, new caps in place.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -952,17 +940,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Customer Replaceable PHA and NOA-F</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design PHA (Print Head Assembly) and NOA-F to be customer-replaceable, supporting self-serviceability for users.</t>
+          <t>Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reduces service costs and printer downtime, improving customer satisfaction.</t>
+          <t>Improves serviceability and reduces downtime/costs for users and support.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -972,17 +960,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>End Users, Service, Support</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Modular design, user documentation, parts availability</t>
+          <t>Component design, user documentation, training</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Users can replace PHA and NOA-F with no tools or with simple instructions; &gt;95% success rate in usability tests.</t>
+          <t>PHA and NOA-F can be replaced by customers following provided instructions, with no tools or minimal tools required.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1003,41 +991,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Product Size Optimization</t>
+          <t>New Warranty Page Life Goal of 80K Pages</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Increase tank size (Reddington ID) with no change to Marconi-HI ADF; optimize input and output trays to accommodate tank protrusion while minimizing overall footprint.</t>
+          <t>Set and support a new warranty page life goal of 80,000 pages for the product.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Supports higher ink capacity while maintaining compact form factor for competitive advantage.</t>
+          <t>Meets market expectations for reliability and reduces warranty costs.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Product Design, End Users, Marketing</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tank and tray design, mechanical integration</t>
+          <t>Component durability, consumables yield</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Final product dimensions meet tank capacity and fit within defined size envelope; trays function reliably with new tank design.</t>
+          <t>Product passes reliability testing for 80,000 pages without major failure.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1054,17 +1042,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sayan Sibstar Tube Integration and New Routing</t>
+          <t>Size Increase for Tank (Reddington ID)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes for 4-tube platform with new routing and integration to support increased tank size and optimized carriage movement.</t>
+          <t>Increase tank size to support higher ink volumes, with no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ensures reliable ink delivery and efficient internal layout for new tank configuration.</t>
+          <t>Supports higher yield bottles and longer intervals between refills.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1074,17 +1062,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Industrial Design, End Users</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tube sourcing, routing design, carriage compatibility</t>
+          <t>Chassis and tank design, packaging</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tube integration passes reliability and flow rate tests; carriage operates within specified dynamic and force parameters.</t>
+          <t>Tank volume increased to specified capacity; product passes all fit and function tests.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1105,17 +1093,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Update service station aerosol management and spit platform to accommodate changes due to new tank design.</t>
+          <t>Use EPS foam for product packaging.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Prevents contamination and ensures long-term reliability as tank and ink system change.</t>
+          <t>Protects product during shipping and handling; aligns with packaging standards.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1125,21 +1113,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality Assurance</t>
+          <t>Logistics, Manufacturing, Sustainability</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Service station design, tank configuration</t>
+          <t>Packaging design, supplier sourcing</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Aerosol management system passes environmental and reliability tests, with no increased contamination over current platform.</t>
+          <t>All shipped products use EPS foam packaging and pass drop/impact tests.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1156,41 +1144,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Carriage Dynamics and Force Model Update</t>
+          <t>EPEAT3, LOT4, Blue Angel Certification (for PDL SKU)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force modeling to account for new tube routing and increased weights from larger tanks.</t>
+          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel environmental certification for the PDL SKU.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Maintains print quality and mechanical reliability with new system configuration.</t>
+          <t>Required for market access and sustainability goals.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>Regulatory, Product Management, Sustainability</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carriage design, tube integration, tank weight</t>
+          <t>Design compliance, documentation</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Carriage dynamics meet print quality and reliability specs under all operational scenarios.</t>
+          <t>PDL SKU is certified for EPEAT3, LOT4, and Blue Angel.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1207,17 +1195,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Paperpath Support for Increased Page Life</t>
+          <t>Input and Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Update paperpath design to support increased page life target (80k pages).</t>
+          <t>Modify input and output trays to accommodate tank protrusion and optimize size.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ensures durability and reliability for higher page count over printer lifespan.</t>
+          <t>Ensures mechanical compatibility and optimal footprint.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1227,17 +1215,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality Assurance</t>
+          <t>R&amp;D, Industrial Design</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Paperpath materials, mechanical design, service model</t>
+          <t>Chassis design, tray engineering</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paperpath passes accelerated wear tests for 80k page life with no major failures.</t>
+          <t>Trays fit and function with new tank design; product passes paper path and handling tests.</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1258,17 +1246,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Service Center)</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Design ink maintenance system as a serviceable part, to be replaced post-80k page life at service centers.</t>
+          <t>Integrate a 4.3-inch color graphical display (CGD) into the product.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Enables continued printer operation beyond warranty period and supports service revenue.</t>
+          <t>Improves user interface and control.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1278,17 +1266,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Service, Support, End Users</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Modular ink maintenance design, service documentation</t>
+          <t>UI software, display sourcing</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Ink maintenance part is replaceable in service center in under 30 minutes; documented in service manuals.</t>
+          <t>Product ships with 4.3” CGD display, and all UI functions are accessible and testable.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1309,41 +1297,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New Make-break and FI Connection for IDS</t>
+          <t>Platform with 4 Tubes and Sayan Sibstar Tube Routing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Implement new make-break and fluidic interconnect (FI) connection in IDS, leveraging LEBI ink-tank with increased size, keying, and LOI (Level of Ink) One SHAID.</t>
+          <t>Leverage Sayan Sibstar tubes with new routing and integration into the ink delivery platform (4 tubes).</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Supports new tank architecture, ensures secure ink delivery, and prevents misinstallation.</t>
+          <t>Supports multi-color ink delivery and reliability.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>IDS design, LEBI tank development, SHAID integration</t>
+          <t>Tube sourcing, chassis integration</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>IDS connections pass leak, misinstallation, and reliability tests; SHAID correctly identifies tank and ink level.</t>
+          <t>System uses 4 Sayan Sibstar tubes with validated routing and integration.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1360,41 +1348,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Develop new startup algorithm and air management for IDS to ensure reliable operation and prevent air ingress.</t>
+          <t>Update service station aerosol management and spit platform to accommodate tank changes.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Maintains print quality and system reliability, especially with new tank and ink system.</t>
+          <t>Maintains printhead reliability and cleanliness with new tank configuration.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality Assurance</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>IDS hardware, firmware update, air management components</t>
+          <t>Service station design, tank interface</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Startup algorithm passes reliability and startup time tests; air management prevents air bubbles in &gt;99% of test cycles.</t>
+          <t>Service station passes aerosol containment and cleaning tests with new tank.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1411,41 +1399,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>Carriage Dynamic and Force Modeling for New Tubes/Weights</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Develop new algorithms for servicing and startup to optimize performance, reliability, and user experience with new ink/tank system.</t>
+          <t>Model carriage dynamics and forces considering new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ensures seamless user experience and supports new hardware features.</t>
+          <t>Ensures mechanical reliability and print quality.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Support</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Firmware development, hardware integration</t>
+          <t>Carriage design, tube integration</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>New algorithms pass functional and reliability tests, and reduce startup/service time by at least 20%.</t>
+          <t>Carriage system passes dynamic and force validation tests.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1462,41 +1450,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New Print Quality (PQ) Goals and Depletion Tracking</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Define and implement new print quality goals and depletion tracking to align with new page yield definition and tank capacity.</t>
+          <t>Update paper path design to support increased page life requirement (80K pages).</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ensures consistent output and accurate yield reporting for end users.</t>
+          <t>Ensures reliable operation over extended product life.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, End Users</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Firmware, IDS, ink/tank design</t>
+          <t>Paper path component durability, reliability testing</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PQ and depletion tracking meet accuracy targets in &gt;95% of test scenarios; yields reported match ISO standards.</t>
+          <t>Paper path passes reliability test for 80,000 pages.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1513,17 +1501,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Reuse Marconi Hi PDL and Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Ink Maintenance as Serviceable Part Post-80K Life</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Hi PDL, Tux dASIC, Hannibal aASIC, and Raccoon PSU modules in the Magellan platform.</t>
+          <t>Design ink maintenance module as a serviceable part at service centers after 80,000-page life.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Reduces development cost and risk by using proven, reliable components.</t>
+          <t>Reduces total cost of ownership and supports product longevity.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1533,21 +1521,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Operations</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Compatibility with new platform architecture</t>
+          <t>Module design, service documentation</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>All reused modules pass integration and functional validation in Magellan system.</t>
+          <t>Ink maintenance module can be replaced at service center after 80K pages; process documented.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1564,17 +1552,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module and Dune Firmware</t>
+          <t>140ml Black and New CMY Bottle Sizes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware for enhanced connectivity and system performance.</t>
+          <t>Introduce 140ml black bottles and new CMY bottle sizes (volume TBD).</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Supports modern wireless standards and improves user experience.</t>
+          <t>Aligns with increased yield and market expectations.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1584,21 +1572,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, End Users, IT</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Firmware integration, Wi-Fi certification</t>
+          <t>Bottle sourcing, tank compatibility</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Wi-Fi module and firmware pass connectivity and performance tests in all supported regions.</t>
+          <t>140ml black and new CMY bottles are available and meet page yield targets.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1615,41 +1603,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security for Hardware and Firmware</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in both hardware and firmware for the Magellan platform.</t>
+          <t>Implement new make-break and fluidic interconnect (FI) connection for the Ink Delivery System (IDS).</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Protects against security threats and meets enterprise requirements.</t>
+          <t>Improves system reliability and serviceability.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IT, Enterprise Customers, Security Team</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HW/FW integration, security certification</t>
+          <t>IDS design, connection validation</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>System passes internal and third-party security audits for Gauss4.xx compliance.</t>
+          <t>IDS passes make-break and FI connection tests as per design specs.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1666,41 +1654,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
+          <t>LEBI Ink-Tank with Increased Size, Keying, and LOI SHAID</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel environmental requirements for PDL SKU.</t>
+          <t>Leverage LEBI ink-tank with increased size, keying, and single SHAID (security/authentication ID).</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Supports sustainability goals and enables sales in regulated markets.</t>
+          <t>Supports higher yield, prevents misinstallation, and enhances security.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Product Management, Regulatory, Marketing</t>
+          <t>R&amp;D, Security, Manufacturing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Design for environment, supply chain compliance</t>
+          <t>Tank design, SHAID integration</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Product is certified for EPEAT3, LOT4, and Blue Angel for all target markets.</t>
+          <t>LEBI ink-tank meets size, keying, and SHAID requirements; passes validation tests.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1717,17 +1705,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Use EPS foam packaging to protect the product during shipping and handling.</t>
+          <t>Develop new startup algorithm and air management system for IDS.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Reduces damage in transit and supports product reliability.</t>
+          <t>Ensures reliable startup and prevents air ingestion issues.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1737,21 +1725,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Logistics, Operations, End Users</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Packaging design, supply chain</t>
+          <t>IDS design, firmware development</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;0.5% damage rate in shipping tests; packaging passes drop and vibration tests.</t>
+          <t>IDS startup and air management validated in system testing.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1768,41 +1756,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Business Model and Solution Support</t>
+          <t>Reuse Marconi Hi PDL for WS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Support Consumer, SMB, and Enterprise business models with solutions including PaaS, WorkFromHome/Flexworker, onboarding paths (Consumer/HPX, HP One, SMB Portal, ECP), scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM).</t>
+          <t>Reuse Marconi Hi PDL (Print Description Language) for WS (Workstation).</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Expands market reach and addresses diverse customer needs.</t>
+          <t>Leverages proven technology and reduces development effort.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Product Management, Sales, End Users</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Software solutions, onboarding flows, support infrastructure</t>
+          <t>Compatibility with new system</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>All business model features are available and tested for respective customer segments at launch.</t>
+          <t>Marconi Hi PDL is functional in the new WS context.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1819,41 +1807,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Client and Driver Compatibility</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>Develop new servicing and startup algorithm to support new hardware and consumables.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Facilitates easy setup and broad compatibility across user environments.</t>
+          <t>Ensures reliable operation and user experience with new components.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>End Users, IT, Support</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Driver development, client integration</t>
+          <t>Firmware development, component integration</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>All listed clients and drivers are fully functional and pass compatibility tests with Magellan platform.</t>
+          <t>Servicing and startup algorithm validated in end-to-end system testing.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1870,45 +1858,45 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Schedule and SuperAmp PHA Life Constraint</t>
+          <t>New Print Quality (PQ) Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Adhere to project schedule and maintain SuperAmp PHA life at 65,000 pages as a hard constraint.</t>
+          <t>Define new print quality goals and depletion metrics to align with new page yield definitions.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ensures timely delivery and reliable component lifespan.</t>
+          <t>Ensures print quality is maintained throughout consumable life.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Program Management, R&amp;D, Operations</t>
+          <t>R&amp;D, Product Management, Quality Assurance</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PHA testing, project management</t>
+          <t>PQ testing, yield validation</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Project milestones are met; SuperAmp PHA achieves 65,000 page life in reliability tests.</t>
+          <t>PQ metrics and depletion definitions are documented and validated in testing.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -1921,17 +1909,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Serviceability - Maintenance Box</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Implement a serviceable maintenance box to support easy replacement and reduce service time.</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the new platform.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Improves field serviceability and reduces total cost of ownership for customers.</t>
+          <t>Reduces hardware development time and leverages proven components.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1941,25 +1929,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Service, End Users, Support</t>
+          <t>R&amp;D, Hardware Engineering</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Maintenance box design, service documentation</t>
+          <t>Compatibility with new system</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Maintenance box is field-replaceable in under 15 minutes by service personnel; &gt;95% success rate in field tests.</t>
+          <t>All reused components pass integration and system tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -1972,441 +1960,445 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K Flexibility</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Provide flexibility to host 12K-CMYK and trade page 6K yields as a lower-priority, customer-driven feature.</t>
+          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Allows adaptation to specific market or customer requirements as needed.</t>
+          <t>Enables wireless printing and network integration.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>End Users, IT, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Firmware development, network certification</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Wi-Fi module is integrated and passes wireless functionality tests.</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FW Dune Platform Usage</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Use FW Dune firmware platform for the printer.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Standardizes firmware and leverages existing ecosystem.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Product Management, Sales</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Ink/tank capacity, firmware, market feedback</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Product can be configured for 12K-CMYK and 6K trade page yields if required by market.</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>R&amp;D, Software Engineering</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Firmware compatibility</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>FW Dune is operational on the Magellan platform.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>0.7</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>AI Productivity and Manageability Solutions</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Integrate advanced AI-powered productivity and manageability solutions into the Magellan printer, including AI-driven print and scan workflows, and support for future AI enhancements.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>SMBs require efficient, easy-to-manage solutions to reduce manual intervention and improve business workflows. AI solutions are a key differentiator and a top customer need.</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Meets security requirements for enterprise and SMB markets.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>SMB portal, hardware support for AI features</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>AI-driven print and scan workflows are available and functional; user feedback indicates improved productivity; solution is integrated with SMB portal.</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>SMB Portal for Printer Management</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Develop a consolidated portal specifically for SMBs to manage their printers, enabling device management, monitoring, and support for multiple devices in a small office environment.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Unmanaged and lightly managed SMBs lack dedicated IT teams and need a simple, consolidated interface for managing their print infrastructure.</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Security, Enterprise Customers, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>HW/FW integration, security validation</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Gauss4.xx security features pass security validation and penetration tests.</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Support for PaaS and WorkFromHome/Flexworker Services</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Enable support for Print-as-a-Service (PaaS) and WorkFromHome/Flexworker service models.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Expands business model and addresses changing work environments.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Business Development, Service, End Users</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Service platform integration, billing</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PaaS and WorkFromHome/Flexworker features are available and functional in product.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Onboarding Paths: Consumer/HPX, HP One, SMB Portal, ECP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Provide onboarding and S&amp;O (Setup &amp; Onboarding) paths for Consumer/HPX, HP One, SMB Portal, and ECP.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ensures smooth onboarding for various customer segments.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>End Users, IT, Service</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Onboarding software, documentation</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>All onboarding paths are functional and validated in user testing.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Scan Solution Integration</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Integrate scan solution for the product.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Required for SMB and enterprise workflows.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>End Users, SMB, Enterprise</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Scanner hardware, software integration</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Scan solution is available and passes functionality and quality tests.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SMB Manageability Solution</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Provide manageability solution for SMB customers.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Addresses needs of SMB market for device management and control.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SMB Customers, IT, Service</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Management software, integration</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SMB manageability features are available and validated with SMB customer feedback.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Enterprise Support: WJA, HPSM, JAM</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Support enterprise management tools: Web Jetadmin (WJA), HP Smart Management (HPSM), and JAM.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Critical for enterprise deployment and manageability.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Integration with AI solutions, telemetry requirements</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Portal is available for SMB customers, supports management of multiple printers, provides monitoring and support features, and is user-friendly for non-IT staff.</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Engineer Magellan to deliver HP’s lowest business TCO through efficient ink usage, minimal maintenance, and cost-effective supplies.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Cost efficiency is a top priority for SMBs, directly impacting purchasing decisions and competitive positioning.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Enterprise Customers, IT</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Software integration, certification</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>WJA, HPSM, and JAM are supported and pass enterprise validation tests.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Clients &amp; Drivers: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Provide clients and drivers including HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ensures compatibility with diverse IT environments and user needs.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Marketing, Supplies Quality, DVAR, BA</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Keyed bottles, maintenance features, sustainability features</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Independent benchmarking confirms lowest TCO compared to competitors; customer feedback validates cost savings.</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>High Sustainability with 60% Recycled Content Plastic (RCP)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ensure that at least 60% of the plastic content in the Magellan printer is made from recycled materials, surpassing key competitors (Epson 30%, Canon TBC).</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Sustainability is a key differentiator and increasingly important for SMB customers and regulatory compliance.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Prod Steward, Tech Reg, Marketing</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Supply chain capability, regulatory compliance</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Material certification verifies 60% RCP; documentation available for regulatory and marketing use.</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Customer Replaceable Maintenance Box</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Design the Magellan printer with a maintenance box that customers can easily replace themselves, reducing downtime and service costs.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Unmanaged SMBs lack IT support and need minimal intervention solutions to keep printers operational.</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Quality, Supplies Quality, DVAR</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Serviceability standards, warranty policy</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>End-users can replace the maintenance box without technical assistance; instructional materials are clear; field testing validates ease of replacement.</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Keyed Ink Bottles</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Reduces user errors, improves reliability, and protects the printer from damage due to incorrect supplies.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Supplies Quality, Quality, Marketing</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Printer design, supply chain</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Ink bottles are uniquely keyed; only compatible bottles fit Magellan printers; field tests confirm effectiveness.</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Warranty: 80k Pages or 2 Years (Whichever First)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Offer a warranty covering either 80,000 printed pages or 2 years, whichever comes first, for the Magellan printer.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Provides assurance of durability and reliability to SMB customers, a key purchase consideration.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Quality, DVAR, Marketing</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Product durability, support infrastructure</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Warranty terms are clearly documented; warranty claims process is established; customers are informed at purchase.</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>PHA and MINK Serviceability</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Design for serviceability such that PHA (customer replaceable) and MINK (service center replaceable) components are clearly defined, with a target for most components to be customer replaceable if out of warranty.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Reduces downtime, service costs, and improves customer satisfaction among SMBs with limited IT support.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, DVAR</t>
+          <t>End Users, IT, Service</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Component design, service process documentation</t>
+          <t>Driver development, certification</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Service manual identifies PHA and MINK components; field testing confirms ease of replacement; customer support materials are available.</t>
+          <t>All listed drivers and clients are available and pass compatibility testing.</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2414,203 +2406,203 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Support for PDL/PS (Page Description Language/PostScript)</t>
+          <t>Throughput: 25/20ppm (PDL: 25/19ppm)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ensure Magellan supports PDL and PostScript printing for the PDL SKU, targeting business users with advanced printing needs.</t>
+          <t>Product must support print speeds of 25 ppm (pages per minute) for standard, 20 ppm for color; PDL must support 25/19 ppm.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Business customers often require advanced print compatibility with enterprise software and workflows.</t>
+          <t>Competitive print speed is a key buying factor.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Engine performance, firmware</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Product achieves specified print speeds in standard and PDL modes.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K Pages (Constraint)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA (Printhead Assembly) life is constrained to 65,000 pages.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Design limitation to be considered in warranty and service planning.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Component durability, warranty policy</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA meets or exceeds 65,000-page life in testing.</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years or Page Life (Optimize)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Warranty must cover 2 years or specified page life, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Aligns with industry standards and customer expectations.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>End Users, Service, Product Management</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Component reliability, legal compliance</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Warranty documentation reflects 2-year or page life coverage; system passes reliability testing.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Serviceability Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Provide a serviceable maintenance box for consumable waste and maintenance operations.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Improves serviceability and reduces downtime/costs.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>GXD, R&amp;D Telemetry, DVAR</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Firmware, hardware compatibility</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>PDL/PS printing is available and passes compatibility tests with common business applications.</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Improved Print Speed for PDL SKU</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Increase print speed for PDL SKU to at least 25/20 ppm (pages per minute), improving over current 25/19 ppm.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Faster print speeds are essential for productivity in SMB environments and a competitive differentiator.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>GXD, R&amp;D Telemetry, DVAR</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Hardware design, firmware optimization</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Print speed for PDL SKU meets or exceeds 25/20 ppm in standard tests.</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Blue Angel Certification Support</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ensure Magellan printer meets Blue Angel environmental certification requirements for relevant SKUs.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Environmental certifications are important for regulatory compliance and as a marketing differentiator in some regions.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Tech Reg, Prod Steward, Marketing</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Design, materials, documentation</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Certification is achieved; documentation is available for marketing and regulatory use.</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Support for PaaS (Platform as a Service)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Magellan must support Platform as a Service (PaaS) offerings, enabling integration with cloud-based solutions and services.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>PaaS support aligns with HP’s strategic goals for solution monetization and enhanced value for SMBs.</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, BA, Marketing</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SMB portal, firmware, cloud integration</t>
+          <t>Maintenance box design, service documentation</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>PaaS integration is tested and functional; customers can access cloud-based services through Magellan.</t>
+          <t>Maintenance box is serviceable and passes functional validation.</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2618,30 +2610,26 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan Features</t>
+          <t>AI Productivity Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Deliver advanced print and scan quality features branded as 'Perfect Print' and 'Perfect Scan', leveraging AI to optimize output and user experience.</t>
+          <t>Integrate advanced AI-based productivity features, including Perfect Print and Perfect Scan, to enhance workflow and manageability for SMB users.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>High quality and reliability in print/scan operations are key differentiators for SMB customers.</t>
+          <t>SMBs require efficient and easy-to-use solutions due to limited IT resources; AI solutions will streamline tasks and reduce manual intervention.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2656,25 +2644,25 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AI solutions, hardware capabilities</t>
+          <t>AI technology stack, software integration with printer firmware and SMB portal</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Print and scan quality meets or exceeds defined benchmarks; user feedback confirms improved experience.</t>
+          <t>AI-based print and scan features are accessible through the printer UI and SMB portal; user testing confirms workflow improvements; meets specified accuracy and speed benchmarks.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan MRD, Page 4, Page 7, Page 11</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2682,50 +2670,50 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mobile Printing with HP App</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing capabilities via the HP App, supporting common mobile operating systems and workflows.</t>
+          <t>Design the printer to achieve HP’s lowest business TCO for SMBs, with minimal intervention and consumables cost.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mobile printing is a standard expectation for SMBs and supports flexible work environments.</t>
+          <t>Cost efficiency is a top priority for SMBs; lower TCO is a key competitive differentiator.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, Marketing</t>
+          <t>Marketing, Quality, Supplies Quality, BA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>App integration, firmware support</t>
+          <t>Consumables design, energy efficiency, sustainability features</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Users can print from mobile devices using the HP App with no major issues reported in field tests.</t>
+          <t>TCO analysis demonstrates lowest cost in class compared to competitors; validated by internal cost modeling and external benchmarking.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan MRD, Page 4, Page 11</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2733,17 +2721,17 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Advanced Telemetry Requirements</t>
+          <t>Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Implement advanced telemetry to capture printer usage, health, and performance data for remote monitoring, diagnostics, and support.</t>
+          <t>Implement a user-replaceable maintenance box to minimize service calls and printer downtime for SMBs.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Telemetry enables proactive support, maintenance, and solution enhancements, reducing downtime for SMBs.</t>
+          <t>SMBs lack dedicated IT support; easy maintenance is critical for operational continuity.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2753,30 +2741,489 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, Quality, BA</t>
+          <t>Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Prod Steward</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SMB portal, firmware, data privacy compliance</t>
+          <t>Maintenance box design, service documentation, user instructions</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Telemetry data is accurate, securely transmitted, and accessible via SMB portal; privacy requirements are met.</t>
+          <t>Maintenance box can be replaced by non-technical users in under 5 minutes without tools; validated in usability studies.</t>
         </is>
       </c>
       <c r="I46" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, Page 11</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SMB Device Management Portal</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Develop a consolidated web-based portal for SMB customers to manage multiple HP printers, monitor usage, and access support.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Target SMB customers have multiple devices and limited IT staff; centralized management increases efficiency and reduces support burden.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Portal software development, telemetry integration, user authentication</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Portal supports registration and management of 6-15 printers per account; allows monitoring, configuration, and support access; positive feedback in user testing.</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, Page 10, Page 11</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ensure the printer is built with at least 60% recycled content plastic, surpassing competitors’ sustainability benchmarks.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sustainability is a top customer priority and competitive differentiator; aligns with HP’s environmental goals.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Prod Steward, Marketing, Tech Reg</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Supply chain sourcing, manufacturing processes</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bill of materials and supplier documentation confirm 60% RCP; validated in third-party audits.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
         <v>0.9</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 3, 12</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles for Refilling</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Use keyed ink bottles to prevent incorrect refilling and ensure user safety and printer reliability.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Prevents user error, reduces service calls, and protects printer warranty.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Quality, Supplies Quality, R&amp;D Telemetry</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ink bottle design, printer hardware compatibility</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Keyed bottles only fit correct tanks; field testing shows zero misfills in test group.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Warranty: 80,000 pages or 2 Years</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Offer a warranty covering either 80,000 pages or 2 years, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Addresses SMBs’ need for reliability and cost predictability; reduces perceived risk of ownership.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Quality, Marketing, DVAR</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Reliability testing, warranty policy alignment</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Warranty terms published; printer passes reliability tests for 80,000 pages or 2 years of typical SMB use.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PHA and MINK Serviceability</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Enable customer replaceable (PHA) and service center replaceable (MINK) parts, targeting maximum customer replaceability for out-of-warranty repairs.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs for SMBs without IT staff; enhances customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Quality, DVAR, Supplies Quality, Prod Steward</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Parts design, service documentation, training materials</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>At least 80% of common service parts are customer replaceable; validated by service call data post-launch.</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Support for PDL/PS and Improved Print Speeds</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ensure the printer supports PDL/PS (Page Description Language/PostScript) and achieves improved print speeds (target: 25/20 ppm for PDL SKUs).</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Essential for business environments with diverse document workflows and higher productivity demands.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Firmware development, hardware optimization</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Printer achieves target speeds in independent testing; PDL/PS compatibility verified with standard business workflows.</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Blue Angel Certification</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Achieve Blue Angel environmental certification for PDL SKUs.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Environmental certifications are increasingly required for business and public sector customers.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tech Reg, Prod Steward, Marketing</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Design for compliance, documentation submission</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Certification awarded by Blue Angel authority for at least one PDL SKU.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Mobile Printing Support via HP App</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Enable mobile printing capabilities through the HP App for seamless printing from smartphones and tablets.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Mobile device usage is growing in SMBs; mobile printing is a critical workflow feature.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>GXD, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>App integration, firmware support</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Mobile print jobs can be submitted and completed from the HP App on iOS and Android; validated by user testing.</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9, Page 10</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Platform Support for PaaS (Printing as a Service)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Printer and portal must support HP’s Printing as a Service (PaaS) business model for SMBs.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Enables recurring revenue and aligns with HP’s strategic shift to service-based offerings.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Marketing, BA, DVAR</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Portal and device integration, subscription management</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SMBs can enroll in and manage PaaS subscriptions through the portal; billing and usage tracked accurately.</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, Page 10</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with Increased Yield</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new generation (NGB) keyed ink bottles supporting 6,000-page yield for Black and 6,000-page yield for CMY, with CMY bottle size supporting &gt;8,000 pages.</t>
+          <t>Develop NGB keyed ink bottles supporting 6K Black and 6K CMY page yield, with CMY bottle size supporting &gt;8K pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Higher yield reduces customer intervention and supports market demand for longer-lasting consumables.</t>
+          <t>Higher page yield reduces frequency of bottle replacement, improving customer satisfaction and operational efficiency.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ink formulation compatibility, bottle design, IDS integration</t>
+          <t>Ink formulation compatibility, bottle design, printer compatibility</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NGB bottles are available and pass page yield tests: 6K for Black, 6K (min) for CMY, with CMY size supporting &gt;8K pages. Bottles must be keyed to prevent incorrect installation.</t>
+          <t>Bottles must pass validation for 6K Black and 6K CMY page yield; CMY bottle must support &gt;8K pages with no spill or reliability issues.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -532,17 +532,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Bottles</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure that new ink bottles and tank integration deliver spill-free operation during installation and refilling.</t>
+          <t>Ensure ink bottles are designed for spill-free operation during installation and replacement.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Spill-free operation is critical for customer satisfaction and to reduce warranty/service costs.</t>
+          <t>Spill-free bottles reduce mess, increase user satisfaction, and lower support costs.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -552,21 +552,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Service</t>
+          <t>End Users, R&amp;D, Customer Support</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle and tank interface design, IDS system</t>
+          <t>Bottle design, manufacturing process</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bottles and tanks pass spill-free reliability tests under all use conditions defined in the test plan.</t>
+          <t>No ink spill incidents during standard installation and replacement tests as per HP QA protocols.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -588,12 +588,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Implement NOA-F (Next-Gen Output Assembly-Filter) with a metal foiled labyrinth and lid label, with no change to click-on push-push and TDF mechanisms.</t>
+          <t>Implement NOA-F (Next-Generation Output Assembly-Filter) with a metal foiled labyrinth and lid label, retaining current push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enhanced filtration and product differentiation, while maintaining compatibility with existing mechanisms.</t>
+          <t>Enhances product reliability and supports new ink system requirements.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Engineering</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOA-F design, existing push-push and TDF compatibility</t>
+          <t>NOA-F component sourcing, assembly line modifications</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F assemblies pass functional and reliability validation, and are compatible with existing mechanisms.</t>
+          <t>NOA-F units must include metal foiled labyrinth and lid label, and pass reliability and compatibility tests.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -634,41 +634,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse of Superamp Si PHA and Magi/Nessie Inks</t>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Inks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leverage existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation for Magellan.</t>
+          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie pigment ink formulations without reformulation.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces development time and cost, ensures proven performance.</t>
+          <t>Reduces development time and costs by reusing proven components.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Procurement, Manufacturing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility with new bottle/tank system, supply chain alignment</t>
+          <t>Compatibility with new system components</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>No ink reformulation required; Superamp Si PHA and Magi/Nessie inks perform to existing specifications in Magellan system.</t>
+          <t>No ink reformulation required; successful integration with new hardware and software.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -685,17 +685,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability, WVTR, Air Gain, Flow Rate, IDS Characterization</t>
+          <t>Reliability and Performance Modelling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Model and characterize reliability, water vapor transmission rate (WVTR), air gain, flow rate, and IDS (Ink Delivery System) for startup and NOA-F end-of-life (EOL).</t>
+          <t>Conduct reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modelling, including startup and NOA-F end-of-life (EOL) scenarios.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ensures system robustness and supports warranty claims.</t>
+          <t>Ensures system performance meets quality and longevity targets.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -710,16 +710,16 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Testing infrastructure, IDS design</t>
+          <t>System design, test lab availability</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Complete reliability and IDS models; pass defined reliability, WVTR, air gain, and flow rate tests for startup and NOA-F EOL.</t>
+          <t>Comprehensive models and test reports demonstrating compliance with HP standards for reliability and performance.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -736,22 +736,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ink Stability Modeling</t>
+          <t>Ink Stability Modelling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Develop and validate ink stability modeling for tank storage and its impact on print quality (PQ).</t>
+          <t>Model ink stability in tanks and assess impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Critical to ensure long-term ink stability and consistent print quality over product life.</t>
+          <t>Prevents print quality degradation and supports warranty claims.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ink chemistry, tank material, environmental testing</t>
+          <t>Ink formulation, tank design</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ink stability model is documented and validated; PQ meets defined standards after long-term storage in tank.</t>
+          <t>Ink stability model completed with recommendations for PQ maintenance.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -787,37 +787,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts in Warranty Support</t>
+          <t>NOA-F as Service Parts for Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NOA-F to be available as service parts for warranty support.</t>
+          <t>Provide NOA-F as a service part for warranty support.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enables effective field service and warranty fulfillment.</t>
+          <t>Improves serviceability and customer satisfaction post-sale.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>Service, End Users, Warranty Management</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parts catalog update, logistics</t>
+          <t>Spare parts logistics, documentation</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F is listed as a service part and available within warranty support channels.</t>
+          <t>NOA-F available as a service part; documented in service manuals.</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -838,17 +838,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid Integration</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 (presumed security/ID feature) on the lid of the product.</t>
+          <t>Integrate Acumen 6 (presumed authentication/identification technology) on the ink bottle lid.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Enhances product security and traceability.</t>
+          <t>Enhances security and authenticity of consumables.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -858,21 +858,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Security, Product Management</t>
+          <t>R&amp;D, Security, Supply Chain</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lid design, Acumen 6 module compatibility</t>
+          <t>Acumen 6 technology integration</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Acumen 6 is integrated and functional on all production lids.</t>
+          <t>All lids feature Acumen 6 and pass authentication tests.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -889,17 +889,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Modify SA14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5. Mold 1-4 new keyed caps.</t>
+          <t>Modify SA14 production line for NOA-F; add Magi ink cartridge and labelling tool in Orcus 5.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Factory readiness for new components and processes.</t>
+          <t>Supports new product features and ensures efficient manufacturing.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -909,21 +909,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, R&amp;D</t>
+          <t>Manufacturing, Operations, Engineering</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Factory engineering, tooling procurement</t>
+          <t>Capex approval, equipment procurement</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SA14 and Orcus 5 lines are modified and validated for production of NOA-F and Magi ink carts, new caps in place.</t>
+          <t>SA14 line and Orcus 5 modifications completed and validated for production.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -940,17 +940,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Support Customer-Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable.</t>
+          <t>Design printer to allow customers to replace PHA (Printhead Assembly) and NOA-F components.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces downtime/costs for users and support.</t>
+          <t>Improves serviceability and reduces downtime for customers.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>End Users, Service, R&amp;D</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Component design, user documentation, training</t>
+          <t>Component design, user documentation</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PHA and NOA-F can be replaced by customers following provided instructions, with no tools or minimal tools required.</t>
+          <t>Customers can replace PHA and NOA-F without service intervention; validated by usability testing.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -996,12 +996,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Set and support a new warranty page life goal of 80,000 pages for the product.</t>
+          <t>Set and support a new warranty page life goal of 80,000 pages for the printer.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Meets market expectations for reliability and reduces warranty costs.</t>
+          <t>Extends product value and supports competitive positioning.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1011,21 +1011,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>Warranty Management, End Users, Marketing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Component durability, consumables yield</t>
+          <t>Component durability, QA testing</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Product passes reliability testing for 80,000 pages without major failure.</t>
+          <t>Printer and key components must meet or exceed 80K page life in accelerated testing.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1042,17 +1042,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Size Increase for Tank (Reddington ID)</t>
+          <t>SKU 2 (Hi + Hi PDL) PaaS Support</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Increase tank size to support higher ink volumes, with no change to Marconi-HI ADF.</t>
+          <t>Develop and support SKU 2 with high throughput and high PDL (Page Description Language) under a PaaS (Product as a Service) model.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Supports higher yield bottles and longer intervals between refills.</t>
+          <t>Expands business model flexibility and market reach.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1062,21 +1062,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>R&amp;D, Industrial Design, End Users</t>
+          <t>Business Development, Product Management, Sales</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chassis and tank design, packaging</t>
+          <t>SKU configuration, PaaS platform integration</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tank volume increased to specified capacity; product passes all fit and function tests.</t>
+          <t>SKU 2 available for PaaS; meets throughput and PDL specifications.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1093,17 +1093,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Use EPS foam for product packaging.</t>
+          <t>Implement Reddington ID with an increased tank size; ensure no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Protects product during shipping and handling; aligns with packaging standards.</t>
+          <t>Supports higher ink capacity without impacting existing document feeder design.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1113,21 +1113,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Logistics, Manufacturing, Sustainability</t>
+          <t>R&amp;D, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Packaging design, supplier sourcing</t>
+          <t>Tank design, ID integration</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>All shipped products use EPS foam packaging and pass drop/impact tests.</t>
+          <t>Tank size increased as specified; ADF remains unchanged and validated.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1144,41 +1144,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, Blue Angel Certification (for PDL SKU)</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel environmental certification for the PDL SKU.</t>
+          <t>Utilize EPS foam packaging for the printer and components.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Required for market access and sustainability goals.</t>
+          <t>Protects product during shipping and handling.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Sustainability</t>
+          <t>Logistics, Manufacturing, Quality Assurance</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Design compliance, documentation</t>
+          <t>Packaging design, supplier selection</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>PDL SKU is certified for EPEAT3, LOT4, and Blue Angel.</t>
+          <t>EPS foam packaging passes drop and vibration tests.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1195,41 +1195,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes for Tank Protrusion</t>
+          <t>EPEAT3, LOT4, and Blue Angel Certification</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Modify input and output trays to accommodate tank protrusion and optimize size.</t>
+          <t>Ensure product compliance with EPEAT3, LOT4, and Blue Angel standards for PDL SKU.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ensures mechanical compatibility and optimal footprint.</t>
+          <t>Meets regulatory and sustainability requirements for key markets.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Industrial Design</t>
+          <t>Regulatory, Marketing, Product Management</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chassis design, tray engineering</t>
+          <t>Design compliance, certification process</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Trays fit and function with new tank design; product passes paper path and handling tests.</t>
+          <t>Product certified for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1246,17 +1246,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.3” CGD Display Integration</t>
+          <t>Input/Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch color graphical display (CGD) into the product.</t>
+          <t>Redesign input and output trays to accommodate increased tank protrusion.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Improves user interface and control.</t>
+          <t>Ensures smooth paper handling and maintains product footprint.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UI software, display sourcing</t>
+          <t>Tank and tray design</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Product ships with 4.3” CGD display, and all UI functions are accessible and testable.</t>
+          <t>Trays function correctly with new tank design; pass paper handling tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Platform with 4 Tubes and Sayan Sibstar Tube Routing</t>
+          <t>Size Optimization</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes with new routing and integration into the ink delivery platform (4 tubes).</t>
+          <t>Optimize overall printer size for efficiency and market requirements.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Supports multi-color ink delivery and reliability.</t>
+          <t>Improves product competitiveness and reduces shipping/storage costs.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Product Management, R&amp;D, Logistics</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tube sourcing, chassis integration</t>
+          <t>Component design, packaging</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>System uses 4 Sayan Sibstar tubes with validated routing and integration.</t>
+          <t>Product size meets defined benchmarks and market expectations.</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1348,17 +1348,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Update service station aerosol management and spit platform to accommodate tank changes.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the printer.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Maintains printhead reliability and cleanliness with new tank configuration.</t>
+          <t>Enhances user interface and experience.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1368,21 +1368,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>End Users, Product Management, Design</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service station design, tank interface</t>
+          <t>Display sourcing, UI design</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Service station passes aerosol containment and cleaning tests with new tank.</t>
+          <t>4.3” CGD display operational and passes usability testing.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1399,17 +1399,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Modeling for New Tubes/Weights</t>
+          <t>Four-Tube Platform with New Routing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Model carriage dynamics and forces considering new tube routing and increased weights.</t>
+          <t>Leverage Sayan Sibstar tubes and implement new tube routing and integration for a four-tube platform.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ensures mechanical reliability and print quality.</t>
+          <t>Supports improved ink delivery and reliability.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1419,21 +1419,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carriage design, tube integration</t>
+          <t>Tube sourcing, system integration</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Carriage system passes dynamic and force validation tests.</t>
+          <t>Four-tube platform integrated and validated for reliability.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1450,41 +1450,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Update paper path design to support increased page life requirement (80K pages).</t>
+          <t>Implement service station aerosol management with spit platform changes due to new tank design.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ensures reliable operation over extended product life.</t>
+          <t>Reduces maintenance issues and improves air quality in service areas.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>Service, R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Paper path component durability, reliability testing</t>
+          <t>Service station design, platform updates</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paper path passes reliability test for 80,000 pages.</t>
+          <t>Aerosol management system operational and passes safety/QA tests.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1501,17 +1501,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part Post-80K Life</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Design ink maintenance module as a serviceable part at service centers after 80,000-page life.</t>
+          <t>Update carriage dynamic and force model to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Reduces total cost of ownership and supports product longevity.</t>
+          <t>Ensures reliable operation and print quality.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1521,17 +1521,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Module design, service documentation</t>
+          <t>Carriage design, system modelling</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Ink maintenance module can be replaced at service center after 80K pages; process documented.</t>
+          <t>Updated force model validated in simulation and physical tests.</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1552,17 +1552,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>140ml Black and New CMY Bottle Sizes</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Introduce 140ml black bottles and new CMY bottle sizes (volume TBD).</t>
+          <t>Redesign paper path to support increased printer page life.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Aligns with increased yield and market expectations.</t>
+          <t>Prevents jams and wear over extended use.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1572,21 +1572,21 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bottle sourcing, tank compatibility</t>
+          <t>Paper path design, component selection</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>140ml black and new CMY bottles are available and meet page yield targets.</t>
+          <t>Paper path validated for 80K+ pages without increased jam rates.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1603,17 +1603,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>Ink Maintenance as Serviceable Part Post-80K Life</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Implement new make-break and fluidic interconnect (FI) connection for the Ink Delivery System (IDS).</t>
+          <t>Design ink maintenance as a serviceable part, replaceable at service centers after 80K page life.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Improves system reliability and serviceability.</t>
+          <t>Extends printer lifespan and supports warranty/service model.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1623,21 +1623,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Service, End Users, Warranty Management</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>IDS design, connection validation</t>
+          <t>Component design, service documentation</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>IDS passes make-break and FI connection tests as per design specs.</t>
+          <t>Ink maintenance part replaceable at service centers; documented in service manuals.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1654,17 +1654,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LEBI Ink-Tank with Increased Size, Keying, and LOI SHAID</t>
+          <t>140ml K Bottles and New CMY Bottle Sizes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leverage LEBI ink-tank with increased size, keying, and single SHAID (security/authentication ID).</t>
+          <t>Introduce 140ml K (black) bottles and new xx ml CMY (cyan, magenta, yellow) bottles.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Supports higher yield, prevents misinstallation, and enhances security.</t>
+          <t>Supports higher page yield and reduces frequency of replacement.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1674,21 +1674,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Manufacturing</t>
+          <t>R&amp;D, Product Management, Supply Chain</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tank design, SHAID integration</t>
+          <t>Bottle design, supply chain readiness</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>LEBI ink-tank meets size, keying, and SHAID requirements; passes validation tests.</t>
+          <t>140ml K and new CMY bottles available and compatible with printer.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1705,17 +1705,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Develop new startup algorithm and air management system for IDS.</t>
+          <t>Implement new make-break and FI (fluidic interface) connection for IDS (Ink Delivery System).</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ensures reliable startup and prevents air ingestion issues.</t>
+          <t>Improves reliability and serviceability of ink system.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1725,17 +1725,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IDS design, firmware development</t>
+          <t>IDS redesign, component sourcing</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>IDS startup and air management validated in system testing.</t>
+          <t>New connection system passes reliability and serviceability tests.</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1756,41 +1756,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Reuse Marconi Hi PDL for WS</t>
+          <t>Leverage LEBI Ink-Tank with Increased Size, Keying, and LOI SHAID</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reuse Marconi Hi PDL (Print Description Language) for WS (Workstation).</t>
+          <t>Use LEBI ink-tank with increased size, keying, and a single SHAID (Secure Hardware Authentication ID).</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Leverages proven technology and reduces development effort.</t>
+          <t>Increases security and capacity of ink tank.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management</t>
+          <t>R&amp;D, Security, Product Management</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Compatibility with new system</t>
+          <t>LEBI tank sourcing, SHAID integration</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Marconi Hi PDL is functional in the new WS context.</t>
+          <t>LEBI tank integrated with keying and SHAID; passes security and capacity tests.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1807,17 +1807,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Develop new servicing and startup algorithm to support new hardware and consumables.</t>
+          <t>Develop new startup algorithm and air management system for IDS.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ensures reliable operation and user experience with new components.</t>
+          <t>Improves system reliability and print quality.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>R&amp;D, Firmware, Quality Assurance</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Firmware development, component integration</t>
+          <t>IDS redesign, firmware update</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Servicing and startup algorithm validated in end-to-end system testing.</t>
+          <t>New algorithm and air management validated in field and lab tests.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1858,17 +1858,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New Print Quality (PQ) Goals and Depletion Definition</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Define new print quality goals and depletion metrics to align with new page yield definitions.</t>
+          <t>Implement new servicing and startup algorithm for printer and ink system.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ensures print quality is maintained throughout consumable life.</t>
+          <t>Improves reliability and serviceability.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Quality Assurance</t>
+          <t>R&amp;D, Firmware, Service</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PQ testing, yield validation</t>
+          <t>Firmware development, system integration</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>PQ metrics and depletion definitions are documented and validated in testing.</t>
+          <t>Algorithm passes reliability and usability tests.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1909,41 +1909,41 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>New Print Quality Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the new platform.</t>
+          <t>Define new print quality (PQ) goals and depletion metrics to meet page yield definitions.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Reduces hardware development time and leverages proven components.</t>
+          <t>Ensures consistent print quality throughout product life.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R&amp;D, Hardware Engineering</t>
+          <t>R&amp;D, Quality Assurance, Product Management</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Compatibility with new system</t>
+          <t>PQ definition, yield testing</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>All reused components pass integration and system tests.</t>
+          <t>PQ goals and depletion definition documented and validated in testing.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1960,17 +1960,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
+          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU components.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Enables wireless printing and network integration.</t>
+          <t>Reduces development time and leverages proven technology.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>End Users, IT, R&amp;D</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Firmware development, network certification</t>
+          <t>Component compatibility</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Wi-Fi module is integrated and passes wireless functionality tests.</t>
+          <t>Components integrated and pass system validation.</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2011,41 +2011,41 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FW Dune Platform Usage</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Use FW Dune firmware platform for the printer.</t>
+          <t>Integrate Stingray Wi-Fi module into the printer platform.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Standardizes firmware and leverages existing ecosystem.</t>
+          <t>Enables wireless connectivity for users.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>R&amp;D, Software Engineering</t>
+          <t>End Users, R&amp;D, IT</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Firmware compatibility</t>
+          <t>Module sourcing, firmware integration</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>FW Dune is operational on the Magellan platform.</t>
+          <t>Wi-Fi module operational and passes connectivity tests.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2062,41 +2062,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Dune Firmware</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+          <t>Implement Dune firmware for printer control.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Meets security requirements for enterprise and SMB markets.</t>
+          <t>Ensures compatibility with hardware and new features.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Security, Enterprise Customers, R&amp;D</t>
+          <t>R&amp;D, Firmware</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HW/FW integration, security validation</t>
+          <t>Firmware development, hardware integration</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Gauss4.xx security features pass security validation and penetration tests.</t>
+          <t>Dune firmware operational and passes system tests.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2113,41 +2113,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Support for PaaS and WorkFromHome/Flexworker Services</t>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Enable support for Print-as-a-Service (PaaS) and WorkFromHome/Flexworker service models.</t>
+          <t>Incorporate Gauss4.xx security features in both hardware and firmware.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Expands business model and addresses changing work environments.</t>
+          <t>Protects device from security threats and ensures compliance.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Business Development, Service, End Users</t>
+          <t>Security, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Service platform integration, billing</t>
+          <t>Security feature integration, compliance testing</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>PaaS and WorkFromHome/Flexworker features are available and functional in product.</t>
+          <t>Gauss4.xx security passes internal and external security audits.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2164,41 +2164,41 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Onboarding Paths: Consumer/HPX, HP One, SMB Portal, ECP</t>
+          <t>High Throughput: 25/20ppm (PDL: 25/19ppm)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Provide onboarding and S&amp;O (Setup &amp; Onboarding) paths for Consumer/HPX, HP One, SMB Portal, and ECP.</t>
+          <t>Printer must support print speeds of 25/20 pages per minute (ppm), with PDL (Page Description Language) speeds of 25/19ppm.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ensures smooth onboarding for various customer segments.</t>
+          <t>Meets market expectations for performance in target segments.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>End Users, IT, Service</t>
+          <t>End Users, Marketing, Product Management</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Onboarding software, documentation</t>
+          <t>Print engine design, firmware optimization</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>All onboarding paths are functional and validated in user testing.</t>
+          <t>Printer achieves 25/20ppm (PDL: 25/19ppm) in benchmark tests.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2215,41 +2215,41 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Scan Solution Integration</t>
+          <t>Business Model: Consumer, SMB, and Enterprise Support</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Integrate scan solution for the product.</t>
+          <t>Support business models for consumer, SMB, and enterprise segments, including PaaS (Product as a Service).</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Required for SMB and enterprise workflows.</t>
+          <t>Expands addressable market and supports flexible deployment.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>End Users, SMB, Enterprise</t>
+          <t>Business Development, Sales, Product Management</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scanner hardware, software integration</t>
+          <t>SKU definition, platform configuration</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Scan solution is available and passes functionality and quality tests.</t>
+          <t>Products and SKUs tailored for consumer, SMB, and enterprise available and marketed.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2266,17 +2266,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SMB Manageability Solution</t>
+          <t>Multi-Path Onboarding and Solution Integration</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Provide manageability solution for SMB customers.</t>
+          <t>Support onboarding and solution paths for Consumer/HPX, HP One, SMB Portal, and ECP.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Addresses needs of SMB market for device management and control.</t>
+          <t>Ensures smooth onboarding and integration for diverse customer segments.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2286,17 +2286,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SMB Customers, IT, Service</t>
+          <t>End Users, IT, Sales</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Management software, integration</t>
+          <t>Platform integration, portal development</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SMB manageability features are available and validated with SMB customer feedback.</t>
+          <t>Onboarding and solution paths operational and validated for all segments.</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2317,41 +2317,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Enterprise Support: WJA, HPSM, JAM</t>
+          <t>Scan Solution and Enterprise Support</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Support enterprise management tools: Web Jetadmin (WJA), HP Smart Management (HPSM), and JAM.</t>
+          <t>Provide scan solution, SMB manageability, and enterprise support including WJA, HPSM, and JAM.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Critical for enterprise deployment and manageability.</t>
+          <t>Meets enterprise and SMB requirements for device management and scanning.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Enterprise Customers, IT</t>
+          <t>Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Software integration, certification</t>
+          <t>Solution integration, software development</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>WJA, HPSM, and JAM are supported and pass enterprise validation tests.</t>
+          <t>Scan and management solutions operational and validated by enterprise users.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2368,41 +2368,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Clients &amp; Drivers: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+          <t>Client and Driver Support</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Provide clients and drivers including HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
+          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ensures compatibility with diverse IT environments and user needs.</t>
+          <t>Ensures compatibility with HP software ecosystem and customer environments.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>End Users, IT, Service</t>
+          <t>End Users, IT, Support</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Driver development, certification</t>
+          <t>Driver development, QA testing</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>All listed drivers and clients are available and pass compatibility testing.</t>
+          <t>All listed clients and drivers supported and pass compatibility tests.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2419,17 +2419,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Throughput: 25/20ppm (PDL: 25/19ppm)</t>
+          <t>Protect SMB Segment and Ink/Laser Profit Pool</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Product must support print speeds of 25 ppm (pages per minute) for standard, 20 ppm for color; PDL must support 25/19 ppm.</t>
+          <t>Product must protect HP's micro/SMB segments and safeguard traditional ink/laser profit pool from competitors.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Competitive print speed is a key buying factor.</t>
+          <t>Defends HP market share and profitability.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2439,25 +2439,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>Marketing, Sales, Product Management</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Engine performance, firmware</t>
+          <t>Competitive analysis, feature set definition</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Product achieves specified print speeds in standard and PDL modes.</t>
+          <t>Market analysis shows maintained or increased share in SMB segment after launch.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2470,41 +2470,41 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages (Constraint)</t>
+          <t>Lead with LaserJet, Flank with PDL in Medium/Enterprise</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SuperAmp PHA (Printhead Assembly) life is constrained to 65,000 pages.</t>
+          <t>Strategically position LaserJet as lead and PDL as flank in medium and enterprise segments, targeting Epson as CISS grows.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Design limitation to be considered in warranty and service planning.</t>
+          <t>Competitive positioning against key market players.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Product Management</t>
+          <t>Product Management, Marketing, Sales</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Component durability, warranty policy</t>
+          <t>Product positioning, marketing strategy</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SuperAmp PHA meets or exceeds 65,000-page life in testing.</t>
+          <t>Product positioning and marketing materials reflect strategy; track win rates vs. competitors.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2521,17 +2521,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years or Page Life (Optimize)</t>
+          <t>Grow CISS Profitable Share in New Segments</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Warranty must cover 2 years or specified page life, whichever comes first.</t>
+          <t>Expand CISS (Continuous Ink Supply System) profitable share by entering new market segments.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Aligns with industry standards and customer expectations.</t>
+          <t>Drives revenue growth and market expansion.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2541,21 +2541,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>Business Development, Sales, Product Management</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Component reliability, legal compliance</t>
+          <t>Market analysis, product adaptation</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Warranty documentation reflects 2-year or page life coverage; system passes reliability testing.</t>
+          <t>Market share in new segments increases post-launch.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2572,41 +2572,41 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Serviceability Maintenance Box</t>
+          <t>Integrate CISS IDS, NOA-F, and Ink Tanks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Provide a serviceable maintenance box for consumable waste and maintenance operations.</t>
+          <t>Integrate CISS IDS, NOA-F, and ink tanks into the product platform.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces downtime/costs.</t>
+          <t>Improves reliability and feature set for target segments.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Maintenance box design, service documentation</t>
+          <t>System integration, component sourcing</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Maintenance box is serviceable and passes functional validation.</t>
+          <t>CISS IDS, NOA-F, and ink tanks integrated and validated in system tests.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2616,20 +2616,24 @@
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AI Productivity Solutions</t>
+          <t>SuperAmp PHA Life at 65K (Schedule Constraint)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-based productivity features, including Perfect Print and Perfect Scan, to enhance workflow and manageability for SMB users.</t>
+          <t>Ensure SuperAmp PHA life is at least 65,000 pages as a non-flexible schedule constraint.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SMBs require efficient and easy-to-use solutions due to limited IT resources; AI solutions will streamline tasks and reduce manual intervention.</t>
+          <t>Guarantees component longevity and supports warranty claims.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2639,48 +2643,48 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Marketing, GXD, R&amp;D Telemetry, BA</t>
+          <t>R&amp;D, Quality Assurance, Warranty Management</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AI technology stack, software integration with printer firmware and SMB portal</t>
+          <t>PHA design, QA testing</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>AI-based print and scan features are accessible through the printer UI and SMB portal; user testing confirms workflow improvements; meets specified accuracy and speed benchmarks.</t>
+          <t>SuperAmp PHA passes 65K page life in accelerated testing.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 11</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>Warranty Life: 2 Years or Defined Page Count</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Design the printer to achieve HP’s lowest business TCO for SMBs, with minimal intervention and consumables cost.</t>
+          <t>Support warranty life of 2 years or defined page count as a business optimization.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cost efficiency is a top priority for SMBs; lower TCO is a key competitive differentiator.</t>
+          <t>Aligns with market expectations and reduces warranty costs.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2690,17 +2694,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Marketing, Quality, Supplies Quality, BA</t>
+          <t>Warranty Management, Product Management, End Users</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Consumables design, energy efficiency, sustainability features</t>
+          <t>Component reliability, warranty policy</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>TCO analysis demonstrates lowest cost in class compared to competitors; validated by internal cost modeling and external benchmarking.</t>
+          <t>Warranty policy published and matches product reliability data.</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -2708,50 +2712,50 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 11</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>Serviceability: Maintenance Box</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Implement a user-replaceable maintenance box to minimize service calls and printer downtime for SMBs.</t>
+          <t>Ensure maintenance box is serviceable to support product longevity.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SMBs lack dedicated IT support; easy maintenance is critical for operational continuity.</t>
+          <t>Reduces downtime and maintenance costs.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Prod Steward</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Maintenance box design, service documentation, user instructions</t>
+          <t>Maintenance box design, service documentation</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by non-technical users in under 5 minutes without tools; validated in usability studies.</t>
+          <t>Maintenance box is easily accessible and replaceable; validated in service tests.</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -2759,30 +2763,30 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 11</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SMB Device Management Portal</t>
+          <t>SMB Solution Support</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Develop a consolidated web-based portal for SMB customers to manage multiple HP printers, monitor usage, and access support.</t>
+          <t>Provide solution features tailored to SMB needs (e.g., manageability, connectivity, cost efficiency).</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Target SMB customers have multiple devices and limited IT staff; centralized management increases efficiency and reduces support burden.</t>
+          <t>Addresses specific requirements of SMB customers.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2792,150 +2796,146 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
+          <t>SMB Customers, Sales, Product Management</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Portal software development, telemetry integration, user authentication</t>
+          <t>Feature definition, solution integration</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Portal supports registration and management of 6-15 printers per account; allows monitoring, configuration, and support access; positive feedback in user testing.</t>
+          <t>SMB-specific features operational and validated by pilot customers.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 10, Page 11</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Host 12K-CMYK (Flexible Priority)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ensure the printer is built with at least 60% recycled content plastic, surpassing competitors’ sustainability benchmarks.</t>
+          <t>Support hosting of 12K-CMYK as a flexible, lower-priority feature.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sustainability is a top customer priority and competitive differentiator; aligns with HP’s environmental goals.</t>
+          <t>Provides future scalability and feature differentiation.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Prod Steward, Marketing, Tech Reg</t>
+          <t>Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Supply chain sourcing, manufacturing processes</t>
+          <t>Ink system design, platform capability</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bill of materials and supplier documentation confirm 60% RCP; validated in third-party audits.</t>
+          <t>12K-CMYK hosting capability validated in system tests.</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles for Refilling</t>
+          <t>Trade Page 6K (Flexible Priority)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Use keyed ink bottles to prevent incorrect refilling and ensure user safety and printer reliability.</t>
+          <t>Support trade page 6K as a flexible, lower-priority feature.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Prevents user error, reduces service calls, and protects printer warranty.</t>
+          <t>Provides future flexibility for specific market needs.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Quality, Supplies Quality, R&amp;D Telemetry</t>
+          <t>Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ink bottle design, printer hardware compatibility</t>
+          <t>Page yield definition, system capability</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Keyed bottles only fit correct tanks; field testing shows zero misfills in test group.</t>
+          <t>Trade page 6K feature validated in system tests.</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Warranty: 80,000 pages or 2 Years</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Offer a warranty covering either 80,000 pages or 2 years, whichever comes first.</t>
+          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer, including Perfect Print and Perfect Scan capabilities.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Addresses SMBs’ need for reliability and cost predictability; reduces perceived risk of ownership.</t>
+          <t>To deliver superior productivity and ease of management for SMB customers, differentiating HP from competitors and addressing key customer needs for efficiency and ROI.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2945,30 +2945,30 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Quality, Marketing, DVAR</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Reliability testing, warranty policy alignment</t>
+          <t>Requires AI software development, integration with SMB portal, and hardware compatibility.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Warranty terms published; printer passes reliability tests for 80,000 pages or 2 years of typical SMB use.</t>
+          <t>AI features (Perfect Print, Perfect Scan, manageability) are functional, user-tested, and available at launch; measurable improvement in workflow efficiency over previous HP models.</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2976,50 +2976,50 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PHA and MINK Serviceability</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Enable customer replaceable (PHA) and service center replaceable (MINK) parts, targeting maximum customer replaceability for out-of-warranty repairs.</t>
+          <t>Design Magellan to achieve HP’s lowest business TCO for SMBs, including cost-efficient ink tank system and minimal intervention requirements.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs for SMBs without IT staff; enhances customer satisfaction.</t>
+          <t>TCO is a top decision criterion for SMBs; achieving the lowest TCO will drive market adoption and competitiveness.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Quality, DVAR, Supplies Quality, Prod Steward</t>
+          <t>['Marketing', 'Quality', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Parts design, service documentation, training materials</t>
+          <t>Requires optimized ink tank design, efficient consumables, and serviceability features.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>At least 80% of common service parts are customer replaceable; validated by service call data post-launch.</t>
+          <t>Independent cost analysis confirms Magellan has the lowest TCO among HP business printers for the SMB segment.</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 7, 11</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3027,37 +3027,37 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Support for PDL/PS and Improved Print Speeds</t>
+          <t>Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ensure the printer supports PDL/PS (Page Description Language/PostScript) and achieves improved print speeds (target: 25/20 ppm for PDL SKUs).</t>
+          <t>Implement a replaceable maintenance box that can be serviced by customers without technical assistance, reducing downtime and service costs.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Essential for business environments with diverse document workflows and higher productivity demands.</t>
+          <t>SMBs lack dedicated IT resources and require easy maintenance to minimize disruptions and costs.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, BA, Marketing</t>
+          <t>['Quality', 'Supplies Quality', 'DVAR', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Firmware development, hardware optimization</t>
+          <t>Requires design for tool-less replacement and clear instructions; must meet warranty/service policies.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Printer achieves target speeds in independent testing; PDL/PS compatibility verified with standard business workflows.</t>
+          <t>Maintenance box can be replaced by a non-technical user in under 5 minutes; validated in user testing.</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3078,50 +3078,50 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Blue Angel Certification</t>
+          <t>SMB Portal for Device Management</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Achieve Blue Angel environmental certification for PDL SKUs.</t>
+          <t>Develop a consolidated online portal for SMBs to manage multiple Magellan printers, including monitoring, configuration, and support functions.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Environmental certifications are increasingly required for business and public sector customers.</t>
+          <t>Unmanaged/Lightly Managed SMBs need centralized, user-friendly management tools to reduce IT burden.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tech Reg, Prod Steward, Marketing</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Design for compliance, documentation submission</t>
+          <t>Integration with AI solutions and telemetry; requires secure authentication and multi-device support.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Certification awarded by Blue Angel authority for at least one PDL SKU.</t>
+          <t>Portal enables management of at least 10 printers, supports all key functions, and passes usability and security reviews.</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3129,37 +3129,37 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mobile Printing Support via HP App</t>
+          <t>Warranty and Serviceability Requirements</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Enable mobile printing capabilities through the HP App for seamless printing from smartphones and tablets.</t>
+          <t>Offer warranty coverage of 80,000 pages or 2 years (whichever is first). Ensure customer replaceable parts (PHA) and service center support for MINK, with a target to maximize customer replaceability.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mobile device usage is growing in SMBs; mobile printing is a critical workflow feature.</t>
+          <t>Minimizes downtime and maintenance costs for SMBs, aligns with service expectations for the target segment.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>GXD, Marketing, BA</t>
+          <t>['Quality', 'Supplies Quality', 'DVAR', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>App integration, firmware support</t>
+          <t>Requires durable components, clear replacement procedures, and supply chain readiness.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Mobile print jobs can be submitted and completed from the HP App on iOS and Android; validated by user testing.</t>
+          <t>Warranty policy is published; customer replaceable parts are validated; service metrics meet targets.</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, Page 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3180,17 +3180,17 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Platform Support for PaaS (Printing as a Service)</t>
+          <t>Keyed Bottles for Ink Refilling</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Printer and portal must support HP’s Printing as a Service (PaaS) business model for SMBs.</t>
+          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Enables recurring revenue and aligns with HP’s strategic shift to service-based offerings.</t>
+          <t>Reduces risk of user error and protects printer performance and warranty.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Marketing, BA, DVAR</t>
+          <t>['Supplies Quality', 'Quality']</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Portal and device integration, subscription management</t>
+          <t>Requires bottle design changes and supply chain coordination.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SMBs can enroll in and manage PaaS subscriptions through the portal; billing and usage tracked accurately.</t>
+          <t>Keyed bottles are available at launch; field testing shows &lt;1% misfill incidents.</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -3218,12 +3218,216 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Non-PDL and PDL SKU Support</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Release both Non-PDL and PDL SKUs. Non-PDL SKU supports SMB2.0 Solutions, Advanced View SMB portal, and PaaS. PDL SKU supports 25/20 ppm speed, PDL/PS support, and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Addresses varied SMB customer requirements for print languages, speed, and compliance.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>['Marketing', 'Quality', 'R&amp;D Telemetry', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Requires product differentiation, certification, and feature validation.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Both SKUs are available at launch with specified features and certifications.</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ensure at least 60% of the printer’s plastic content is from recycled sources, surpassing key competitors.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and customer requirement, especially for SMBs with ESG goals.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Material sourcing, supply chain adjustments, compliance with environmental standards.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bill of materials and independent audit confirm 60% RCP in shipping units.</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Implement telemetry features to support remote monitoring, diagnostics, and usage analytics for Magellan printers.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Enables proactive support, usage insights, and continuous improvement for SMB customers and HP.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'BA']</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Integration with SMB portal and privacy/compliance measures.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Telemetry data is collected, securely transmitted, and accessible in the SMB portal; meets privacy regulations.</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 3, 12</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Enable seamless mobile printing via HP App and ensure compatibility with major mobile platforms.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Mobile-first workflows are critical for SMBs; enhances convenience and productivity.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>['GXD', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>App development, platform certification, and user documentation.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Mobile printing works with iOS and Android; validated by user testing and app store reviews.</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9, 10</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -413,63 +413,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Stakeholders</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Stakeholders</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Requirement ID</t>
         </is>
       </c>
     </row>
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity features and scan workflow solutions, as well as manageability tools, into the Magellan printer to simplify business operations for SMBs.</t>
+          <t>Develop new NGB keyed ink bottles with 6,000-page yield for black and CMY, and increased bottle size for CMY (&gt;8,000 pages).</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Target customers (unmanaged/lightly managed SMBs) require easy-to-use, efficient management and productivity tools without dedicated IT staff.</t>
+          <t>To meet market demand for higher capacity and reduce frequency of bottle replacement, supporting cost efficiency and user convenience.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,17 +501,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires software and firmware support for AI features and portal integration.</t>
+          <t>Ink system compatibility, bottle design, supply chain adjustments</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Printer includes AI-powered print/scan features and a management portal accessible to office managers/generalists; verified via feature demo and user testing.</t>
+          <t>Bottles are available in both 6K (Black/CMY) and &gt;8K (CMY) capacities, function reliably with the printer, and pass yield and quality testing.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -519,7 +519,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -532,17 +532,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Design Magellan to deliver HP’s lowest business TCO in the SMB segment, minimizing intervention and maintenance costs.</t>
+          <t>Ensure new ink bottles and refilling system are designed for spill-free operation during user handling and servicing.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SMBs are highly cost-sensitive and require solutions that reduce ongoing operational expenses.</t>
+          <t>Spill-free operation improves user experience, reduces mess, and minimizes warranty claims due to ink spills.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -552,25 +552,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'BA']</t>
+          <t>End Users, Service, R&amp;D</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Requires hardware design for efficiency, supply chain for affordable consumables, and warranty/service model alignment.</t>
+          <t>Bottle and ink tank interface design</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Verified TCO analysis shows Magellan is lowest among HP business printers for SMBs; independent validation or internal benchmarking completed.</t>
+          <t>Refilling process must pass defined spill-free reliability tests in lab and field trials.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -583,17 +583,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>High Serviceability &amp; Customer Replaceable Parts</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ensure key components (e.g., maintenance box) are customer replaceable and design for easy serviceability, with PHA (Primary Hardware Assembly) replaceable by customer and MINK at service center if out of warranty.</t>
+          <t>Implement NOA-F (Next-Gen Output Assembly-Filter) with a metal foiled labyrinth and lid label, with no change to click-on push-push and TDF mechanism.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SMB customers lack IT staff and need minimal downtime, so easy part replacement is critical.</t>
+          <t>Improved reliability and traceability for service and warranty support.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
+          <t>R&amp;D, Service, Manufacturing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Requires hardware design for tool-less or simple replacement and clear documentation.</t>
+          <t>NOA-F component sourcing and assembly process</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Field test demonstrates customer can replace designated parts without technical support; documented in user manual.</t>
+          <t>NOA-F units must include metal foiled labyrinth and lid label, and maintain compatibility with existing push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -621,7 +621,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -634,45 +634,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Supply</t>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.</t>
+          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without ink reformulation for Magellan.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces user errors, improves reliability, and protects supply revenue.</t>
+          <t>Reduces R&amp;D cost and time, ensures proven reliability and performance.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Quality']</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Requires new bottle design and printer hardware interface.</t>
+          <t>Compatibility testing with new system components</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Keyed bottles pass usability and compatibility tests; only correct bottles can be inserted and used.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie inks are validated for use in Magellan with no reformulation.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -685,17 +685,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Support for SMB2.0 Solutions &amp; Advanced View SMB Portal</t>
+          <t>Reliability and Characterization Modeling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Integrate Magellan with HP's SMB2.0 Solutions and Advanced View SMB portal for device and fleet management.</t>
+          <t>Conduct full reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F EOL (End of Life).</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Enables efficient management for target SMB customers, enhances product value.</t>
+          <t>Ensures robust system performance and supports warranty/service claims.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -705,17 +705,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['GXD', 'DVAR', 'R&amp;D Telemetry']</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Requires portal backend integration and device firmware support.</t>
+          <t>Test infrastructure, access to new components</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Portal recognizes, manages, and reports on Magellan devices in customer environments.</t>
+          <t>Comprehensive reliability and characterization reports completed and reviewed before launch.</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -736,17 +736,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PaaS (Platform as a Service) Support</t>
+          <t>Ink Stability Modeling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ensure Magellan supports HP's Platform as a Service (PaaS) offerings for flexible business models.</t>
+          <t>Model ink stability in the tank and assess impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Aligns with HP's strategic intent to accelerate PaaS and address evolving customer needs.</t>
+          <t>Ensures consistent print quality and prevents ink degradation over product life.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -756,25 +756,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['Marketing', 'BA', 'DVAR']</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Requires backend and firmware support for PaaS.</t>
+          <t>Ink/tank compatibility studies</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Magellan can be deployed and managed as part of HP’s PaaS portfolio; validated by IT and business team integration tests.</t>
+          <t>Ink stability model completed, with recommendations implemented if PQ risks are identified.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -787,45 +787,45 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PDL/PS Support and Speed Enhancement</t>
+          <t>NOA-F as Service Parts for Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>For PDL SKUs, support PDL/PS and achieve minimum print speeds of 25/20 ppm (improved from current 25/19).</t>
+          <t>Provide NOA-F as service parts to support in-warranty repairs and replacements.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Meets higher performance needs for certain SMB segments and maintains competitive positioning.</t>
+          <t>Improves serviceability and reduces downtime for end users.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Tech Reg']</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Requires hardware and firmware capable of supporting specified speeds and PDL/PS.</t>
+          <t>Parts supply chain, service documentation</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Independent lab validation of print speeds and PDL/PS functionality for PDL SKUs.</t>
+          <t>NOA-F service parts available in distribution and listed in service manuals.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -838,17 +838,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Angel Certification for PDL SKU</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Obtain Blue Angel environmental certification for PDL SKUs of Magellan.</t>
+          <t>Integrate Acumen 6 (traceability/serialization solution) onto the lid of the relevant component.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Addresses sustainability requirements and competitive differentiation in regulated markets.</t>
+          <t>Supports traceability for quality and warranty management.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -858,25 +858,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Prod Steward']</t>
+          <t>Quality Assurance, Service</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Requires compliance with Blue Angel standards and documentation submission.</t>
+          <t>Acumen 6 implementation, lid design</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Blue Angel certification awarded for PDL SKU.</t>
+          <t>Lid includes Acumen 6 traceability feature and is readable in manufacturing and service environments.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -889,17 +889,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Replaceable Maintenance Box</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Design Magellan with a user-replaceable maintenance box as a new feature for HP OJ Pro with Ink Tanks.</t>
+          <t>Modify existing SA14 production line for NOA-F and add Magi ink cartridge and labeling tool in Orcus 5.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs for SMB customers; new feature for this segment.</t>
+          <t>Ensures manufacturing readiness for new components and packaging.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'R&amp;D Telemetry']</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Depends on hardware design and supply chain for replacement parts.</t>
+          <t>Capex approval, line reconfiguration</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>User can replace the maintenance box without technical support; validated by usability testing.</t>
+          <t>SA14 and Orcus 5 lines modified and validated for new products before mass production.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -927,7 +927,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -940,17 +940,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan with AI</t>
+          <t>New Keyed Caps for Bottles</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Deliver advanced AI-powered print and scan features branded as 'Perfect Print' and 'Perfect Scan' for superior document quality and workflow automation.</t>
+          <t>Design and mold 1 to 4 new keyed caps for ink bottles to ensure correct installation and prevent cross-contamination.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Key differentiator and top customer need for productivity and efficiency.</t>
+          <t>Prevents user errors and maintains system reliability.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing', 'Quality']</t>
+          <t>R&amp;D, Manufacturing, Quality Assurance</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Requires AI software stack and hardware support.</t>
+          <t>Bottle design, mold tooling</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Independent testing confirms improved accuracy and efficiency in print/scan tasks versus baseline.</t>
+          <t>All new bottles use keyed caps, and installation errors are reduced to below defined threshold in validation testing.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -991,17 +991,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sustainability: 60% Recycled Content Plastic (RCP)</t>
+          <t>Support Customer-Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ensure Magellan is built with at least 60% recycled content plastic (RCP), exceeding main competitors.</t>
+          <t>Enable end users to replace PHA (Printhead Assembly) and NOA-F components without technician intervention.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Meets rising customer and regulatory demands for sustainability, and outperforms competitors (Epson 30%).</t>
+          <t>Improves serviceability, reduces downtime, and lowers service costs.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1011,25 +1011,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg']</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Supply chain and materials sourcing for recycled plastics.</t>
+          <t>Design for user access, documentation, packaging</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Third-party verification of RCP percentage in shipped units.</t>
+          <t>PHA and NOA-F replacement can be completed by users following instructions, with success rate above 95% in usability testing.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1042,45 +1042,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Warranty: 80k Pages or 2 Years</t>
+          <t>Warranty Page Life Goal of 80,000 Pages</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, for Magellan printers.</t>
+          <t>Set and validate a new warranty page life goal of 80,000 pages for the product.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Provides assurance to SMB customers and supports value proposition of reliability.</t>
+          <t>Aligns with new service and customer expectations for durability and value.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['Quality', 'Marketing']</t>
+          <t>Product Management, Service, End Users</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Requires alignment with service and support teams.</t>
+          <t>Component reliability, system testing</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Warranty policy published and supported in all launch markets.</t>
+          <t>Product passes life testing with at least 80,000 pages printed without major failures.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1093,45 +1093,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>Support for SKU 2 (Hi + Hi PDL) PaaS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing through the HP App for Magellan.</t>
+          <t>Enable support for SKU 2 (High + High PDL) as a Platform as a Service (PaaS) offering.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Supports flexible work environments and is a top customer expectation for SMBs.</t>
+          <t>Expands business model flexibility and addresses new customer segments.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing']</t>
+          <t>Business Development, Product Management</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Requires app compatibility and firmware support.</t>
+          <t>SKU definition, service platform integration</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Magellan is selectable and operational in HP App for mobile printing; confirmed by QA.</t>
+          <t>SKU 2 available for PaaS with defined service and support structure.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1144,17 +1144,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Telemetry Requirements</t>
+          <t>Size Increase for Tank and Input/Output Tray Alignment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Implement telemetry features to support device health monitoring, usage analytics, and proactive support.</t>
+          <t>Increase tank size and adjust input/output trays to align with tank protrusion and optimize overall size.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Enables better fleet management, support, and future product improvements.</t>
+          <t>Accommodates higher ink volumes and maintains ergonomic design.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Quality']</t>
+          <t>R&amp;D, Industrial Design, Manufacturing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Requires firmware and backend integration.</t>
+          <t>Tank and tray redesign, mechanical integration</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Telemetry data is collected, transmitted, and accessible in HP’s analytics platform; validated by test data.</t>
+          <t>Printer accommodates larger tank and trays are aligned, passing ergonomic and capacity validation.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1182,237 +1182,241 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 3, 12</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NGB Keyed Ink Bottles with Increased Yield</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles with 6K Black and 6K CMY page yield, and ensure CMY bottle sizes support &gt;8K page yield.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the printer control panel.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Higher yield bottles reduce frequency of replacement and lower total cost of ownership, supporting high-volume users and competitive positioning.</t>
+          <t>Improves user interface and accessibility for advanced features.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Display sourcing, firmware support</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4.3” CGD display fully functional and passes usability and reliability testing.</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Leverage Sayan Sibstar Tubes and New Tube Routing</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Use Sayan Sibstar tubes and implement new tube routing and integration for ink delivery.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ensures reliable ink flow and supports new tank design.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tube design, routing validation</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ink delivery system uses Sayan Sibstar tubes and meets flow/reliability targets.</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Update service station with aerosol management features and adapt spit platform due to tank changes.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Reduces maintenance needs and supports new tank configuration.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Service station redesign, aerosol capture validation</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Aerosol management system implemented and passes emissions/maintenance tests.</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model with New Weights</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased component weights.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ensures print quality and mechanical reliability with new system configuration.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>R&amp;D, Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Component weight data, modeling tools</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Updated models completed and reviewed, with no negative impact on print quality or reliability.</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Paper Path Supports Increased Page Life</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Redesign paper path to support increased page life target (80,000 pages).</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces paper jams over extended product use.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>R&amp;D, Product Management, End Users</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Bottle design, IDS system compatibility, ink formulation reuse</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>NGB bottles are available in 6K Black and 6K CMY, CMY bottle is available in a size supporting &gt;8K yield; bottles are keyed for correct installation.</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Spill-Free Ink Bottle Reliability</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ensure that the ink bottle and tank interface is spill-free during user installation and refilling.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Reduces mess, improves user satisfaction, and lowers support costs from spill-related incidents.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>R&amp;D, End Users, Service Teams</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Bottle and tank interface design, NOA-F integration</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>User testing confirms no ink spillage in &gt;99% of installations/refills under normal conditions.</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Integrate NOA-F (Next-Gen Output Assembly - Filter) with a metal-foiled labyrinth and a lid label into the product.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Improves reliability, ink flow management, and product differentiation.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>R&amp;D, Manufacturing, Service Teams</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>NOA-F component supply, manufacturing process update</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>NOA-F is present with specified labyrinth and lid label in all units; passes reliability and ink flow tests.</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Reuse the SuperAmp Si PHA and Magi/Nessie pigment inks without ink reformulation for the Magellan platform.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Reduces development time and leverages existing validated technology.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>R&amp;D, Product Management</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Compatibility verification with new system architecture</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks are used in the new product without reformulation; system passes all functional and reliability tests.</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Enhanced Reliability, WVTR, Air Gain, Flow Rate, and IDS Characterization</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Model and characterize reliability, Water Vapor Transmission Rate (WVTR), air gain, flow rate, and IDS (Ink Delivery System) for startup and NOA-F end-of-life (EOL).</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Ensures long-term performance and reliability of the ink delivery system.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>R&amp;D, Quality Assurance</t>
@@ -1420,12 +1424,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Access to test data, modeling resources</t>
+          <t>Paper path design, durability testing</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Complete documented models and test data for all specified parameters, reviewed and approved by QA.</t>
+          <t>Paper path passes life testing and supports 80,000-page warranty goal.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1436,47 +1440,47 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ink Stability Modeling (Tank and PQ Impact)</t>
+          <t>Ink Maintenance as Serviceable Part Post-80K Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Develop predictive models for ink stability in the tank and its impact on print quality (PQ).</t>
+          <t>Design ink maintenance as a serviceable part for replacement after 80,000-page life.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Prevents print quality issues and supports warranty commitments.</t>
+          <t>Supports extended product use and reduces total cost of ownership.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ink formulation data, tank design</t>
+          <t>Maintenance part design, service documentation</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Model accurately predicts ink stability and PQ outcomes over expected usage period.</t>
+          <t>Ink maintenance part can be replaced post-80K pages, with instructions provided.</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1487,27 +1491,27 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Support for Service Parts and Warranty for NOA-F</t>
+          <t>New IDS Make-Break and FI Connection</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NOA-F must be available as a service part and supported under warranty.</t>
+          <t>Implement new make-break and FI (Fluidic Interconnect) connection in IDS (Ink Delivery System), leveraging LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Enables field serviceability and supports warranty claims.</t>
+          <t>Improves system reliability, prevents leaks, and supports new bottle/tank design.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1517,99 +1521,99 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>R&amp;D, Manufacturing, Quality Assurance</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Spare part logistics, documentation</t>
+          <t>IDS design, LEBI ink-tank development</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NOA-F is available as a service part and covered under warranty per policy.</t>
+          <t>New IDS connections validated for reliability, leak-proofing, and compatibility with new tanks.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 technology on the ink bottle or tank lid.</t>
+          <t>Develop new IDS startup algorithm and air management system to improve reliability and ink flow.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Provides enhanced authentication or tracking for consumables.</t>
+          <t>Reduces startup failures and ensures consistent print quality.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Supplies Team</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Acumen 6 integration, lid design</t>
+          <t>Firmware development, IDS hardware</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Acumen 6 is present and functional on all lids; passes security and usability tests.</t>
+          <t>IDS startup passes all reliability and performance tests under defined conditions.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
+          <t>New Print Quality Goals and Depletion Definitions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Modify existing SA14 production line for NOA-F and add Magi ink cartridge and labeling tool in Orcus 5 line.</t>
+          <t>Define new print quality (PQ) goals and depletion metrics to align with revised page yield targets.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ensures manufacturing capability for new components and labeling requirements.</t>
+          <t>Ensures customer expectations are met for print performance and yield.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1619,17 +1623,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>Product Management, Quality Assurance</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Capex approval, line engineering</t>
+          <t>PQ testing, yield analysis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Production lines are modified, validated, and ready for volume manufacturing before launch.</t>
+          <t>PQ goals and depletion definitions documented and validated through testing.</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1640,282 +1644,282 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Design the product so that PHA (Printhead Assembly) and NOA-F are customer-replaceable parts.</t>
+          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in Magellan design.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Improves serviceability, reduces downtime, and lowers service costs.</t>
+          <t>Reduces development cost and leverages proven hardware.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Compatibility validation with new system</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>dASIC, aASIC, and PSU reused without modification and validated in system tests.</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module and Dune Firmware</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware for connectivity and device control.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ensures up-to-date wireless connectivity and firmware management.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>End Users, Product Management, IT</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Module sourcing, firmware integration</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Wi-Fi and firmware features validated in field and lab tests.</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Enhances device security and compliance with enterprise requirements.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>End Users, Service Teams, Product Management</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Design for serviceability, documentation</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>End users can replace PHA and NOA-F with basic instructions; validated by usability testing.</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Warranty Page Life Goal of 80K Pages</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Product must support a new warranty page life goal of 80,000 pages.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Improves value proposition and supports high-volume use cases.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Enterprise Customers, IT, Security</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>HW/FW integration, security certification</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Security features pass internal and external security audits.</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel eco-label requirements for PDL SKU.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Supports environmental goals and regulatory compliance for target markets.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Warranty, Product Management, End Users</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Component durability, consumable life</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Product reliably achieves 80,000 pages under normal use conditions; validated by endurance testing.</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SKU 2 (Hi + Hi PDL) PaaS</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Launch SKU 2 with high capacity and high PDL (Page Description Language) support as part of Printer as a Service (PaaS) offering.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Expands product offering to different customer segments and supports service-based business models.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Product Management, Regulatory, Marketing</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Design changes, documentation, certification process</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Product certified for EPEAT3, LOT4, Blue Angel prior to launch.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EPS Foam Packaging</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Use EPS foam packaging for product shipment and protection.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ensures safe transport and reduces damage during shipping.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Product Management, Sales, SMB/Enterprise Customers</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>SKU definition, PaaS platform integration</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>SKU 2 is available for order with PaaS, and supports high PDL as specified.</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Manufacturing, Logistics</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Packaging design, supplier sourcing</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>EPS foam packaging passes drop, vibration, and environmental tests.</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>0.85</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Reddington ID with Increased Tank Size</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Adopt Reddington industrial design (ID) with increased tank size; no change to Marconi-HI ADF.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Supports higher ink capacity and aligns with new bottle sizes.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Industrial Design, R&amp;D, Marketing</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Tank and chassis redesign, ID approval</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Product design is approved with increased tank size and Reddington ID; passes mechanical fit and finish tests.</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>EPS Foam Packaging</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Use EPS foam for product packaging.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Protects product during shipment and handling.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Packaging, Logistics, Operations</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Packaging design, drop test validation</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Product passes all standard packaging drop and vibration tests with EPS foam packaging.</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>0.9</v>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Certification for PDL SKU</t>
+          <t>Business Model and Solution Support</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ensure EPEAT3, LOT4, and Blue Angel environmental certifications for the PDL SKU.</t>
+          <t>Support multiple business models (Consumer, SMB, Enterprise) and solutions (Scan solution, SMB manageability, Enterprise support: WJA, HPSM, JAM).</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Meets regulatory and sustainability requirements for target markets.</t>
+          <t>Increases market reach and addresses diverse customer needs.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1925,17 +1929,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Marketing</t>
+          <t>Business Development, Product Management, IT</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Product design, certification process</t>
+          <t>Software integration, service platform support</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>PDL SKU is listed as certified for EPEAT3, LOT4, and Blue Angel before launch.</t>
+          <t>All business models and solutions supported and validated in pilot deployments.</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -1946,129 +1950,129 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Input/Output Tray Modifications for Tank Protrusion</t>
+          <t>Client and Driver Compatibility</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Modify input and output trays to accommodate tank protrusion and optimize product size.</t>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ensures mechanical compatibility and optimizes overall footprint.</t>
+          <t>Seamless integration into existing IT environments and support for all user types.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Industrial Design</t>
+          <t>End Users, IT, Product Management</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tray redesign, tank size finalization</t>
+          <t>Driver development, client validation</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Trays are compatible with tank protrusion and pass all functional and durability tests.</t>
+          <t>All listed clients and drivers fully functional with Magellan in system testing.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Schedule Adherence for S’27 Launch</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the control panel.</t>
+          <t>Adhere to defined schedule checkpoints for hardware, NOA-F, and bottle development, ensuring S’27 launch.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Enhances usability and supports advanced UI features.</t>
+          <t>Critical to meet market timing and revenue goals.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UI/UX, Product Management, End Users</t>
+          <t>Program Management, Product Management</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Display sourcing, UI development</t>
+          <t>All development activities, milestone tracking</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>All units include a 4.3” CGD, and UI is fully functional and validated.</t>
+          <t>All scheduled checkpoints met on time with required deliverables.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Four-Tube Platform Using Sayan Sibstar Tubes</t>
+          <t>SuperAmp PHA Life at 65K Constraint</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes with new routing and integration for a four-tube ink delivery platform.</t>
+          <t>Constrain SuperAmp PHA (Printhead Assembly) life to 65,000 pages for this program.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Supports increased ink flow and reliability for new tank and bottle sizes.</t>
+          <t>Defines service intervals and warranty coverage for key component.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2078,17 +2082,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Service, Quality Assurance, End Users</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tube sourcing, platform integration</t>
+          <t>PHA reliability testing, service documentation</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>System uses four Sayan Sibstar tubes with validated routing and integration.</t>
+          <t>SuperAmp PHA consistently meets or exceeds 65,000-page life in validation tests.</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2096,101 +2100,101 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Warranty Life of 2 Years or Page Life Goal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Update service station for improved aerosol management, considering spit platform changes due to new tank.</t>
+          <t>Optimize for a warranty life of 2 years or 80,000 pages, whichever comes first.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Reduces ink aerosol contamination and improves reliability.</t>
+          <t>Aligns warranty with market expectations and supports product positioning.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Product Management, Service, End Users</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>System reliability, warranty policy</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Product warranty is clearly stated and supported by reliability data.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Throughput Target of 25/20 PPM (PDL)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Optimize product for a throughput target of 25 pages per minute (ppm) for standard and 20 ppm for PDL (Page Description Language).</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Competitive performance in target segments.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>R&amp;D, Service Teams</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Service station redesign, aerosol test results</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Service station passes aerosol management tests with new tank configuration.</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Carriage Dynamic and Force Model Update</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Ensures print quality and mechanical reliability with new hardware configuration.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tube and tank design, mechanical modeling</t>
+          <t>Print engine capability, firmware tuning</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Validated dynamic and force models for carriage with new configuration.</t>
+          <t>Throughput validated at 25/20 ppm in standard and PDL modes in lab testing.</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2198,183 +2202,179 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>Serviceability of Maintenance Box</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased page life (80K pages).</t>
+          <t>Optimize design for easy serviceability of the maintenance box.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ensures reliable paper handling over product lifetime.</t>
+          <t>Reduces service costs and improves customer satisfaction.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Service, End Users</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Maintenance box design, documentation</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Maintenance box can be serviced/replaced in under defined time by users or technicians.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SMB Solution Support</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Support SMB (Small and Medium Business) solutions as part of the product offering.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Addresses needs of key market segment and increases adoption.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>R&amp;D, Quality Assurance</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Paper path design, endurance testing</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Paper path supports 80K page life without increased jam or wear rates.</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management, IT</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Solution integration, documentation</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SMB solutions available and validated with Magellan in pilot testing.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>0.9</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Serviceable Ink Maintenance Part (Post-80K Life)</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Designate an ink maintenance part as serviceable by service centers after 80K page life is reached.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Supports extended product use and post-warranty servicing.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PaaS Schedule Optimization</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Optimize schedule to support Platform as a Service (PaaS) offering for Magellan.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Aligns with business model evolution and customer demand.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Service Teams, End Users</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Part design, service documentation</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Ink maintenance part is replaceable by service centers and documented in service manuals.</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Business Development, Program Management</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>PaaS infrastructure, SKU readiness</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>PaaS offering available at launch, with schedule milestones met.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
         <v>0.85</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>New Make-Break and FI Connection for IDS</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Implement a new make-break and fluidic interconnect (FI) connection in the Ink Delivery System (IDS), leveraging LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Supports new bottle and tank architecture and enhances reliability.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>R&amp;D, Manufacturing</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>IDS redesign, LEBI ink-tank sourcing</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>IDS with new make-break and FI connection is fully integrated and validated for reliability.</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>0.9</v>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Develop a new startup algorithm for the IDS, including improved air management.</t>
+          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer to simplify business management for SMBs, both now and in the future.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Improves startup reliability and reduces air-related print defects.</t>
+          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI features differentiate HP in the market.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2384,30 +2384,30 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Algorithm development, IDS hardware</t>
+          <t>['SMB portal', 'AI solutions development']</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Startup process is robust, with air management validated by test prints and startup cycles.</t>
+          <t>AI features for productivity, scan workflow, and manageability are available and functional in the released product; validated with at least 3 SMB customer use cases.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2415,17 +2415,17 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definition</t>
+          <t>Lowest Business TCO for SMB Segment</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Define new print quality (PQ) goals and ink depletion criteria to align with updated page yield definitions.</t>
+          <t>Ensure Magellan delivers the lowest total cost of ownership (TCO) in HP's business printer lineup, specifically targeting SMB usage patterns.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ensures consistent quality and meets customer expectations for yield.</t>
+          <t>Cost efficiency is a key decision factor for SMBs and a major competitive differentiator.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2435,17 +2435,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Product Management</t>
+          <t>['Marketing', 'BA']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PQ test development, yield analysis</t>
+          <t>['Consumables pricing', 'Hardware cost structure']</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Documented PQ goals and depletion definitions are met in product validation tests.</t>
+          <t>Independent TCO analysis confirms Magellan has the lowest business TCO among HP SMB printers and is competitive with leading rivals.</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4, 11</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2466,50 +2466,50 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>High Serviceability and Customer Replaceable Components</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new platform.</t>
+          <t>Design Magellan with a warranty of 80k pages or 2 years (whichever comes first) and ensure critical components (e.g., PHA, maintenance box) are customer replaceable or easily serviced at a service center.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Reduces development cost and leverages proven hardware.</t>
+          <t>SMBs lack IT staff; reducing downtime and simplifying maintenance is critical.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>R&amp;D, Engineering</t>
+          <t>['Quality', 'Tech Reg', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Compatibility verification</t>
+          <t>['Component design', 'Service center readiness']</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>All reused components are fully compatible and pass functional validation.</t>
+          <t>Components such as PHA and maintenance box can be replaced by customer or at service center within 30 minutes; warranty terms are clearly documented.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2517,17 +2517,17 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>Keyed Bottles for Ink Refilling</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Integrate the Stingray Wi-Fi module for wireless connectivity.</t>
+          <t>Implement keyed bottles for ink refilling to prevent incorrect ink usage and improve user experience.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Provides robust wireless printing capabilities.</t>
+          <t>Reduces user error and service incidents, improving reliability and customer satisfaction.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2537,17 +2537,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>End Users, IT, Product Management</t>
+          <t>['Supplies Quality', 'Quality']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Module integration, firmware support</t>
+          <t>['Supplies design']</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi module is present in all units and passes wireless connectivity tests.</t>
+          <t>All ink bottles are uniquely keyed and only fit the correct tank; tested with 10+ end users for error prevention.</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2568,50 +2568,50 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dune Firmware Platform</t>
+          <t>Non-PDL and PDL SKU Feature Differentiation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Adopt Dune as the firmware platform for the Magellan printer.</t>
+          <t>Offer both Non-PDL and PDL SKUs with distinct features: Non-PDL supports SMB2.0 Solutions, Advanced View SMB portal, and PaaS; PDL SKU offers improved speed (25/20ppm), PDL/PS support, and Blue Angel certification.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Provides a consistent and up-to-date firmware environment.</t>
+          <t>Addresses varying SMB needs and regulatory requirements, supports broader market coverage.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Firmware, R&amp;D, Product Management</t>
+          <t>['Marketing', 'Tech Reg', 'DVAR']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Firmware adaptation, hardware compatibility</t>
+          <t>['Firmware development', 'Certification process']</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>All units run Dune firmware; passes all required functional and security tests.</t>
+          <t>Both SKUs available at launch with listed features; PDL SKU meets Blue Angel standards and speed targets.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2619,17 +2619,17 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security Platform (HW &amp; FW)</t>
+          <t>SMB Portal for Printer Management</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Integrate Gauss4.xx security platform for both hardware and firmware.</t>
+          <t>Develop a consolidated portal tailored for SMBs to manage multiple printers, monitor status, and access AI solutions for print, scan, and support.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Strengthens device and data security, meeting enterprise requirements.</t>
+          <t>Unmanaged/lightly managed SMBs need simple, centralized management to reduce IT overhead.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2639,30 +2639,30 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>IT, Enterprise Customers, Security, R&amp;D</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'Marketing']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HW/FW integration, security certification</t>
+          <t>['AI solutions', 'Portal development']</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Device passes all Gauss4.xx security validation tests and certifications.</t>
+          <t>Portal supports management of at least 15 printers per SMB, includes AI features, and is rated 'easy to use' by at least 80% of pilot users.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 7, 10</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2670,17 +2670,17 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>High Print Speed: 25/20 ppm (PDL: 25/19 ppm)</t>
+          <t>Perfect Print and Perfect Scan AI Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Achieve print speeds of 25/20 pages per minute (ppm), and 25/19 ppm for PDL.</t>
+          <t>Integrate 'Perfect Print' and 'Perfect Scan' AI-driven features for optimal print and scan quality, error detection, and workflow automation.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Supports productivity needs for SMB and enterprise markets.</t>
+          <t>Improves productivity and output quality, addresses top customer needs and pain points.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2690,30 +2690,30 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Marketing</t>
+          <t>['Marketing', 'R&amp;D Telemetry']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Engine design, firmware optimization</t>
+          <t>['AI solutions', 'Firmware integration']</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Product achieves specified print speeds in standard test conditions.</t>
+          <t>AI features reduce print/scan errors by 50% and improve workflow speed by 30% in SMB pilot tests.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 7, 11</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2721,50 +2721,50 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SMB and Enterprise Solution Integration</t>
+          <t>Sustainability: 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Integrate scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM) into the product.</t>
+          <t>Manufacture Magellan with at least 60% recycled content plastic, exceeding competitor benchmarks (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Expands market reach and supports business workflows.</t>
+          <t>Sustainability is a key differentiator and aligns with HP's environmental goals.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SMB/Enterprise Customers, Product Management, IT</t>
+          <t>['Prod Steward', 'Marketing']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Solution integration, driver support</t>
+          <t>['Supply chain sourcing', 'Manufacturing process']</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Product supports all listed solutions and passes integration testing.</t>
+          <t>Material composition verified by 3rd party audit; marketing claims substantiated.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2772,50 +2772,50 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Client and Driver Support: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+          <t>Maintenance-Free or Reduced Maintenance Design</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Support a comprehensive set of clients and drivers: HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
+          <t>Engineer Magellan for maintenance-free or significantly reduced maintenance over its operational life, with fewer parts to replace.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ensures broad compatibility and ease of deployment for various customer segments.</t>
+          <t>Reduces SMB operational burden and downtime; key customer pain point.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>End Users, IT, Product Management</t>
+          <t>['Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Driver development, OS compatibility</t>
+          <t>['Component reliability testing']</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>All listed drivers are available and validated for the product.</t>
+          <t>Printer requires 30% fewer maintenance interventions over 2 years compared to HP OJ Pro; validated in field trials.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2823,17 +2823,17 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages (Constraint)</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SuperAmp PHA must achieve a life of 65,000 pages as a hard constraint.</t>
+          <t>Support mobile printing and seamless integration with the HP App for setup, usage, and support.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Critical for reliability and warranty compliance.</t>
+          <t>SMBs increasingly require mobile workflows and easy setup for non-IT users.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2843,30 +2843,30 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Service, Warranty</t>
+          <t>['GXD', 'Marketing']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PHA design, reliability testing</t>
+          <t>['App development']</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SuperAmp PHA achieves 65K page life in accelerated life tests.</t>
+          <t>Printer is fully functional with HP App on iOS/Android; 95% of setup tasks can be completed via app.</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2874,50 +2874,50 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Warranty Life: 2 Years or Page Limit</t>
+          <t>PaaS (Platform as a Service) Support</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Provide a warranty for 2 years or the specified page limit, whichever comes first.</t>
+          <t>Magellan must support HP's PaaS offerings for SMBs, enabling service-based business models and future solution enhancements.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Aligns with market expectations and supports sales.</t>
+          <t>Aligns with HP's strategic goals for recurring revenue and solution monetization.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Warranty, Product Management, End Users</t>
+          <t>['BA', 'Marketing']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Component durability, service policy</t>
+          <t>['PaaS integration']</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Warranty terms are clearly stated and supported by product reliability data.</t>
+          <t>Printer is compatible with HP's SMB PaaS platform at launch; validated with 2 pilot customers.</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -2925,17 +2925,17 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Serviceability: Maintenance Box</t>
+          <t>Telemetry and Advanced Analytics</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Design for easy serviceability, including a replaceable maintenance box.</t>
+          <t>Include telemetry features to enable remote monitoring, diagnostics, and usage analytics for both HP and customers.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Reduces service time and cost, improves user experience.</t>
+          <t>Supports proactive support, product improvements, and customer manageability.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2945,17 +2945,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Service Teams, End Users</t>
+          <t>['R&amp;D Telemetry', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Maintenance box design, service documentation</t>
+          <t>['Portal integration']</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Maintenance box is easily replaceable and documented in user/service manuals.</t>
+          <t>Telemetry data is accessible via SMB portal and HP internal tools; at least 5 key metrics available.</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -2963,114 +2963,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Host 12K-CMYK (Flexible)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Optionally support 12K page yield for CMYK as a flexible goal.</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Provides future scalability for high-volume use cases.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Product Management, R&amp;D</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Ink formulation, tank capacity</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>12K-CMYK variant is available as an option and validated for yield.</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Trade Page 6K (Flexible)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Optionally offer a trade SKU with 6K page yield as a flexible goal.</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Enables market-specific or promotional offerings.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Marketing, Product Management</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>SKU definition, regional requirements</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>6K trade SKU is available and validated for yield.</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>37</t>
+          <t>12</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,61 +425,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Requirement ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -481,17 +493,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>NGB Keyed Bottles with Increased Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles with 6,000-page yield for black and CMY, and increased bottle size for CMY (&gt;8,000 pages).</t>
+          <t>Develop new generation bottles with keying features for 6K Black, 6K CMY page yield, and ensure CMY bottle size supports &gt;8K pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To meet market demand for higher capacity and reduce frequency of bottle replacement, supporting cost efficiency and user convenience.</t>
+          <t>Higher yield bottles reduce customer intervention and improve cost-per-page competitiveness.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,17 +513,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Supplies, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ink system compatibility, bottle design, supply chain adjustments</t>
+          <t>Bottle design, ink compatibility, printer firmware support</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bottles are available in both 6K (Black/CMY) and &gt;8K (CMY) capacities, function reliably with the printer, and pass yield and quality testing.</t>
+          <t>Bottles must pass keying validation, support &gt;8K CMY, and deliver specified page yields in standard test conditions.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -532,17 +544,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>Spill-Free Bottle Reliability</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure new ink bottles and refilling system are designed for spill-free operation during user handling and servicing.</t>
+          <t>The bottle and refill system must ensure spill-free operation during installation and use.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Spill-free operation improves user experience, reduces mess, and minimizes warranty claims due to ink spills.</t>
+          <t>Spill-free refilling is critical for user satisfaction and to reduce mess/complaints.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -552,17 +564,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, Service, R&amp;D</t>
+          <t>End Users, Customer Support</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle and ink tank interface design</t>
+          <t>Bottle and tank interface design</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Refilling process must pass defined spill-free reliability tests in lab and field trials.</t>
+          <t>Refill process must pass HP internal spill test procedures with zero ink spillage observed.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -588,12 +600,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Implement NOA-F (Next-Gen Output Assembly-Filter) with a metal foiled labyrinth and lid label, with no change to click-on push-push and TDF mechanism.</t>
+          <t>Implement NOA-F design with a metal foiled labyrinth and a lid label; no changes to click-on push-push and TDF.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Improved reliability and traceability for service and warranty support.</t>
+          <t>Enhanced NOA-F design for reliability and differentiation, while maintaining existing user interactions.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -603,17 +615,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Manufacturing</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOA-F component sourcing and assembly process</t>
+          <t>NOA-F part design, supplier capability</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F units must include metal foiled labyrinth and lid label, and maintain compatibility with existing push-push and TDF mechanisms.</t>
+          <t>NOA-F part must meet HP reliability standards and pass design reviews; user operation remains unchanged.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -634,17 +646,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without ink reformulation for Magellan.</t>
+          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces R&amp;D cost and time, ensures proven reliability and performance.</t>
+          <t>Reduces R&amp;D effort, leverages proven technology, and ensures supply chain continuity.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -654,21 +666,21 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>R&amp;D, Supply Chain, Manufacturing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility testing with new system components</t>
+          <t>Compatibility with new platform and bottle design</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks are validated for use in Magellan with no reformulation.</t>
+          <t>No ink reformulation required; performance verified in new product context.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -685,17 +697,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability and Characterization Modeling</t>
+          <t>Ink System Reliability and Characterization</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Conduct full reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F EOL (End of Life).</t>
+          <t>Model and validate reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, IDS, including startup and NOA-F end-of-life.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ensures robust system performance and supports warranty/service claims.</t>
+          <t>Ensures robust ink delivery and long-term reliability for the new system.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -705,17 +717,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Quality, Service</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Test infrastructure, access to new components</t>
+          <t>Ink system design, IDS development</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Comprehensive reliability and characterization reports completed and reviewed before launch.</t>
+          <t>All models and tests must meet HP reliability criteria over expected product life.</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -736,37 +748,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ink Stability Modeling</t>
+          <t>Support Services and Warranty Parts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Model ink stability in the tank and assess impact on print quality (PQ).</t>
+          <t>NOA-F must be available as a service part during warranty; support for services/contractual obligations.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ensures consistent print quality and prevents ink degradation over product life.</t>
+          <t>Ensures field serviceability and contractual compliance.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ink/tank compatibility studies</t>
+          <t>Parts supply chain, service documentation</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ink stability model completed, with recommendations implemented if PQ risks are identified.</t>
+          <t>NOA-F listed as a service part and available within warranty timeframes.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -787,41 +799,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts for Warranty Support</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provide NOA-F as service parts to support in-warranty repairs and replacements.</t>
+          <t>Modify existing SA14 line for NOA-F, add Magi ink cart and labeling tool in Orcus 5; support assembly of PHA, Dry FI, USG, push-push in printer factory.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces downtime for end users.</t>
+          <t>Enables production of new product variants with minimal investment.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parts supply chain, service documentation</t>
+          <t>Factory engineering, Capex approval</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F service parts available in distribution and listed in service manuals.</t>
+          <t>Factory lines modified and validated for new product builds before launch.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -838,41 +850,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 (traceability/serialization solution) onto the lid of the relevant component.</t>
+          <t>Design system so that customers can replace PHA and NOA-F themselves.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Supports traceability for quality and warranty management.</t>
+          <t>Reduces service costs and downtime, aligns with customer self-service trends.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Quality Assurance, Service</t>
+          <t>End Users, Service</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Acumen 6 implementation, lid design</t>
+          <t>Component design, user documentation</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lid includes Acumen 6 traceability feature and is readable in manufacturing and service environments.</t>
+          <t>Customer can replace PHA and NOA-F using standard tools and instructions; process validated by usability testing.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -889,17 +901,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+          <t>Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Modify existing SA14 production line for NOA-F and add Magi ink cartridge and labeling tool in Orcus 5.</t>
+          <t>Set and support a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ensures manufacturing readiness for new components and packaging.</t>
+          <t>Increases competitive positioning for high-use environments and reduces TCO.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -909,17 +921,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>Product Management, Marketing, End Users</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Capex approval, line reconfiguration</t>
+          <t>Component reliability, consumables yield</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SA14 and Orcus 5 lines modified and validated for new products before mass production.</t>
+          <t>Product must reliably print 80,000 pages without major service under standard use conditions.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -940,41 +952,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New Keyed Caps for Bottles</t>
+          <t>SKU 2 (Hi + Hi PDL) PaaS Enablement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design and mold 1 to 4 new keyed caps for ink bottles to ensure correct installation and prevent cross-contamination.</t>
+          <t>Enable SKU 2 with high throughput and PDL (Page Description Language) for PaaS (Print as a Service) business models.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Prevents user errors and maintains system reliability.</t>
+          <t>Supports flexible business models and meets enterprise/SMB needs.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Quality Assurance</t>
+          <t>Business, Channel Partners, IT</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bottle design, mold tooling</t>
+          <t>Firmware, service platform integration</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>All new bottles use keyed caps, and installation errors are reduced to below defined threshold in validation testing.</t>
+          <t>SKU 2 available for PaaS, with high throughput and PDL support validated.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -991,41 +1003,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Support Customer-Replaceable PHA and NOA-F</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Enable end users to replace PHA (Printhead Assembly) and NOA-F components without technician intervention.</t>
+          <t>Adopt Reddington ID with an increased tank size; no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Improves serviceability, reduces downtime, and lowers service costs.</t>
+          <t>Accommodates higher yield bottles and aligns with product family design.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>Design, Marketing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Design for user access, documentation, packaging</t>
+          <t>Industrial design, mechanical engineering</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PHA and NOA-F replacement can be completed by users following instructions, with success rate above 95% in usability testing.</t>
+          <t>Tank size increased and validated for new bottle compatibility; ID matches Reddington.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1042,17 +1054,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80,000 Pages</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Set and validate a new warranty page life goal of 80,000 pages for the product.</t>
+          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel requirements for environmental standards (PDL SKU).</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aligns with new service and customer expectations for durability and value.</t>
+          <t>Mandatory for regulatory compliance and market access.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1062,21 +1074,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>Regulatory, Marketing, Sustainability</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Component reliability, system testing</t>
+          <t>Design, materials sourcing</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Product passes life testing with at least 80,000 pages printed without major failures.</t>
+          <t>Product passes certification for EPEAT3, LOT4, and Blue Angel before launch.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1093,17 +1105,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Support for SKU 2 (Hi + Hi PDL) PaaS</t>
+          <t>Input/Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Enable support for SKU 2 (High + High PDL) as a Platform as a Service (PaaS) offering.</t>
+          <t>Redesign input and output trays to accommodate increased tank protrusion and optimize size.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Expands business model flexibility and addresses new customer segments.</t>
+          <t>Ensures proper paper handling and maintains compact footprint.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1113,17 +1125,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Business Development, Product Management</t>
+          <t>Design, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SKU definition, service platform integration</t>
+          <t>Mechanical design, tray component sourcing</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SKU 2 available for PaaS with defined service and support structure.</t>
+          <t>Trays fit with new tank size; paper handling performance unchanged or improved.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1144,17 +1156,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Size Increase for Tank and Input/Output Tray Alignment</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Increase tank size and adjust input/output trays to align with tank protrusion and optimize overall size.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) for user interface.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Accommodates higher ink volumes and maintains ergonomic design.</t>
+          <t>Improves user experience and aligns with modern UI expectations.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1164,21 +1176,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R&amp;D, Industrial Design, Manufacturing</t>
+          <t>End Users, Marketing, UI/UX</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tank and tray redesign, mechanical integration</t>
+          <t>Display sourcing, firmware UI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Printer accommodates larger tank and trays are aligned, passing ergonomic and capacity validation.</t>
+          <t>Product includes 4.3” CGD and passes usability testing.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1195,17 +1207,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the printer control panel.</t>
+          <t>Update service station for improved aerosol management due to tank changes.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Improves user interface and accessibility for advanced features.</t>
+          <t>Prevents contamination and ensures print quality.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1215,21 +1227,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Display sourcing, firmware support</t>
+          <t>Service station design, tank integration</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.3” CGD display fully functional and passes usability and reliability testing.</t>
+          <t>Aerosol containment validated in lab and field tests.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1246,17 +1258,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar Tubes and New Tube Routing</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Use Sayan Sibstar tubes and implement new tube routing and integration for ink delivery.</t>
+          <t>Update carriage dynamics and force models to account for new tube routing and increased component weights.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ensures reliable ink flow and supports new tank design.</t>
+          <t>Ensures reliable printhead movement and system durability.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1266,17 +1278,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Reliability Engineering</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tube design, routing validation</t>
+          <t>Mechanical engineering, simulation</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Ink delivery system uses Sayan Sibstar tubes and meets flow/reliability targets.</t>
+          <t>Carriage system passes HP reliability and performance tests with new configuration.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1297,41 +1309,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Paper Path Upgrade for Increased Page Life</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Update service station with aerosol management features and adapt spit platform due to tank changes.</t>
+          <t>Upgrade paper path to support increased page life (80k pages).</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Reduces maintenance needs and supports new tank configuration.</t>
+          <t>Reduces wear and maintains print quality over extended use.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>R&amp;D, End Users, Service</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Service station redesign, aerosol capture validation</t>
+          <t>Paper path component selection, reliability testing</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Aerosol management system implemented and passes emissions/maintenance tests.</t>
+          <t>Paper path components meet durability targets in accelerated life testing.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1348,17 +1360,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model with New Weights</t>
+          <t>Ink Maintenance as Serviceable Part</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased component weights.</t>
+          <t>Make ink maintenance a serviceable part at service centers, especially post 80k page life.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ensures print quality and mechanical reliability with new system configuration.</t>
+          <t>Improves serviceability and extends product life.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1368,21 +1380,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Component weight data, modeling tools</t>
+          <t>Part design, service training</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Updated models completed and reviewed, with no negative impact on print quality or reliability.</t>
+          <t>Ink maintenance part available and replaceable at service centers post 80k pages.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1399,17 +1411,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Paper Path Supports Increased Page Life</t>
+          <t>New IDS Make-Break and FI Connection</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased page life target (80,000 pages).</t>
+          <t>Implement new IDS make-break and fluidic interconnect (FI) connection, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ensures reliability and reduces paper jams over extended product use.</t>
+          <t>Improves reliability and security of ink delivery system.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1419,21 +1431,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Supplies</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Paper path design, durability testing</t>
+          <t>IDS design, firmware</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paper path passes life testing and supports 80,000-page warranty goal.</t>
+          <t>IDS connection passes reliability and security validation.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1450,37 +1462,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part Post-80K Life</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part for replacement after 80,000-page life.</t>
+          <t>Develop new IDS startup algorithm and air management system.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Supports extended product use and reduces total cost of ownership.</t>
+          <t>Ensures consistent print quality and reliable startup.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>Firmware, R&amp;D</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Maintenance part design, service documentation</t>
+          <t>IDS hardware, firmware development</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ink maintenance part can be replaced post-80K pages, with instructions provided.</t>
+          <t>Startup and air management validated in field and lab tests.</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1501,17 +1513,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New IDS Make-Break and FI Connection</t>
+          <t>New PQ Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Implement new make-break and FI (Fluidic Interconnect) connection in IDS (Ink Delivery System), leveraging LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
+          <t>Set new print quality (PQ) goals and deplete-to-empty definition to align with page yield targets.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Improves system reliability, prevents leaks, and supports new bottle/tank design.</t>
+          <t>Ensures customer expectations are met for print quality and yield.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1521,21 +1533,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Quality Assurance</t>
+          <t>R&amp;D, Quality, Marketing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>IDS design, LEBI ink-tank development</t>
+          <t>Print quality testing, yield analysis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>New IDS connections validated for reliability, leak-proofing, and compatibility with new tanks.</t>
+          <t>PQ and depletion metrics defined and validated in test prints.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1552,41 +1564,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Reuse of Marconi Hi PDL and Tux dASIC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Develop new IDS startup algorithm and air management system to improve reliability and ink flow.</t>
+          <t>Reuse Marconi Hi PDL, Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in new platform.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Reduces startup failures and ensures consistent print quality.</t>
+          <t>Reduces development cost and leverages proven components.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Firmware development, IDS hardware</t>
+          <t>Compatibility validation</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>IDS startup passes all reliability and performance tests under defined conditions.</t>
+          <t>Components function as required in new product context.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1603,41 +1615,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definitions</t>
+          <t>Stingray Wi-Fi Module and Dune Firmware</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Define new print quality (PQ) goals and depletion metrics to align with revised page yield targets.</t>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ensures customer expectations are met for print performance and yield.</t>
+          <t>Meets modern connectivity expectations and supports HP ecosystem.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Product Management, Quality Assurance</t>
+          <t>End Users, IT, R&amp;D</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>PQ testing, yield analysis</t>
+          <t>Module sourcing, firmware integration</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PQ goals and depletion definitions documented and validated through testing.</t>
+          <t>Wireless connectivity passes HP standard performance and security tests.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1654,41 +1666,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in Magellan design.</t>
+          <t>Implement Gauss4.xx hardware and firmware security features.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Reduces development cost and leverages proven hardware.</t>
+          <t>Protects against modern security threats and meets enterprise requirements.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>IT, Enterprise Customers, Security Team</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Compatibility validation with new system</t>
+          <t>Firmware, hardware integration</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>dASIC, aASIC, and PSU reused without modification and validated in system tests.</t>
+          <t>Security features validated against HP security standards.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1705,41 +1717,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module and Dune Firmware</t>
+          <t>Support for Multiple Business Models and Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware for connectivity and device control.</t>
+          <t>Enable support for Consumer, SMB, and Enterprise business models, including PaaS, WorkFromHome/Flexworker, onboarding/S&amp;O paths, scan solutions, SMB manageability, and Enterprise support (WJA, HPSM, JAM).</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ensures up-to-date wireless connectivity and firmware management.</t>
+          <t>Expands market reach and meets diverse customer needs.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>End Users, Product Management, IT</t>
+          <t>Business, Channel Partners, End Users</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Module sourcing, firmware integration</t>
+          <t>Solution integration, firmware, services</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Wi-Fi and firmware features validated in field and lab tests.</t>
+          <t>All listed business models and solutions supported and validated in launch readiness review.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1756,17 +1768,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Clients &amp; Drivers Compatibility</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Enhances device security and compliance with enterprise requirements.</t>
+          <t>Ensures seamless deployment and management in various environments.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1776,17 +1788,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Enterprise Customers, IT, Security</t>
+          <t>IT, End Users, Channel Partners</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HW/FW integration, security certification</t>
+          <t>Driver development, OS compatibility</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Security features pass internal and external security audits.</t>
+          <t>All clients and drivers validated on supported platforms.</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1807,17 +1819,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
+          <t>Speed: 25/20ppm (PDL: 25/19ppm)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel eco-label requirements for PDL SKU.</t>
+          <t>Achieve print speeds of 25/20 ppm (pages per minute), and 25/19 ppm for PDL SKU.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Supports environmental goals and regulatory compliance for target markets.</t>
+          <t>Meets market expectations for performance.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1827,17 +1839,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Product Management, Regulatory, Marketing</t>
+          <t>Product Management, End Users</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Design changes, documentation, certification process</t>
+          <t>Engine design, firmware optimization</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Product certified for EPEAT3, LOT4, Blue Angel prior to launch.</t>
+          <t>Print speed validated in standard HP performance tests.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1858,45 +1870,45 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>SuperAmp PHA Life at 65K Pages</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Use EPS foam packaging for product shipment and protection.</t>
+          <t>Ensure SuperAmp PHA supports a minimum life of 65,000 pages.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ensures safe transport and reduces damage during shipping.</t>
+          <t>Critical for reliability and cost of ownership.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manufacturing, Logistics</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Packaging design, supplier sourcing</t>
+          <t>PHA design, reliability testing</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>EPS foam packaging passes drop, vibration, and environmental tests.</t>
+          <t>SuperAmp PHA passes life testing for 65,000 pages.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -1909,45 +1921,45 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Business Model and Solution Support</t>
+          <t>Warranty Life: 2 Years or Page Limit</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Support multiple business models (Consumer, SMB, Enterprise) and solutions (Scan solution, SMB manageability, Enterprise support: WJA, HPSM, JAM).</t>
+          <t>Provide a warranty of 2 years or up to defined page life, whichever comes first.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Increases market reach and addresses diverse customer needs.</t>
+          <t>Aligns with market standards and customer expectations.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Business Development, Product Management, IT</t>
+          <t>Product Management, Service</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Software integration, service platform support</t>
+          <t>Reliability targets, legal requirements</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>All business models and solutions supported and validated in pilot deployments.</t>
+          <t>Warranty terms published and supported in all launch regions.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -1960,45 +1972,45 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Client and Driver Compatibility</t>
+          <t>Serviceability: Maintenance Box</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>Include a maintenance box as a serviceable component to improve serviceability.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Seamless integration into existing IT environments and support for all user types.</t>
+          <t>Reduces downtime and simplifies maintenance.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>End Users, IT, Product Management</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Driver development, client validation</t>
+          <t>Component design, service documentation</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>All listed clients and drivers fully functional with Magellan in system testing.</t>
+          <t>Maintenance box is field-replaceable and validated in service tests.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2011,139 +2023,135 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Schedule Adherence for S’27 Launch</t>
+          <t>Host 12K-CMYK and Trade Page 6K</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Adhere to defined schedule checkpoints for hardware, NOA-F, and bottle development, ensuring S’27 launch.</t>
+          <t>Support host-based 12K-CMYK and trade page 6K options as flexible priorities.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Critical to meet market timing and revenue goals.</t>
+          <t>Provides options for different markets and customer segments.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Product Management, Channel Partners</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Firmware, SKU configuration</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK and trade 6K SKUs available for order and validated.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI-powered productivity, scan workflow, and manageability solutions into the Magellan printer to streamline business operations for SMBs.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SMBs need easy-to-use, efficient tools to manage printing workflows without dedicated IT staff.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Program Management, Product Management</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>All development activities, milestone tracking</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>All scheduled checkpoints met on time with required deliverables.</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Requires integration with SMB portal and AI solution infrastructure.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>AI features for productivity, scanning, and device management are available and functional for SMB users. Usability validated by non-IT office managers.</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>0.95</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>SuperAmp PHA Life at 65K Constraint</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Constrain SuperAmp PHA (Printhead Assembly) life to 65,000 pages for this program.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Defines service intervals and warranty coverage for key component.</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Design Magellan to deliver the lowest TCO in HP's business printer lineup, minimizing intervention and maximizing efficiency.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Cost efficiency is a top purchasing driver for SMBs with limited budgets.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Service, Quality Assurance, End Users</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>PHA reliability testing, service documentation</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>SuperAmp PHA consistently meets or exceeds 65,000-page life in validation tests.</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Warranty Life of 2 Years or Page Life Goal</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Optimize for a warranty life of 2 years or 80,000 pages, whichever comes first.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Aligns warranty with market expectations and supports product positioning.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Product Management, Service, End Users</t>
+          <t>['Marketing', 'BA']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>System reliability, warranty policy</t>
+          <t>Depends on consumable pricing, maintenance model, and supply chain management.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Product warranty is clearly stated and supported by reliability data.</t>
+          <t>Independent cost analysis shows Magellan has the lowest TCO compared to other HP business printers.</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2151,50 +2159,50 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, 11</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Throughput Target of 25/20 PPM (PDL)</t>
+          <t>Customer-Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Optimize product for a throughput target of 25 pages per minute (ppm) for standard and 20 ppm for PDL (Page Description Language).</t>
+          <t>Implement a replaceable maintenance box that allows end users to perform maintenance without service technician intervention.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Competitive performance in target segments.</t>
+          <t>Reduces downtime and service costs for SMBs lacking IT support.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D</t>
+          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Print engine capability, firmware tuning</t>
+          <t>Requires design changes and supply of maintenance kits.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Throughput validated at 25/20 ppm in standard and PDL modes in lab testing.</t>
+          <t>End users can replace the maintenance box following provided instructions; validated by usability testing.</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2202,50 +2210,50 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Serviceability of Maintenance Box</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Optimize design for easy serviceability of the maintenance box.</t>
+          <t>Ensure the printer is manufactured with at least 60% recycled content plastic, surpassing key competitors in sustainability.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Reduces service costs and improves customer satisfaction.</t>
+          <t>Environmental responsibility is a growing requirement for businesses and offers a competitive advantage.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>['Prod Steward', 'Marketing']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Maintenance box design, documentation</t>
+          <t>Material sourcing and manufacturing process changes.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Maintenance box can be serviced/replaced in under defined time by users or technicians.</t>
+          <t>Bill of materials and certification confirm 60% RCP in final product.</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2253,30 +2261,30 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SMB Solution Support</t>
+          <t>SMB Portal for Device Management</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Support SMB (Small and Medium Business) solutions as part of the product offering.</t>
+          <t>Develop a consolidated portal (SMB portal) for managing multiple printers, targeting unmanaged or lightly managed SMBs.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Addresses needs of key market segment and increases adoption.</t>
+          <t>Enables easy device management for offices without IT staff.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2286,17 +2294,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SMB Customers, Product Management, IT</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Solution integration, documentation</t>
+          <t>Requires software development and integration with printer firmware.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SMB solutions available and validated with Magellan in pilot testing.</t>
+          <t>Portal enables registration, monitoring, and management of all Magellan devices in an office environment.</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2304,30 +2312,30 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>Magellan MRD, Page 7, 10</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PaaS Schedule Optimization</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Optimize schedule to support Platform as a Service (PaaS) offering for Magellan.</t>
+          <t>Enable seamless mobile printing via HP App, supporting modern work environments and BYOD scenarios.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Aligns with business model evolution and customer demand.</t>
+          <t>Mobile device usage is prevalent in SMBs; enables flexibility and convenience.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2337,17 +2345,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Business Development, Program Management</t>
+          <t>['Marketing', 'GXD']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PaaS infrastructure, SKU readiness</t>
+          <t>Requires app and firmware updates.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>PaaS offering available at launch, with schedule milestones met.</t>
+          <t>Users can print from mobile devices using the HP App with no additional setup.</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2355,59 +2363,63 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>Magellan MRD, Page 9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>Warranty: 80,000 Pages or 2 Years</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability solutions into the Magellan printer to simplify business management for SMBs, both now and in the future.</t>
+          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB expectations.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SMBs require easy-to-use, efficient solutions due to lack of dedicated IT staff. AI features differentiate HP in the market.</t>
+          <t>SMBs seek reliability and predictable service costs.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['Quality', 'BA']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>['SMB portal', 'AI solutions development']</t>
+          <t>Support and service readiness.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>AI features for productivity, scan workflow, and manageability are available and functional in the released product; validated with at least 3 SMB customer use cases.</t>
+          <t>Warranty terms are published and honored in all launch markets.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2415,50 +2427,50 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lowest Business TCO for SMB Segment</t>
+          <t>Keyed Bottles for Supplies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ensure Magellan delivers the lowest total cost of ownership (TCO) in HP's business printer lineup, specifically targeting SMB usage patterns.</t>
+          <t>Use keyed bottles for ink supplies to prevent errors and ensure only compatible supplies are used.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cost efficiency is a key decision factor for SMBs and a major competitive differentiator.</t>
+          <t>Reduces risk of incorrect refilling and ensures product reliability.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['Marketing', 'BA']</t>
+          <t>['Supplies Quality', 'Quality']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>['Consumables pricing', 'Hardware cost structure']</t>
+          <t>Supply chain and packaging changes.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Independent TCO analysis confirms Magellan has the lowest business TCO among HP SMB printers and is competitive with leading rivals.</t>
+          <t>All supply bottles are uniquely keyed and cannot be misused with other products.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2466,41 +2478,41 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>High Serviceability and Customer Replaceable Components</t>
+          <t>Serviceability: PHA and MINK</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Design Magellan with a warranty of 80k pages or 2 years (whichever comes first) and ensure critical components (e.g., PHA, maintenance box) are customer replaceable or easily serviced at a service center.</t>
+          <t>Design for serviceability: customer replaceable parts (PHA) and MINK at service center, with threshold target for customer replaceable items.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SMBs lack IT staff; reducing downtime and simplifying maintenance is critical.</t>
+          <t>Minimizes downtime and reduces service costs for SMBs.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['Quality', 'Tech Reg', 'Prod Steward']</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>['Component design', 'Service center readiness']</t>
+          <t>Design and documentation of replaceable/serviceable parts.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Components such as PHA and maintenance box can be replaced by customer or at service center within 30 minutes; warranty terms are clearly documented.</t>
+          <t>Parts designated as customer-replaceable are documented and validated via service manuals.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2509,7 +2521,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2517,17 +2529,17 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Refilling</t>
+          <t>PDL SKU Performance and Features</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Implement keyed bottles for ink refilling to prevent incorrect ink usage and improve user experience.</t>
+          <t>PDL SKU to support print speeds of 25/20 ppm (improvement from current 25/19), PDL/PS support, and Blue Angel certification.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Reduces user error and service incidents, improving reliability and customer satisfaction.</t>
+          <t>Meets higher performance and environmental standards required in certain markets.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2537,21 +2549,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Quality']</t>
+          <t>['Tech Reg', 'Quality']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>['Supplies design']</t>
+          <t>Firmware and hardware updates, certification testing.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>All ink bottles are uniquely keyed and only fit the correct tank; tested with 10+ end users for error prevention.</t>
+          <t>PDL SKU achieves targeted print speeds, supports PDL/PS, and is Blue Angel certified.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2560,7 +2572,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2568,41 +2580,41 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Non-PDL and PDL SKU Feature Differentiation</t>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View Portal</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Offer both Non-PDL and PDL SKUs with distinct features: Non-PDL supports SMB2.0 Solutions, Advanced View SMB portal, and PaaS; PDL SKU offers improved speed (25/20ppm), PDL/PS support, and Blue Angel certification.</t>
+          <t>Non-PDL SKU to support SMB2.0 solutions and Advanced View SMB portal, as well as Platform-as-a-Service (PaaS) support.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Addresses varying SMB needs and regulatory requirements, supports broader market coverage.</t>
+          <t>Enables differentiated feature sets for different market segments and supports new business models.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['Marketing', 'Tech Reg', 'DVAR']</t>
+          <t>['Marketing', 'BA', 'GXD']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>['Firmware development', 'Certification process']</t>
+          <t>Software and service integration.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Both SKUs available at launch with listed features; PDL SKU meets Blue Angel standards and speed targets.</t>
+          <t>Non-PDL SKU is shipped with SMB2.0 solutions and Advanced View Portal enabled, and supports PaaS.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2611,7 +2623,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -2619,17 +2631,17 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>Perfect Print and Perfect Scan AI Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Develop a consolidated portal tailored for SMBs to manage multiple printers, monitor status, and access AI solutions for print, scan, and support.</t>
+          <t>Integrate 'Perfect Print' and 'Perfect Scan' AI solutions to optimize print and scan quality automatically.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Unmanaged/lightly managed SMBs need simple, centralized management to reduce IT overhead.</t>
+          <t>Delivers superior user experience and reduces manual intervention for quality issues.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2639,30 +2651,30 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'Marketing']</t>
+          <t>['GXD', 'R&amp;D Telemetry']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>['AI solutions', 'Portal development']</t>
+          <t>Requires AI software development and integration with printer hardware.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Portal supports management of at least 15 printers per SMB, includes AI features, and is rated 'easy to use' by at least 80% of pilot users.</t>
+          <t>Print and scan outputs are optimized automatically and validated in user testing.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10</t>
+          <t>Magellan MRD, Page 7, 11</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -2670,305 +2682,50 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
+          <t>Telemetry Requirements</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Integrate 'Perfect Print' and 'Perfect Scan' AI-driven features for optimal print and scan quality, error detection, and workflow automation.</t>
+          <t>Implement telemetry to collect usage, performance, and diagnostic data, supporting proactive support and product improvement.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Improves productivity and output quality, addresses top customer needs and pain points.</t>
+          <t>Enables data-driven support, remote diagnostics, and continuous improvement.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['Marketing', 'R&amp;D Telemetry']</t>
+          <t>['R&amp;D Telemetry', 'Quality']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>['AI solutions', 'Firmware integration']</t>
+          <t>Data privacy compliance, backend infrastructure.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>AI features reduce print/scan errors by 50% and improve workflow speed by 30% in SMB pilot tests.</t>
+          <t>Telemetry data is collected, transmitted securely, and used for product insights; compliant with data privacy regulations.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Sustainability: 60% Recycled Content Plastic (RCP)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Manufacture Magellan with at least 60% recycled content plastic, exceeding competitor benchmarks (Epson 30%, Canon TBC).</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Sustainability is a key differentiator and aligns with HP's environmental goals.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>['Prod Steward', 'Marketing']</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>['Supply chain sourcing', 'Manufacturing process']</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Material composition verified by 3rd party audit; marketing claims substantiated.</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Maintenance-Free or Reduced Maintenance Design</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Engineer Magellan for maintenance-free or significantly reduced maintenance over its operational life, with fewer parts to replace.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Reduces SMB operational burden and downtime; key customer pain point.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>['Quality', 'Prod Steward']</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>['Component reliability testing']</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Printer requires 30% fewer maintenance interventions over 2 years compared to HP OJ Pro; validated in field trials.</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Mobile Printing and HP App Integration</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Support mobile printing and seamless integration with the HP App for setup, usage, and support.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SMBs increasingly require mobile workflows and easy setup for non-IT users.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>['GXD', 'Marketing']</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>['App development']</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Printer is fully functional with HP App on iOS/Android; 95% of setup tasks can be completed via app.</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>PaaS (Platform as a Service) Support</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Magellan must support HP's PaaS offerings for SMBs, enabling service-based business models and future solution enhancements.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Aligns with HP's strategic goals for recurring revenue and solution monetization.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>['BA', 'Marketing']</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>['PaaS integration']</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Printer is compatible with HP's SMB PaaS platform at launch; validated with 2 pilot customers.</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Telemetry and Advanced Analytics</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Include telemetry features to enable remote monitoring, diagnostics, and usage analytics for both HP and customers.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Supports proactive support, product improvements, and customer manageability.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>['R&amp;D Telemetry', 'Tech Reg']</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>['Portal integration']</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Telemetry data is accessible via SMB portal and HP internal tools; at least 5 key metrics available.</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 3, 12</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
     </row>

--- a/consolidation/output/consolidated_requirements.xlsx
+++ b/consolidation/output/consolidated_requirements.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,61 +413,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Requirement ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -493,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with Increased Yield</t>
+          <t>NGB Keyed Bottles with High Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new generation bottles with keying features for 6K Black, 6K CMY page yield, and ensure CMY bottle size supports &gt;8K pages.</t>
+          <t>Develop new NGB keyed bottles supporting 6,000-page yield for black and CMY, with CMY bottle size &gt;8,000 pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Higher yield bottles reduce customer intervention and improve cost-per-page competitiveness.</t>
+          <t>Increases ink capacity and reduces customer intervention, aligning with competitive CISS offerings.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -513,17 +501,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Supplies, End Users</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bottle design, ink compatibility, printer firmware support</t>
+          <t>Requires new bottle design and compatibility with existing system.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bottles must pass keying validation, support &gt;8K CMY, and deliver specified page yields in standard test conditions.</t>
+          <t>Bottles must deliver specified page yields in standard ISO tests; must be keyed to prevent incorrect insertion.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -544,17 +532,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Bottle Reliability</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The bottle and refill system must ensure spill-free operation during installation and use.</t>
+          <t>Ensure the new NGB bottles provide spill-free operation during installation and use.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Spill-free refilling is critical for user satisfaction and to reduce mess/complaints.</t>
+          <t>Enhances user experience and reduces service costs related to ink spills.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -564,21 +552,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, Customer Support</t>
+          <t>End Users, Service, R&amp;D</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle and tank interface design</t>
+          <t>Bottle and tank interface design.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Refill process must pass HP internal spill test procedures with zero ink spillage observed.</t>
+          <t>No ink spill observed in 100% of installation tests under normal conditions.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -600,12 +588,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Implement NOA-F design with a metal foiled labyrinth and a lid label; no changes to click-on push-push and TDF.</t>
+          <t>Integrate NOA-F component with a metal foiled labyrinth and lid label for improved performance.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enhanced NOA-F design for reliability and differentiation, while maintaining existing user interactions.</t>
+          <t>Improves reliability and traceability of the NOA-F component.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -615,21 +603,21 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOA-F part design, supplier capability</t>
+          <t>Design integration with NOA-F and labeling process.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F part must meet HP reliability standards and pass design reviews; user operation remains unchanged.</t>
+          <t>All NOA-F units include metal foiled labyrinth and lid label as verified in quality audits.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -646,17 +634,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>Support for Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
+          <t>Enable end customers to replace PHA and NOA-F components themselves.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces R&amp;D effort, leverages proven technology, and ensures supply chain continuity.</t>
+          <t>Reduces service costs and downtime for customers, improving satisfaction.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -666,17 +654,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Manufacturing</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility with new platform and bottle design</t>
+          <t>Component design for tool-less replacement and user instructions.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>No ink reformulation required; performance verified in new product context.</t>
+          <t>Customers can replace PHA and NOA-F without tools within 5 minutes following provided instructions.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -697,17 +685,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ink System Reliability and Characterization</t>
+          <t>Warranty Page Life Goal of 80,000 Pages</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Model and validate reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, IDS, including startup and NOA-F end-of-life.</t>
+          <t>Set and support a new warranty page life goal of 80,000 pages for the printer.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ensures robust ink delivery and long-term reliability for the new system.</t>
+          <t>Enhances product value and aligns with new competitive benchmarks.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -717,21 +705,21 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Service</t>
+          <t>Product Management, End Users, Warranty</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ink system design, IDS development</t>
+          <t>Component durability, ink system reliability.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>All models and tests must meet HP reliability criteria over expected product life.</t>
+          <t>Device must operate without major failure for 80,000 pages under standard usage conditions.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -748,37 +736,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Support Services and Warranty Parts</t>
+          <t>Product ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NOA-F must be available as a service part during warranty; support for services/contractual obligations.</t>
+          <t>Increase the tank size for the Reddington ID product variant, ensuring no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ensures field serviceability and contractual compliance.</t>
+          <t>Supports higher ink capacity and longer use between refills.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>Product Management, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parts supply chain, service documentation</t>
+          <t>Mechanical design changes, packaging.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NOA-F listed as a service part and available within warranty timeframes.</t>
+          <t>Tank size increased as per specifications; no interference with ADF operation.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -799,41 +787,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Modify existing SA14 line for NOA-F, add Magi ink cart and labeling tool in Orcus 5; support assembly of PHA, Dry FI, USG, push-push in printer factory.</t>
+          <t>Ensure the PDL SKU meets EPEAT3, LOT4, and Blue Angel environmental requirements.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enables production of new product variants with minimal investment.</t>
+          <t>Mandatory for market access and sustainability goals.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>Regulatory, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Factory engineering, Capex approval</t>
+          <t>Design and materials selection, certification process.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Factory lines modified and validated for new product builds before launch.</t>
+          <t>Product passes all required certifications prior to launch.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -850,41 +838,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Input and Output Tray Redesign for Tank Protrusion</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Design system so that customers can replace PHA and NOA-F themselves.</t>
+          <t>Modify input and output trays to accommodate the increased tank protrusion due to larger ink tanks.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Reduces service costs and downtime, aligns with customer self-service trends.</t>
+          <t>Ensures mechanical compatibility and user convenience.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>End Users, Service</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Component design, user documentation</t>
+          <t>Mechanical and industrial design changes.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Customer can replace PHA and NOA-F using standard tools and instructions; process validated by usability testing.</t>
+          <t>Trays function correctly with new tank dimensions; verified in assembly and user testing.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -901,37 +889,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80k Pages</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Set and support a new warranty page life goal of 80,000 pages.</t>
+          <t>Integrate a 4.3” CGD display into the product for improved user interface.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Increases competitive positioning for high-use environments and reduces TCO.</t>
+          <t>Enhances usability and aligns with modern user expectations.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, End Users</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Component reliability, consumables yield</t>
+          <t>Electrical and mechanical integration, UI software.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Product must reliably print 80,000 pages without major service under standard use conditions.</t>
+          <t>Display operates with full functionality; passes usability and reliability tests.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -952,37 +940,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SKU 2 (Hi + Hi PDL) PaaS Enablement</t>
+          <t>Service Station Aerosol Management with Spit Platform Changes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Enable SKU 2 with high throughput and PDL (Page Description Language) for PaaS (Print as a Service) business models.</t>
+          <t>Implement aerosol management in the service station to handle changes due to increased tank size and spit platform updates.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Supports flexible business models and meets enterprise/SMB needs.</t>
+          <t>Maintains print quality and prevents contamination inside the printer.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Business, Channel Partners, IT</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Firmware, service platform integration</t>
+          <t>Service station and spit platform design.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SKU 2 available for PaaS, with high throughput and PDL support validated.</t>
+          <t>No aerosol-related print defects or contamination after 80,000 pages of operation.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1003,41 +991,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reddington ID with Increased Tank Size</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Adopt Reddington ID with an increased tank size; no change to Marconi-HI ADF.</t>
+          <t>Update the carriage dynamic and force model to account for new tube routing and increased weights from larger tanks.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Accommodates higher yield bottles and aligns with product family design.</t>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Design, Marketing</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Industrial design, mechanical engineering</t>
+          <t>Tube design, tank and carriage integration.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tank size increased and validated for new bottle compatibility; ID matches Reddington.</t>
+          <t>Carriage operates reliably under all tested conditions; no increased wear or failure.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1054,17 +1042,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
+          <t>Paper Path Enhancement for Increased Page Life</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel requirements for environmental standards (PDL SKU).</t>
+          <t>Modify paper path components to support increased warranty page life (80,000 pages).</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mandatory for regulatory compliance and market access.</t>
+          <t>Reduces maintenance and supports higher warranty targets.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1074,21 +1062,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Regulatory, Marketing, Sustainability</t>
+          <t>R&amp;D, Service, End Users</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Design, materials sourcing</t>
+          <t>Component material and design changes.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Product passes certification for EPEAT3, LOT4, and Blue Angel before launch.</t>
+          <t>Paper path components show no excessive wear after 80,000 pages.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1105,17 +1093,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Input/Output Tray Changes for Tank Protrusion</t>
+          <t>Ink Maintenance as a Serviceable Part Post-80K Life</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Redesign input and output trays to accommodate increased tank protrusion and optimize size.</t>
+          <t>Design ink maintenance components to be serviceable at a service center after 80,000 pages.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ensures proper paper handling and maintains compact footprint.</t>
+          <t>Extends printer life and supports service business model.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1125,21 +1113,21 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Design, R&amp;D, End Users</t>
+          <t>Service, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mechanical design, tray component sourcing</t>
+          <t>Component modularity and service documentation.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Trays fit with new tank size; paper handling performance unchanged or improved.</t>
+          <t>Service center can replace/maintain ink components after 80,000 pages within 30 minutes.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1156,41 +1144,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) for user interface.</t>
+          <t>Implement a new make-break and fluidic interface (FI) connection for the IDS system, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Improves user experience and aligns with modern UI expectations.</t>
+          <t>Improves reliability and compatibility with new ink system.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>End Users, Marketing, UI/UX</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Display sourcing, firmware UI</t>
+          <t>IDS, LEBI tank design, SHAID integration.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Product includes 4.3” CGD and passes usability testing.</t>
+          <t>System passes all connection integrity and leak tests in production units.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1207,22 +1195,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Update service station for improved aerosol management due to tank changes.</t>
+          <t>Develop a new IDS startup algorithm and air management system to support the new ink system.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Prevents contamination and ensures print quality.</t>
+          <t>Ensures reliable startup and prevents air-related print defects.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1232,12 +1220,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Service station design, tank integration</t>
+          <t>IDS hardware and firmware.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Aerosol containment validated in lab and field tests.</t>
+          <t>Startup passes 100% of reliability tests; no air-related failures reported in field trials.</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1258,41 +1246,41 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>New Print Quality Goals and Depletion Metrics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Update carriage dynamics and force models to account for new tube routing and increased component weights.</t>
+          <t>Establish new print quality (PQ) goals and ink depletion metrics to align with new page yield definitions.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ensures reliable printhead movement and system durability.</t>
+          <t>Ensures product meets customer expectations and yield claims.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Reliability Engineering</t>
+          <t>Product Management, R&amp;D, Quality</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mechanical engineering, simulation</t>
+          <t>Ink system, firmware algorithms.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Carriage system passes HP reliability and performance tests with new configuration.</t>
+          <t>Print quality and depletion metrics meet or exceed defined targets in validation tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1309,41 +1297,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Paper Path Upgrade for Increased Page Life</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Upgrade paper path to support increased page life (80k pages).</t>
+          <t>Continue use of Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new product.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Reduces wear and maintains print quality over extended use.</t>
+          <t>Reduces development costs and leverages proven components.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, End Users, Service</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Paper path component selection, reliability testing</t>
+          <t>Component compatibility with new system.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paper path components meet durability targets in accelerated life testing.</t>
+          <t>No issues found in integration and reliability tests with reused components.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1360,41 +1348,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part</t>
+          <t>Integration of Stingray Wi-Fi Module and Dune Firmware</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Make ink maintenance a serviceable part at service centers, especially post 80k page life.</t>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity and control.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Improves serviceability and extends product life.</t>
+          <t>Supports modern connectivity requirements and feature set.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>End Users, Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Part design, service training</t>
+          <t>Firmware and hardware integration.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Ink maintenance part available and replaceable at service centers post 80k pages.</t>
+          <t>Wireless features function as specified in all supported environments.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1411,17 +1399,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New IDS Make-Break and FI Connection</t>
+          <t>Gauss4.xx Security Implementation (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Implement new IDS make-break and fluidic interconnect (FI) connection, leveraging LEBI ink-tank with increased size, keying, and LOI SHAID.</t>
+          <t>Implement Gauss4.xx security features in hardware and firmware.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Improves reliability and security of ink delivery system.</t>
+          <t>Ensures compliance with HP security standards and protects customer data.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1431,17 +1419,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Supplies</t>
+          <t>Security, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>IDS design, firmware</t>
+          <t>HW &amp; FW design and integration.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>IDS connection passes reliability and security validation.</t>
+          <t>All security features pass HP security audit and penetration testing.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1462,17 +1450,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>PaaS Model and Solution Integration</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Develop new IDS startup algorithm and air management system.</t>
+          <t>Support PaaS (Printing as a Service) model and integrate with onboarding paths (Consumer/HPX, HP One, SMB Portal, ECP).</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ensures consistent print quality and reliable startup.</t>
+          <t>Enables flexible business models and broader market reach.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1482,17 +1470,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Firmware, R&amp;D</t>
+          <t>Business Development, Product Management, End Users</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IDS hardware, firmware development</t>
+          <t>Software and service platform integration.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Startup and air management validated in field and lab tests.</t>
+          <t>All onboarding and service paths functional and tested with PaaS.</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1513,17 +1501,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New PQ Goals and Depletion Definition</t>
+          <t>SMB Manageability and Enterprise Support (WJA, HPSM, JAM)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and deplete-to-empty definition to align with page yield targets.</t>
+          <t>Provide SMB manageability solutions and enterprise support for WJA, HPSM, and JAM.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ensures customer expectations are met for print quality and yield.</t>
+          <t>Expands market reach and supports business customer requirements.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1533,17 +1521,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Marketing</t>
+          <t>SMB and Enterprise Customers, Product Management, IT</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Print quality testing, yield analysis</t>
+          <t>Solution software integration.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PQ and depletion metrics defined and validated in test prints.</t>
+          <t>All specified enterprise solutions function as intended in customer environments.</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1564,45 +1552,45 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Reuse of Marconi Hi PDL and Tux dASIC</t>
+          <t>Host 12K-CMYK Trade Page (Flexible Priority)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Reuse Marconi Hi PDL, Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in new platform.</t>
+          <t>Support hosting a 12,000-page CMYK trade page yield as a flexible feature.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Reduces development cost and leverages proven components.</t>
+          <t>Provides flexibility for higher yield SKUs based on market demand.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Product Management, Marketing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Compatibility validation</t>
+          <t>Ink system capacity, SKU management.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Components function as required in new product context.</t>
+          <t>SKU with 12K-CMYK available for markets that require it.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1615,45 +1603,45 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module and Dune Firmware</t>
+          <t>SuperAmp PHA Life at 65K (Constrained Priority)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware for wireless connectivity.</t>
+          <t>Ensure SuperAmp PHA achieves a minimum life of 65,000 pages as a hard constraint.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Meets modern connectivity expectations and supports HP ecosystem.</t>
+          <t>Critical component reliability requirement for the platform.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>End Users, IT, R&amp;D</t>
+          <t>R&amp;D, Quality, Service</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Module sourcing, firmware integration</t>
+          <t>Component design and materials.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Wireless connectivity passes HP standard performance and security tests.</t>
+          <t>SuperAmp PHA passes all reliability tests for 65,000-page life.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1666,17 +1654,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Warranty Life of 2 Years (Optimized Priority)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx hardware and firmware security features.</t>
+          <t>Support a warranty life of 2 years for the product, in addition to page life targets.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Protects against modern security threats and meets enterprise requirements.</t>
+          <t>Aligns with competitive and customer expectations.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1686,17 +1674,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IT, Enterprise Customers, Security Team</t>
+          <t>Product Management, Warranty, End Users</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Firmware, hardware integration</t>
+          <t>Component reliability, support policies.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Security features validated against HP security standards.</t>
+          <t>Product warranty covers 2 years or 80,000 pages, whichever comes first.</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1704,7 +1692,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1717,17 +1705,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Support for Multiple Business Models and Solutions</t>
+          <t>Throughput of 25/20 ppm (PDL: 25/19 ppm)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Enable support for Consumer, SMB, and Enterprise business models, including PaaS, WorkFromHome/Flexworker, onboarding/S&amp;O paths, scan solutions, SMB manageability, and Enterprise support (WJA, HPSM, JAM).</t>
+          <t>Achieve print throughput of 25/20 pages per minute (PDL: 25/19 ppm).</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Expands market reach and meets diverse customer needs.</t>
+          <t>Meets market expectations for print speed in target segments.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1737,17 +1725,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Business, Channel Partners, End Users</t>
+          <t>End Users, Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Solution integration, firmware, services</t>
+          <t>Print engine design, firmware tuning.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>All listed business models and solutions supported and validated in launch readiness review.</t>
+          <t>Device achieves specified throughput in ISO standard test conditions.</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1768,139 +1756,135 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Clients &amp; Drivers Compatibility</t>
+          <t>Serviceability of Maintenance Box</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>Ensure the maintenance box is easily serviceable to optimize product uptime.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ensures seamless deployment and management in various environments.</t>
+          <t>Reduces downtime and service costs.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Service, End Users, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Mechanical design, service documentation.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Maintenance box can be replaced by service personnel within 10 minutes.</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AI Productivity and Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Implement AI-driven productivity, scan workflow, and device manageability solutions tailored for SMB customers, including features like Perfect Print and Perfect Scan.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AI solutions are a key differentiator, addressing SMB needs for efficiency and ease of management, especially for non-IT users.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>IT, End Users, Channel Partners</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Driver development, OS compatibility</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>All clients and drivers validated on supported platforms.</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Speed: 25/20ppm (PDL: 25/19ppm)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Achieve print speeds of 25/20 ppm (pages per minute), and 25/19 ppm for PDL SKU.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Meets market expectations for performance.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Requires integration with SMB portal and device management capabilities.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>AI-powered features (Perfect Print, Perfect Scan) demonstrably improve workflow efficiency and device manageability in user testing by at least 30% over baseline.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 11</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Design the product to achieve HP's lowest business TCO for SMB tank printers, minimizing both upfront and operational costs.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Cost efficiency is a primary purchasing driver for SMBs, and TCO is a core value proposition for Magellan.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Product Management, End Users</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Engine design, firmware optimization</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Print speed validated in standard HP performance tests.</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SuperAmp PHA Life at 65K Pages</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ensure SuperAmp PHA supports a minimum life of 65,000 pages.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Critical for reliability and cost of ownership.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, End Users</t>
+          <t>['Marketing', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PHA design, reliability testing</t>
+          <t>Requires efficient consumables, high-yield tanks, and low-maintenance design.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SuperAmp PHA passes life testing for 65,000 pages.</t>
+          <t>Product TCO is at least 10% lower than previous HP SMB tank printers and leading competitors, validated by cost analysis.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1908,101 +1892,101 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, 11</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Warranty Life: 2 Years or Page Limit</t>
+          <t>Serviceability: Customer-Replaceable and Service Center Parts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Provide a warranty of 2 years or up to defined page life, whichever comes first.</t>
+          <t>Enable customer-replaceable parts (PHA) and make MINK serviceable at service centers, with a target for customer replaceability if out of warranty.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Aligns with market standards and customer expectations.</t>
+          <t>SMBs lack dedicated IT staff, so easy serviceability reduces downtime and support costs.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>['Quality', 'R&amp;D Telemetry', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Design constraints for modular and accessible components.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>At least 80% of common maintenance tasks can be performed by end users without technical training, as validated by usability studies.</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Keyed Bottles for Consumables</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Use keyed bottles to prevent incorrect refilling and ensure compatibility with the printer.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Reduces user error and support incidents, improving reliability and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Product Management, Service</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Reliability targets, legal requirements</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Warranty terms published and supported in all launch regions.</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Serviceability: Maintenance Box</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Include a maintenance box as a serviceable component to improve serviceability.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Reduces downtime and simplifies maintenance.</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>['Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Component design, service documentation</t>
+          <t>Design of tank and bottle interface.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Maintenance box is field-replaceable and validated in service tests.</t>
+          <t>100% of bottles must be uniquely keyed to prevent incorrect installation in field tests.</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2010,110 +1994,114 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K</t>
+          <t>SMB Portal for Device Management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Support host-based 12K-CMYK and trade page 6K options as flexible priorities.</t>
+          <t>Provide a consolidated SMB portal for managing printers, targeting unmanaged and lightly managed SMB environments.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Provides options for different markets and customer segments.</t>
+          <t>Simplifies device management for non-IT users, improving efficiency and user experience.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Product Management, Channel Partners</t>
+          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Firmware, SKU configuration</t>
+          <t>Integration with AI manageability solutions and telemetry systems.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and trade 6K SKUs available for order and validated.</t>
+          <t>Portal allows users to add, monitor, and manage at least 10 devices with role-based access and reporting, validated in pilot deployments.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>Magellan MRD, Page 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>Support for PaaS (Platform as a Service)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-powered productivity, scan workflow, and manageability solutions into the Magellan printer to streamline business operations for SMBs.</t>
+          <t>Magellan must support HP's PaaS offerings, enabling advanced service models and solutions integration.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SMBs need easy-to-use, efficient tools to manage printing workflows without dedicated IT staff.</t>
+          <t>PaaS support is a strategic goal for HP to drive recurring revenue and solution stickiness.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Requires integration with SMB portal and AI solution infrastructure.</t>
+          <t>Requires software platform compatibility and service APIs.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>AI features for productivity, scanning, and device management are available and functional for SMB users. Usability validated by non-IT office managers.</t>
+          <t>Printer is fully certified with HP's PaaS platform and passes all integration and billing tests.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2121,37 +2109,37 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>PDL/PS Support and Speed Improvement</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Design Magellan to deliver the lowest TCO in HP's business printer lineup, minimizing intervention and maximizing efficiency.</t>
+          <t>For PDL SKU: Support PDL/PS and achieve print speeds of 25/20 ppm (improved from current 25/19 ppm).</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cost efficiency is a top purchasing driver for SMBs with limited budgets.</t>
+          <t>Meets business customer performance expectations and competitive benchmarks.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['Marketing', 'BA']</t>
+          <t>['R&amp;D Telemetry', 'Quality']</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Depends on consumable pricing, maintenance model, and supply chain management.</t>
+          <t>Hardware and firmware development for speed and protocol support.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Independent cost analysis shows Magellan has the lowest TCO compared to other HP business printers.</t>
+          <t>PDL SKU achieves minimum 25 ppm (mono) and 20 ppm (color) in standardized print tests, with full PDL/PS compatibility.</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2159,12 +2147,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2172,41 +2160,41 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Customer-Replaceable Maintenance Box</t>
+          <t>Blue Angel Certification</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Implement a replaceable maintenance box that allows end users to perform maintenance without service technician intervention.</t>
+          <t>Obtain Blue Angel environmental certification for PDL SKU.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs for SMBs lacking IT support.</t>
+          <t>Environmental certifications are increasingly required in procurement and valued by SMBs.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
+          <t>['Prod Steward', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Requires design changes and supply of maintenance kits.</t>
+          <t>Product design must meet Blue Angel criteria.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>End users can replace the maintenance box following provided instructions; validated by usability testing.</t>
+          <t>PDL SKU is certified by Blue Angel prior to product launch.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2215,7 +2203,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2223,37 +2211,37 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ensure the printer is manufactured with at least 60% recycled content plastic, surpassing key competitors in sustainability.</t>
+          <t>Introduce a replaceable maintenance box for the printer, a new feature for this segment.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Environmental responsibility is a growing requirement for businesses and offers a competitive advantage.</t>
+          <t>Reduces service downtime and lowers TCO for SMBs by allowing users to replace key maintenance components.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Marketing']</t>
+          <t>['Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Material sourcing and manufacturing process changes.</t>
+          <t>Design for user-replaceability and consumables logistics.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bill of materials and certification confirm 60% RCP in final product.</t>
+          <t>Maintenance box can be replaced by user in under 5 minutes with no tools, as validated in usability testing.</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2261,12 +2249,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2274,37 +2262,37 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SMB Portal for Device Management</t>
+          <t>High Sustainability: 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Develop a consolidated portal (SMB portal) for managing multiple printers, targeting unmanaged or lightly managed SMBs.</t>
+          <t>Achieve 60% recycled content plastic in product construction, exceeding major competitors (Epson 30%).</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Enables easy device management for offices without IT staff.</t>
+          <t>Sustainability is a key differentiator and customer demand.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>['Prod Steward', 'Marketing']</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Requires software development and integration with printer firmware.</t>
+          <t>Supply chain and materials sourcing.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Portal enables registration, monitoring, and management of all Magellan devices in an office environment.</t>
+          <t>Final product BOM shows at least 60% of plastics are from recycled sources, verified by supplier certifications.</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2312,12 +2300,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2325,50 +2313,50 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>Warranty: 80k Pages or 2 Years</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing via HP App, supporting modern work environments and BYOD scenarios.</t>
+          <t>Offer a warranty of 80,000 pages or 2 years, whichever comes first.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mobile device usage is prevalent in SMBs; enables flexibility and convenience.</t>
+          <t>Meets SMB expectations for reliability and reduces perceived risk.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD']</t>
+          <t>['Quality', 'Marketing']</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Requires app and firmware updates.</t>
+          <t>Component reliability and support infrastructure.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Users can print from mobile devices using the HP App with no additional setup.</t>
+          <t>Warranty policy is implemented and communicated in all launch regions.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -2376,17 +2364,17 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Warranty: 80,000 Pages or 2 Years</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Offer a warranty covering 80,000 pages or 2 years, whichever comes first, to align with SMB expectations.</t>
+          <t>Enable mobile printing capabilities and seamless integration with the HP App.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SMBs seek reliability and predictable service costs.</t>
+          <t>SMBs require flexible printing options, including from mobile devices.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2396,17 +2384,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['Quality', 'BA']</t>
+          <t>['GXD', 'BA']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Support and service readiness.</t>
+          <t>Mobile app development and printer firmware support.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Warranty terms are published and honored in all launch markets.</t>
+          <t>Printer is discoverable and fully functional via HP App on iOS and Android in field trials.</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2414,12 +2402,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -2427,17 +2415,17 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Supplies</t>
+          <t>Advanced Telemetry Requirements</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Use keyed bottles for ink supplies to prevent errors and ensure only compatible supplies are used.</t>
+          <t>Implement telemetry features to support device usage tracking, proactive support, and solution enhancements.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Reduces risk of incorrect refilling and ensures product reliability.</t>
+          <t>Telemetry enables better manageability, support, and future solution improvements for SMB customers.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2447,17 +2435,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Quality']</t>
+          <t>['R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Supply chain and packaging changes.</t>
+          <t>Requires secure data collection and cloud integration.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>All supply bottles are uniquely keyed and cannot be misused with other products.</t>
+          <t>Telemetry data is securely transmitted, stored, and accessible for at least 90% of deployed devices in pilot tests.</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2465,265 +2453,10 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Serviceability: PHA and MINK</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Design for serviceability: customer replaceable parts (PHA) and MINK at service center, with threshold target for customer replaceable items.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Minimizes downtime and reduces service costs for SMBs.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>['Quality', 'Supplies Quality']</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Design and documentation of replaceable/serviceable parts.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Parts designated as customer-replaceable are documented and validated via service manuals.</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>PDL SKU Performance and Features</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>PDL SKU to support print speeds of 25/20 ppm (improvement from current 25/19), PDL/PS support, and Blue Angel certification.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Meets higher performance and environmental standards required in certain markets.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>['Tech Reg', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Firmware and hardware updates, certification testing.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>PDL SKU achieves targeted print speeds, supports PDL/PS, and is Blue Angel certified.</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View Portal</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Non-PDL SKU to support SMB2.0 solutions and Advanced View SMB portal, as well as Platform-as-a-Service (PaaS) support.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Enables differentiated feature sets for different market segments and supports new business models.</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>['Marketing', 'BA', 'GXD']</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Software and service integration.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Non-PDL SKU is shipped with SMB2.0 solutions and Advanced View Portal enabled, and supports PaaS.</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Integrate 'Perfect Print' and 'Perfect Scan' AI solutions to optimize print and scan quality automatically.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Delivers superior user experience and reduces manual intervention for quality issues.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>['GXD', 'R&amp;D Telemetry']</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Requires AI software development and integration with printer hardware.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Print and scan outputs are optimized automatically and validated in user testing.</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 7, 11</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Telemetry Requirements</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Implement telemetry to collect usage, performance, and diagnostic data, supporting proactive support and product improvement.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Enables data-driven support, remote diagnostics, and continuous improvement.</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>['R&amp;D Telemetry', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Data privacy compliance, backend infrastructure.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Telemetry data is collected, transmitted securely, and used for product insights; compliant with data privacy regulations.</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 3, 12</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
         <is>
           <t>13</t>
         </is>
